--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -132,6 +132,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>建筑名称ID</t>
+  </si>
+  <si>
     <t>建筑名称</t>
   </si>
   <si>
@@ -165,6 +168,9 @@
     <t>UnlockCost</t>
   </si>
   <si>
+    <t>BuildingNameId</t>
+  </si>
+  <si>
     <t>EmployeeProfile</t>
   </si>
   <si>
@@ -222,7 +228,7 @@
     <t>2_7</t>
   </si>
   <si>
-    <t>经营扑克厅</t>
+    <t>精英扑克厅</t>
   </si>
   <si>
     <t>2_8</t>
@@ -270,7 +276,7 @@
     <t>1_5</t>
   </si>
   <si>
-    <t>研究院</t>
+    <t>研发部</t>
   </si>
   <si>
     <t>1_6</t>
@@ -484,12 +490,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1522,7 +1528,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
@@ -1530,12 +1536,14 @@
     <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="13.25" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1560,66 +1568,75 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="J2" s="1"/>
+      <c r="K2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="1"/>
+      <c r="K3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1629,9 +1646,10 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="J4" s="1"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <f>D5*1000+B5*100+C5</f>
         <v>1101</v>
@@ -1645,24 +1663,29 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <v>1302</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7">
+      <c r="H5" s="1">
+        <v>4010004</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A27" si="0">D6*1000+B6*100+C6</f>
         <v>1102</v>
@@ -1680,22 +1703,25 @@
         <v>1101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="7">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4010005</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
@@ -1710,25 +1736,28 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4010006</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
@@ -1746,22 +1775,25 @@
         <v>1103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="7">
+        <v>22</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4010007</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
@@ -1779,22 +1811,25 @@
         <v>1104</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="7">
+        <v>22</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4010008</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
@@ -1812,22 +1847,25 @@
         <v>1105</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="7">
+        <v>22</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4010009</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
@@ -1842,25 +1880,28 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="7">
+        <v>22</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4010010</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
@@ -1875,25 +1916,28 @@
         <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="7">
+        <v>22</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4010011</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
@@ -1911,22 +1955,25 @@
         <v>1108</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="7">
+        <v>22</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4010012</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
@@ -1941,25 +1988,28 @@
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>1109</v>
+        <v>1304</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="7">
+        <v>22</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4010013</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
@@ -1974,25 +2024,28 @@
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>1110</v>
+        <v>1202</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="7">
+        <v>22</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4010014</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>1112</v>
@@ -2010,22 +2063,25 @@
         <v>1111</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="7">
+        <v>22</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4010015</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>1201</v>
@@ -2041,22 +2097,25 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="7">
+      <c r="H17" s="1">
+        <v>4010016</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>1202</v>
@@ -2071,25 +2130,28 @@
         <v>1</v>
       </c>
       <c r="E18" s="2">
-        <v>1201</v>
+        <v>1106</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="7">
+        <v>47</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4010017</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>1301</v>
@@ -2105,22 +2167,25 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="7">
+      <c r="H19" s="1">
+        <v>4010018</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>1302</v>
@@ -2136,22 +2201,25 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" s="7">
+        <v>52</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4010021</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>1303</v>
@@ -2165,24 +2233,29 @@
       <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2">
+        <v>1102</v>
+      </c>
       <c r="F21" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" s="7">
+        <v>52</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4010019</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>1304</v>
@@ -2196,24 +2269,29 @@
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2">
+        <v>1303</v>
+      </c>
       <c r="F22" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" s="7">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1">
+        <v>4010020</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>1401</v>
@@ -2229,19 +2307,20 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="H23" s="1"/>
+      <c r="I23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>1402</v>
@@ -2257,19 +2336,20 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>61</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>1403</v>
@@ -2285,19 +2365,20 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>61</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>1404</v>
@@ -2313,19 +2394,20 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>61</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>1405</v>
@@ -2341,16 +2423,17 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -490,12 +490,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1663,9 +1663,7 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
-        <v>1302</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>21</v>
       </c>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
     <t>序列ID</t>
   </si>
   <si>
-    <t>赌场ID</t>
+    <t>场景ID</t>
   </si>
   <si>
     <t>解锁方式</t>
@@ -159,7 +159,7 @@
     <t>SequenceID</t>
   </si>
   <si>
-    <t>CasinoID</t>
+    <t>RegionID</t>
   </si>
   <si>
     <t>UnlockMethod</t>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -144,6 +144,9 @@
     <t>受影响的雇员类型</t>
   </si>
   <si>
+    <t>等级上限</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -172,6 +175,9 @@
   </si>
   <si>
     <t>EmployeeProfile</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
   </si>
   <si>
     <t>1990000_10000</t>
@@ -701,7 +707,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -722,6 +728,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -848,7 +867,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -860,34 +879,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -972,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -982,7 +1001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -990,6 +1009,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1528,7 +1556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
@@ -1540,10 +1568,11 @@
     <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="10" max="10" width="13.25" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="12" max="12" width="10.125" customWidth="1"/>
     <col min="13" max="13" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1577,66 +1606,75 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>12</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1647,9 +1685,10 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <f>D5*1000+B5*100+C5</f>
         <v>1101</v>
@@ -1665,25 +1704,28 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="1">
         <v>4010004</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="7">
+        <v>25</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A27" si="0">D6*1000+B6*100+C6</f>
         <v>1102</v>
@@ -1701,25 +1743,28 @@
         <v>1101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1">
         <v>4010005</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="7">
+        <v>27</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
@@ -1737,25 +1782,28 @@
         <v>1107</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1">
         <v>4010006</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="7">
+        <v>29</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
@@ -1773,25 +1821,28 @@
         <v>1103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1">
         <v>4010007</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="7">
+        <v>31</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
@@ -1809,25 +1860,28 @@
         <v>1104</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1">
         <v>4010008</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="7">
+        <v>33</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
@@ -1845,25 +1899,28 @@
         <v>1105</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1">
         <v>4010009</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="7">
+        <v>35</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
@@ -1881,25 +1938,28 @@
         <v>1110</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1">
         <v>4010010</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" s="7">
+        <v>37</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
@@ -1917,25 +1977,28 @@
         <v>1112</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="1">
         <v>4010011</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="7">
+        <v>39</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
@@ -1953,25 +2016,28 @@
         <v>1108</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H13" s="1">
         <v>4010012</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="7">
+        <v>41</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
@@ -1989,25 +2055,28 @@
         <v>1304</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H14" s="1">
         <v>4010013</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" s="7">
+        <v>43</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
@@ -2025,25 +2094,28 @@
         <v>1202</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H15" s="1">
         <v>4010014</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="7">
+        <v>45</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>1112</v>
@@ -2061,25 +2133,28 @@
         <v>1111</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H16" s="1">
         <v>4010015</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="7">
+        <v>47</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>1201</v>
@@ -2095,25 +2170,28 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H17" s="1">
         <v>4010016</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="7">
+        <v>50</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="10">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>1202</v>
@@ -2131,25 +2209,28 @@
         <v>1106</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H18" s="1">
         <v>4010017</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="7">
+        <v>52</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="10">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>1301</v>
@@ -2165,25 +2246,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H19" s="1">
         <v>4010018</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="7">
+        <v>55</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>1302</v>
@@ -2199,25 +2283,28 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H20" s="1">
         <v>4010021</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K20" s="7">
+        <v>57</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>1303</v>
@@ -2235,25 +2322,28 @@
         <v>1102</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H21" s="1">
         <v>4010019</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K21" s="7">
+        <v>59</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>1304</v>
@@ -2271,25 +2361,28 @@
         <v>1303</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H22" s="1">
         <v>4010020</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K22" s="7">
+        <v>61</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>1401</v>
@@ -2305,20 +2398,22 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="3" t="s">
-        <v>62</v>
+      <c r="I23" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>65</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>1402</v>
@@ -2334,20 +2429,22 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="I24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>1403</v>
@@ -2363,20 +2460,22 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="I25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>1404</v>
@@ -2392,20 +2491,22 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="I26" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>1405</v>
@@ -2421,18 +2522,20 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>71</v>
-      </c>
+      <c r="I27" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,39 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 建筑产金币
+2. 建筑产能量
+3. 服务能力
+4. 游戏上限
+5. 知名度
+6. 曝光度
+7. 联盟奖杯
+8. 宣传牌
+9. 风云榜
+10. 装饰-无作用
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -117,6 +149,9 @@
     <t>建筑分类</t>
   </si>
   <si>
+    <t>建筑属性分类</t>
+  </si>
+  <si>
     <t>序列ID</t>
   </si>
   <si>
@@ -157,6 +192,9 @@
   </si>
   <si>
     <t>type</t>
+  </si>
+  <si>
+    <t>typeValue</t>
   </si>
   <si>
     <t>SequenceID</t>
@@ -991,7 +1029,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,12 +1047,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1556,23 +1588,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
     <col min="2" max="2" width="9.125" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="13.25" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="18.25" customWidth="1"/>
-    <col min="10" max="10" width="13.25" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="12" width="10.125" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18.25" customWidth="1"/>
+    <col min="11" max="11" width="13.25" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="10.125" customWidth="1"/>
+    <col min="14" max="14" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1594,103 +1627,113 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:12">
+    <row r="2" ht="18" customHeight="1" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>12</v>
+      <c r="K2" s="1"/>
+      <c r="L2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>22</v>
+      <c r="K3" s="1"/>
+      <c r="L3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="2"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <f>D5*1000+B5*100+C5</f>
+        <f>E5*1000+B5*100+D5</f>
         <v>1101</v>
       </c>
       <c r="B5" s="2">
@@ -1702,69 +1745,75 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1">
         <v>4010004</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="8">
+        <v>10</v>
+      </c>
+      <c r="M5" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A27" si="0">E6*1000+B6*100+D6</f>
+        <v>1102</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1101</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="H6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="10">
-        <v>10</v>
-      </c>
-      <c r="L5" s="8">
-        <v>100</v>
+      <c r="I6" s="1">
+        <v>4010005</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="8">
+        <v>10</v>
+      </c>
+      <c r="M6" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1">
-        <f t="shared" ref="A6:A27" si="0">D6*1000+B6*100+C6</f>
-        <v>1102</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1101</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="1">
-        <v>4010005</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="10">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
@@ -1773,37 +1822,40 @@
         <v>1</v>
       </c>
       <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
         <v>3</v>
       </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
       <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
         <v>1107</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1">
         <v>4010006</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="10">
-        <v>10</v>
+      <c r="J7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="L7" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M7" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
@@ -1812,37 +1864,40 @@
         <v>1</v>
       </c>
       <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
       <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
         <v>1103</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1">
+        <v>25</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="1">
         <v>4010007</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="10">
-        <v>10</v>
+      <c r="J8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="L8" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M8" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
@@ -1851,37 +1906,40 @@
         <v>1</v>
       </c>
       <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
       <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
         <v>1104</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="1">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1">
         <v>4010008</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="10">
-        <v>10</v>
+      <c r="J9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="L9" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M9" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
@@ -1890,37 +1948,40 @@
         <v>1</v>
       </c>
       <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
         <v>6</v>
       </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
       <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
         <v>1105</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="1">
+        <v>25</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="1">
         <v>4010009</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" s="10">
-        <v>10</v>
+      <c r="J10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="L10" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M10" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
@@ -1929,37 +1990,40 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
         <v>7</v>
       </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
       <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
         <v>1110</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="1">
+        <v>25</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="1">
         <v>4010010</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="10">
-        <v>10</v>
+      <c r="J11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="L11" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M11" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
@@ -1968,37 +2032,40 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
         <v>8</v>
       </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
       <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
         <v>1112</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="1">
+        <v>25</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="1">
         <v>4010011</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="10">
-        <v>10</v>
+      <c r="J12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="L12" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M12" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
@@ -2007,37 +2074,40 @@
         <v>1</v>
       </c>
       <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
         <v>9</v>
       </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
       <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
         <v>1108</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="1">
+        <v>25</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="1">
         <v>4010012</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="10">
-        <v>10</v>
+      <c r="J13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="L13" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M13" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
@@ -2046,37 +2116,40 @@
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
         <v>1304</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="1">
+        <v>25</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1">
         <v>4010013</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="10">
-        <v>10</v>
+      <c r="J14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="L14" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M14" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
@@ -2085,37 +2158,40 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
         <v>11</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
       <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
         <v>1202</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="1">
+        <v>25</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="1">
         <v>4010014</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15" s="10">
-        <v>10</v>
+      <c r="J15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="L15" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M15" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>1112</v>
@@ -2124,37 +2200,40 @@
         <v>1</v>
       </c>
       <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
         <v>12</v>
       </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
       <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
         <v>1111</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="1">
+        <v>25</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1">
         <v>4010015</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="10">
-        <v>10</v>
+      <c r="J16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="L16" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="M16" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>1201</v>
@@ -2163,35 +2242,38 @@
         <v>2</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="1">
+        <v>25</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="1">
         <v>4010016</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="10">
+      <c r="J17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="8">
         <v>20</v>
       </c>
-      <c r="L17" s="8">
-        <v>100</v>
+      <c r="M17" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>1202</v>
@@ -2203,34 +2285,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
         <v>1106</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="1">
+        <v>25</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="1">
         <v>4010017</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="10">
+      <c r="J18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="8">
         <v>20</v>
       </c>
-      <c r="L18" s="8">
-        <v>100</v>
+      <c r="M18" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>1301</v>
@@ -2239,35 +2324,38 @@
         <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="1">
+        <v>25</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="1">
         <v>4010018</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" s="10">
+      <c r="J19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="8">
         <v>30</v>
       </c>
-      <c r="L19" s="8">
-        <v>100</v>
+      <c r="M19" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>1302</v>
@@ -2276,35 +2364,38 @@
         <v>3</v>
       </c>
       <c r="C20" s="2">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="1">
+        <v>25</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="1">
         <v>4010021</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K20" s="10">
+      <c r="J20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="8">
         <v>30</v>
       </c>
-      <c r="L20" s="8">
-        <v>100</v>
+      <c r="M20" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>1303</v>
@@ -2313,37 +2404,40 @@
         <v>3</v>
       </c>
       <c r="C21" s="2">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2">
         <v>3</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
       <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
         <v>1102</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="1">
+        <v>25</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="1">
         <v>4010019</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="J21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="8">
         <v>30</v>
       </c>
-      <c r="L21" s="8">
-        <v>100</v>
+      <c r="M21" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>1304</v>
@@ -2352,37 +2446,40 @@
         <v>3</v>
       </c>
       <c r="C22" s="2">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2">
         <v>4</v>
       </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
       <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
         <v>1303</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="1">
+        <v>25</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="1">
         <v>4010020</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K22" s="10">
+      <c r="J22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L22" s="8">
         <v>30</v>
       </c>
-      <c r="L22" s="8">
-        <v>100</v>
+      <c r="M22" s="6">
+        <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>1401</v>
@@ -2391,29 +2488,32 @@
         <v>4</v>
       </c>
       <c r="C23" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>1402</v>
@@ -2422,29 +2522,32 @@
         <v>4</v>
       </c>
       <c r="C24" s="5">
+        <v>8</v>
+      </c>
+      <c r="D24" s="5">
         <v>2</v>
       </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>1403</v>
@@ -2453,29 +2556,32 @@
         <v>4</v>
       </c>
       <c r="C25" s="5">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5">
         <v>3</v>
       </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>1404</v>
@@ -2484,29 +2590,32 @@
         <v>4</v>
       </c>
       <c r="C26" s="5">
+        <v>10</v>
+      </c>
+      <c r="D26" s="5">
         <v>4</v>
       </c>
-      <c r="D26" s="5">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>1405</v>
@@ -2515,27 +2624,30 @@
         <v>4</v>
       </c>
       <c r="C27" s="5">
+        <v>10</v>
+      </c>
+      <c r="D27" s="5">
         <v>5</v>
       </c>
-      <c r="D27" s="5">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+解锁顺序：根据数据的配置顺序来确定的。
+注：ID确定后不允许修改  前端在使用 。</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B1" authorId="0">
       <text>
         <r>
@@ -53,7 +76,7 @@
 1-游戏区
 2-休息区
 3-管理区
-4-参观区</t>
+4-参观区- 不点击操作，没加锁 默认显示</t>
         </r>
       </text>
     </comment>
@@ -107,8 +130,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-解锁建筑的前置条件；
-手动点击解锁；</t>
+解锁建筑的前置条件：建筑ID_等级
+注：手动点击解锁</t>
         </r>
       </text>
     </comment>
@@ -141,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -185,6 +208,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>map&lt;int{_}int&gt;{|}</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
@@ -221,6 +247,30 @@
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>研发部</t>
+  </si>
+  <si>
+    <t>1_6</t>
+  </si>
+  <si>
+    <t>1302_1</t>
+  </si>
+  <si>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>普通休息区</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>1201_1</t>
+  </si>
+  <si>
     <t>游戏</t>
   </si>
   <si>
@@ -230,40 +280,124 @@
     <t>1_1</t>
   </si>
   <si>
+    <t>1101_1</t>
+  </si>
+  <si>
+    <t>接待区</t>
+  </si>
+  <si>
+    <t>1_5</t>
+  </si>
+  <si>
+    <t>1102_1</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1_7</t>
+  </si>
+  <si>
+    <t>1303_2</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1_8</t>
+  </si>
+  <si>
+    <t>1101_3</t>
+  </si>
+  <si>
     <t>贵宾厅</t>
   </si>
   <si>
     <t>1_2</t>
   </si>
   <si>
+    <t>1304_4</t>
+  </si>
+  <si>
+    <t>欢乐捕鱼厅</t>
+  </si>
+  <si>
+    <t>1_3</t>
+  </si>
+  <si>
+    <t>1110_5</t>
+  </si>
+  <si>
+    <t>博弈扑克厅</t>
+  </si>
+  <si>
+    <t>1_4</t>
+  </si>
+  <si>
+    <t>1107_1</t>
+  </si>
+  <si>
     <t>辉煌厅</t>
   </si>
   <si>
     <t>2_1</t>
   </si>
   <si>
+    <t>1103_2</t>
+  </si>
+  <si>
     <t>鸿运厅</t>
   </si>
   <si>
     <t>2_2</t>
   </si>
   <si>
+    <t>1104_2</t>
+  </si>
+  <si>
     <t>尊享厅</t>
   </si>
   <si>
     <t>2_3</t>
   </si>
   <si>
+    <t>1105_3</t>
+  </si>
+  <si>
     <t>至尊厅</t>
   </si>
   <si>
     <t>2_4</t>
   </si>
   <si>
-    <t>博弈扑克厅</t>
-  </si>
-  <si>
-    <t>1_4</t>
+    <t>1106_4</t>
+  </si>
+  <si>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>2_10</t>
+  </si>
+  <si>
+    <t>1202_5</t>
+  </si>
+  <si>
+    <t>天际捕鱼厅</t>
+  </si>
+  <si>
+    <t>2_5</t>
+  </si>
+  <si>
+    <t>1111_1</t>
+  </si>
+  <si>
+    <t>富豪捕鱼厅</t>
+  </si>
+  <si>
+    <t>2_6</t>
+  </si>
+  <si>
+    <t>1112_2</t>
   </si>
   <si>
     <t>沙龙扑克厅</t>
@@ -272,70 +406,13 @@
     <t>2_7</t>
   </si>
   <si>
+    <t>1108_3</t>
+  </si>
+  <si>
     <t>精英扑克厅</t>
   </si>
   <si>
     <t>2_8</t>
-  </si>
-  <si>
-    <t>欢乐捕鱼厅</t>
-  </si>
-  <si>
-    <t>1_3</t>
-  </si>
-  <si>
-    <t>天际捕鱼厅</t>
-  </si>
-  <si>
-    <t>2_5</t>
-  </si>
-  <si>
-    <t>富豪捕鱼厅</t>
-  </si>
-  <si>
-    <t>2_6</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>普通休息区</t>
-  </si>
-  <si>
-    <t>1_11</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
-  </si>
-  <si>
-    <t>2_10</t>
-  </si>
-  <si>
-    <t>管理</t>
-  </si>
-  <si>
-    <t>接待区</t>
-  </si>
-  <si>
-    <t>1_5</t>
-  </si>
-  <si>
-    <t>研发部</t>
-  </si>
-  <si>
-    <t>1_6</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1_7</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1_8</t>
   </si>
   <si>
     <t>参观</t>
@@ -381,13 +458,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -545,18 +628,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -899,168 +976,195 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1589,1065 +1693,1074 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="6.875" customWidth="1"/>
-    <col min="2" max="2" width="9.125" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18.25" customWidth="1"/>
-    <col min="11" max="11" width="13.25" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.25" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:13">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="6" t="s">
+      <c r="H3" s="8"/>
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9" t="s">
         <v>24</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1">
-        <f>E5*1000+B5*100+D5</f>
+    <row r="5" s="2" customFormat="1" spans="1:13">
+      <c r="A5" s="12">
+        <f t="shared" ref="A5:A27" si="0">E5*1000+B5*100+D5</f>
+        <v>1302</v>
+      </c>
+      <c r="B5" s="13">
+        <v>3</v>
+      </c>
+      <c r="C5" s="13">
+        <v>4</v>
+      </c>
+      <c r="D5" s="13">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="12">
+        <v>4010021</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="13">
+        <v>30</v>
+      </c>
+      <c r="M5" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:13">
+      <c r="A6" s="12">
+        <f t="shared" si="0"/>
+        <v>1201</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13">
+        <v>2</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="12">
+        <v>4010016</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="13">
+        <v>20</v>
+      </c>
+      <c r="M6" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:13">
+      <c r="A7" s="12">
+        <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="B7" s="13">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="1">
+      <c r="H7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="12">
         <v>4010004</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="13">
+        <v>10</v>
+      </c>
+      <c r="M7" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:13">
+      <c r="A8" s="12">
+        <f t="shared" si="0"/>
+        <v>1301</v>
+      </c>
+      <c r="B8" s="13">
+        <v>3</v>
+      </c>
+      <c r="C8" s="13">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="8">
-        <v>10</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="I8" s="12">
+        <v>4010018</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="13">
+        <v>30</v>
+      </c>
+      <c r="M8" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1">
-        <f t="shared" ref="A6:A27" si="0">E6*1000+B6*100+D6</f>
+    <row r="9" s="2" customFormat="1" spans="1:13">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>1303</v>
+      </c>
+      <c r="B9" s="13">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13">
+        <v>5</v>
+      </c>
+      <c r="D9" s="13">
+        <v>3</v>
+      </c>
+      <c r="E9" s="13">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="12">
+        <v>4010019</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="13">
+        <v>30</v>
+      </c>
+      <c r="M9" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:13">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>1304</v>
+      </c>
+      <c r="B10" s="13">
+        <v>3</v>
+      </c>
+      <c r="C10" s="13">
+        <v>6</v>
+      </c>
+      <c r="D10" s="13">
+        <v>4</v>
+      </c>
+      <c r="E10" s="13">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="12">
+        <v>4010020</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="13">
+        <v>30</v>
+      </c>
+      <c r="M10" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:13">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B11" s="13">
+        <v>1</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1101</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="E11" s="13">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="1">
+      <c r="H11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="12">
         <v>4010005</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="8">
-        <v>10</v>
-      </c>
-      <c r="M6" s="6">
+      <c r="J11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="13">
+        <v>10</v>
+      </c>
+      <c r="M11" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1">
+    <row r="12" s="2" customFormat="1" spans="1:13">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="B12" s="13">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="12">
+        <v>4010013</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="13">
+        <v>10</v>
+      </c>
+      <c r="M12" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:13">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>1107</v>
+      </c>
+      <c r="B13" s="13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13">
+        <v>7</v>
+      </c>
+      <c r="E13" s="13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="12">
+        <v>4010010</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="13">
+        <v>10</v>
+      </c>
+      <c r="M13" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:13">
+      <c r="A14" s="12">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B14" s="13">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1107</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="E14" s="13">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H14" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="12">
         <v>4010006</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="8">
-        <v>10</v>
-      </c>
-      <c r="M7" s="6">
+      <c r="J14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="13">
+        <v>10</v>
+      </c>
+      <c r="M14" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1">
+    <row r="15" s="2" customFormat="1" spans="1:13">
+      <c r="A15" s="12">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B15" s="13">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
         <v>4</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1103</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="1">
+      <c r="H15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="12">
         <v>4010007</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="8">
-        <v>10</v>
-      </c>
-      <c r="M8" s="6">
+      <c r="J15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="13">
+        <v>10</v>
+      </c>
+      <c r="M15" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1">
+    <row r="16" s="2" customFormat="1" spans="1:13">
+      <c r="A16" s="12">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13">
         <v>5</v>
       </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1104</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="E16" s="13">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="1">
+      <c r="H16" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="12">
         <v>4010008</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="8">
-        <v>10</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="J16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="13">
+        <v>10</v>
+      </c>
+      <c r="M16" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1">
+    <row r="17" s="2" customFormat="1" spans="1:13">
+      <c r="A17" s="12">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B17" s="13">
+        <v>1</v>
+      </c>
+      <c r="C17" s="13">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13">
         <v>6</v>
       </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="E17" s="13">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="1">
+      <c r="H17" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="12">
         <v>4010009</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="8">
-        <v>10</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="J17" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="13">
+        <v>10</v>
+      </c>
+      <c r="M17" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1">
+    <row r="18" s="2" customFormat="1" spans="1:13">
+      <c r="A18" s="12">
         <f t="shared" si="0"/>
-        <v>1107</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1110</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B18" s="13">
+        <v>2</v>
+      </c>
+      <c r="C18" s="13">
+        <v>2</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2</v>
+      </c>
+      <c r="E18" s="13">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="1">
-        <v>4010010</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="8">
-        <v>10</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="H18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="12">
+        <v>4010017</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="13">
+        <v>20</v>
+      </c>
+      <c r="M18" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="1">
+    <row r="19" s="2" customFormat="1" spans="1:13">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>1111</v>
+      </c>
+      <c r="B19" s="13">
+        <v>1</v>
+      </c>
+      <c r="C19" s="13">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13">
+        <v>11</v>
+      </c>
+      <c r="E19" s="13">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="12">
+        <v>4010014</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="13">
+        <v>10</v>
+      </c>
+      <c r="M19" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:13">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>1112</v>
+      </c>
+      <c r="B20" s="13">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13">
+        <v>12</v>
+      </c>
+      <c r="E20" s="13">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="12">
+        <v>4010015</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="13">
+        <v>10</v>
+      </c>
+      <c r="M20" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:13">
+      <c r="A21" s="12">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B21" s="13">
+        <v>1</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13">
         <v>8</v>
       </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1112</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="1">
+      <c r="H21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="12">
         <v>4010011</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="8">
-        <v>10</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="J21" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L21" s="13">
+        <v>10</v>
+      </c>
+      <c r="M21" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="1">
+    <row r="22" s="2" customFormat="1" spans="1:13">
+      <c r="A22" s="12">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B22" s="13">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13">
         <v>9</v>
       </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1108</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="E22" s="13">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="1">
+      <c r="H22" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="12">
         <v>4010012</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="8">
-        <v>10</v>
-      </c>
-      <c r="M13" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1304</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="1">
-        <v>4010013</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="8">
-        <v>10</v>
-      </c>
-      <c r="M14" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>1111</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1202</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="1">
-        <v>4010014</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L15" s="8">
-        <v>10</v>
-      </c>
-      <c r="M15" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>1112</v>
-      </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>12</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1111</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="1">
-        <v>4010015</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L16" s="8">
-        <v>10</v>
-      </c>
-      <c r="M16" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>1201</v>
-      </c>
-      <c r="B17" s="2">
-        <v>2</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="1">
-        <v>4010016</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="8">
-        <v>20</v>
-      </c>
-      <c r="M17" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>1202</v>
-      </c>
-      <c r="B18" s="2">
-        <v>2</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1106</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="1">
-        <v>4010017</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="8">
-        <v>20</v>
-      </c>
-      <c r="M18" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>1301</v>
-      </c>
-      <c r="B19" s="2">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="1">
-        <v>4010018</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" s="8">
-        <v>30</v>
-      </c>
-      <c r="M19" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>1302</v>
-      </c>
-      <c r="B20" s="2">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="1">
-        <v>4010021</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" s="8">
-        <v>30</v>
-      </c>
-      <c r="M20" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>1303</v>
-      </c>
-      <c r="B21" s="2">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1102</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4010019</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="8">
-        <v>30</v>
-      </c>
-      <c r="M21" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>1304</v>
-      </c>
-      <c r="B22" s="2">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1303</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4010020</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L22" s="8">
-        <v>30</v>
-      </c>
-      <c r="M22" s="6">
+      <c r="J22" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" s="13">
+        <v>10</v>
+      </c>
+      <c r="M22" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="1">
+      <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>1401</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="10">
         <v>4</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="10">
         <v>7</v>
       </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="1">
+      <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>1402</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="10">
         <v>4</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="10">
         <v>8</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="10">
         <v>2</v>
       </c>
-      <c r="E24" s="5">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="1">
+      <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>1403</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="10">
         <v>4</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="10">
         <v>9</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="10">
         <v>3</v>
       </c>
-      <c r="E25" s="5">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="1">
+      <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>1404</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="10">
         <v>4</v>
       </c>
-      <c r="C26" s="5">
-        <v>10</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="10">
+        <v>10</v>
+      </c>
+      <c r="D26" s="10">
         <v>4</v>
       </c>
-      <c r="E26" s="5">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="1">
+      <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>1405</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="10">
         <v>4</v>
       </c>
-      <c r="C27" s="5">
-        <v>10</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="10">
+        <v>10</v>
+      </c>
+      <c r="D27" s="10">
         <v>5</v>
       </c>
-      <c r="E27" s="5">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -156,6 +156,30 @@
 10-导玩员
 20-服务员
 30-管理员</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这里的等级，根据 建筑配置表中的 最大等级来配置
+：BuildingUpgradeTable.xlsx
+</t>
         </r>
       </text>
     </comment>
@@ -1106,11 +1130,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1125,38 +1146,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1713,1054 +1704,1054 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="4" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="8"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:13">
-      <c r="A5" s="12">
+    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="A5" s="2">
         <f t="shared" ref="A5:A27" si="0">E5*1000+B5*100+D5</f>
         <v>1302</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="2">
         <v>4010021</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="3">
         <v>30</v>
       </c>
-      <c r="M5" s="17">
-        <v>10</v>
+      <c r="M5" s="6">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:13">
-      <c r="A6" s="12">
+    <row r="6" s="1" customFormat="1" spans="1:13">
+      <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>1201</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13">
-        <v>1</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="2">
         <v>4010016</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="3">
         <v>20</v>
       </c>
-      <c r="M6" s="17">
-        <v>10</v>
+      <c r="M6" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:13">
-      <c r="A7" s="12">
+    <row r="7" s="1" customFormat="1" spans="1:13">
+      <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>1</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14" t="s">
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="2">
         <v>4010004</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="3">
         <v>10</v>
       </c>
-      <c r="M7" s="17">
-        <v>10</v>
+      <c r="M7" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="12">
+    <row r="8" s="1" customFormat="1" spans="1:13">
+      <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>1301</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="3">
         <v>3</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="13">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13">
-        <v>1</v>
-      </c>
-      <c r="F8" s="14" t="s">
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="2">
         <v>4010018</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="3">
         <v>30</v>
       </c>
-      <c r="M8" s="17">
-        <v>10</v>
+      <c r="M8" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:13">
-      <c r="A9" s="12">
+    <row r="9" s="1" customFormat="1" spans="1:13">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>1303</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="3">
         <v>5</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="13">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="2">
         <v>4010019</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="3">
         <v>30</v>
       </c>
-      <c r="M9" s="17">
-        <v>10</v>
+      <c r="M9" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:13">
-      <c r="A10" s="12">
+    <row r="10" s="1" customFormat="1" spans="1:13">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>1304</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="3">
         <v>6</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="3">
         <v>4</v>
       </c>
-      <c r="E10" s="13">
-        <v>1</v>
-      </c>
-      <c r="F10" s="14" t="s">
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="2">
         <v>4010020</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="3">
         <v>30</v>
       </c>
-      <c r="M10" s="17">
-        <v>10</v>
+      <c r="M10" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:13">
-      <c r="A11" s="12">
+    <row r="11" s="1" customFormat="1" spans="1:13">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="B11" s="13">
-        <v>1</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
         <v>2</v>
       </c>
-      <c r="E11" s="13">
-        <v>1</v>
-      </c>
-      <c r="F11" s="14" t="s">
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="2">
         <v>4010005</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="3">
         <v>10</v>
       </c>
-      <c r="M11" s="17">
-        <v>10</v>
+      <c r="M11" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="12">
+    <row r="12" s="1" customFormat="1" spans="1:13">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="B12" s="13">
-        <v>1</v>
-      </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
         <v>10</v>
       </c>
-      <c r="E12" s="13">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="2">
         <v>4010013</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="3">
         <v>10</v>
       </c>
-      <c r="M12" s="17">
-        <v>10</v>
+      <c r="M12" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:13">
-      <c r="A13" s="12">
+    <row r="13" s="1" customFormat="1" spans="1:13">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="B13" s="13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
         <v>7</v>
       </c>
-      <c r="E13" s="13">
-        <v>1</v>
-      </c>
-      <c r="F13" s="14" t="s">
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="2">
         <v>4010010</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="3">
         <v>10</v>
       </c>
-      <c r="M13" s="17">
-        <v>10</v>
+      <c r="M13" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:13">
-      <c r="A14" s="12">
+    <row r="14" s="1" customFormat="1" spans="1:13">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="13">
-        <v>1</v>
-      </c>
-      <c r="F14" s="14" t="s">
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="2">
         <v>4010006</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="3">
         <v>10</v>
       </c>
-      <c r="M14" s="17">
-        <v>10</v>
+      <c r="M14" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:13">
-      <c r="A15" s="12">
+    <row r="15" s="1" customFormat="1" spans="1:13">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="B15" s="13">
-        <v>1</v>
-      </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="13">
-        <v>1</v>
-      </c>
-      <c r="F15" s="14" t="s">
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="2">
         <v>4010007</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="3">
         <v>10</v>
       </c>
-      <c r="M15" s="17">
-        <v>10</v>
+      <c r="M15" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:13">
-      <c r="A16" s="12">
+    <row r="16" s="1" customFormat="1" spans="1:13">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
         <v>5</v>
       </c>
-      <c r="E16" s="13">
-        <v>1</v>
-      </c>
-      <c r="F16" s="14" t="s">
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="2">
         <v>4010008</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="3">
         <v>10</v>
       </c>
-      <c r="M16" s="17">
-        <v>10</v>
+      <c r="M16" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:13">
-      <c r="A17" s="12">
+    <row r="17" s="1" customFormat="1" spans="1:13">
+      <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="B17" s="13">
-        <v>1</v>
-      </c>
-      <c r="C17" s="13">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
         <v>6</v>
       </c>
-      <c r="E17" s="13">
-        <v>1</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="2">
         <v>4010009</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="3">
         <v>10</v>
       </c>
-      <c r="M17" s="17">
-        <v>10</v>
+      <c r="M17" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:13">
-      <c r="A18" s="12">
+    <row r="18" s="1" customFormat="1" spans="1:13">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>1202</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="3">
         <v>2</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="3">
         <v>2</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="13">
-        <v>1</v>
-      </c>
-      <c r="F18" s="14" t="s">
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="2">
         <v>4010017</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="3">
         <v>20</v>
       </c>
-      <c r="M18" s="17">
-        <v>10</v>
+      <c r="M18" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:13">
-      <c r="A19" s="12">
+    <row r="19" s="1" customFormat="1" spans="1:13">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="B19" s="13">
-        <v>1</v>
-      </c>
-      <c r="C19" s="13">
-        <v>1</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
         <v>11</v>
       </c>
-      <c r="E19" s="13">
-        <v>1</v>
-      </c>
-      <c r="F19" s="14" t="s">
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="2">
         <v>4010014</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="3">
         <v>10</v>
       </c>
-      <c r="M19" s="17">
-        <v>10</v>
+      <c r="M19" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:13">
-      <c r="A20" s="12">
+    <row r="20" s="1" customFormat="1" spans="1:13">
+      <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>1112</v>
       </c>
-      <c r="B20" s="13">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13">
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
         <v>12</v>
       </c>
-      <c r="E20" s="13">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14" t="s">
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="2">
         <v>4010015</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="3">
         <v>10</v>
       </c>
-      <c r="M20" s="17">
-        <v>10</v>
+      <c r="M20" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:13">
-      <c r="A21" s="12">
+    <row r="21" s="1" customFormat="1" spans="1:13">
+      <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="B21" s="13">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
         <v>8</v>
       </c>
-      <c r="E21" s="13">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="2">
         <v>4010011</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="3">
         <v>10</v>
       </c>
-      <c r="M21" s="17">
-        <v>10</v>
+      <c r="M21" s="6">
+        <v>60</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:13">
-      <c r="A22" s="12">
+    <row r="22" s="1" customFormat="1" spans="1:13">
+      <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="B22" s="13">
-        <v>1</v>
-      </c>
-      <c r="C22" s="13">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13">
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
         <v>9</v>
       </c>
-      <c r="E22" s="13">
-        <v>1</v>
-      </c>
-      <c r="F22" s="14" t="s">
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="2">
         <v>4010012</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="3">
         <v>10</v>
       </c>
-      <c r="M22" s="17">
-        <v>10</v>
+      <c r="M22" s="6">
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="8">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>1401</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="3">
         <v>7</v>
       </c>
-      <c r="D23" s="10">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="9" t="s">
+      <c r="I23" s="2"/>
+      <c r="J23" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="8">
+      <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>1402</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="3">
         <v>4</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="3">
         <v>8</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="3">
         <v>2</v>
       </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="4" t="s">
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="9" t="s">
+      <c r="I24" s="2"/>
+      <c r="J24" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K24" s="18" t="s">
+      <c r="K24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="8">
+      <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>1403</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="3">
         <v>4</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="3">
         <v>9</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="3">
         <v>3</v>
       </c>
-      <c r="E25" s="10">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="4" t="s">
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="9" t="s">
+      <c r="I25" s="2"/>
+      <c r="J25" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="K25" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="8">
+      <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>1404</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="3">
         <v>4</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="3">
         <v>10</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="3">
         <v>4</v>
       </c>
-      <c r="E26" s="10">
-        <v>1</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="4" t="s">
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="19" t="s">
+      <c r="I26" s="2"/>
+      <c r="J26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="8">
+      <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>1405</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="3">
         <v>4</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="3">
         <v>10</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="3">
         <v>5</v>
       </c>
-      <c r="E27" s="10">
-        <v>1</v>
-      </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="4" t="s">
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="19" t="s">
+      <c r="I27" s="2"/>
+      <c r="J27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -199,9 +199,6 @@
     <t>建筑属性分类</t>
   </si>
   <si>
-    <t>序列ID</t>
-  </si>
-  <si>
     <t>场景ID</t>
   </si>
   <si>
@@ -220,15 +217,17 @@
     <t>建筑名称</t>
   </si>
   <si>
-    <t>建筑编号</t>
-  </si>
-  <si>
     <t>受影响的雇员类型</t>
   </si>
   <si>
     <t>等级上限</t>
   </si>
   <si>
+    <t>#重要说明：注：
+1. 该表配置数据顺序即为解锁建筑的顺序。
+2.修改了解锁顺序，前端文件“”也需要修改，直接找前端程序修改或策划自己去修改。</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -247,9 +246,6 @@
     <t>typeValue</t>
   </si>
   <si>
-    <t>SequenceID</t>
-  </si>
-  <si>
     <t>RegionID</t>
   </si>
   <si>
@@ -277,9 +273,6 @@
     <t>研发部</t>
   </si>
   <si>
-    <t>1_6</t>
-  </si>
-  <si>
     <t>1302_1</t>
   </si>
   <si>
@@ -289,9 +282,6 @@
     <t>普通休息区</t>
   </si>
   <si>
-    <t>1_11</t>
-  </si>
-  <si>
     <t>1201_1</t>
   </si>
   <si>
@@ -301,175 +291,112 @@
     <t>富贵厅</t>
   </si>
   <si>
-    <t>1_1</t>
-  </si>
-  <si>
     <t>1101_1</t>
   </si>
   <si>
     <t>接待区</t>
   </si>
   <si>
-    <t>1_5</t>
+    <t>1301_1</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_1</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1304_1</t>
+  </si>
+  <si>
+    <t>贵宾厅</t>
   </si>
   <si>
     <t>1102_1</t>
   </si>
   <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1_7</t>
-  </si>
-  <si>
-    <t>1303_2</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1_8</t>
-  </si>
-  <si>
-    <t>1101_3</t>
-  </si>
-  <si>
-    <t>贵宾厅</t>
-  </si>
-  <si>
-    <t>1_2</t>
-  </si>
-  <si>
-    <t>1304_4</t>
-  </si>
-  <si>
     <t>欢乐捕鱼厅</t>
   </si>
   <si>
-    <t>1_3</t>
-  </si>
-  <si>
-    <t>1110_5</t>
+    <t>1110_1</t>
   </si>
   <si>
     <t>博弈扑克厅</t>
   </si>
   <si>
-    <t>1_4</t>
-  </si>
-  <si>
     <t>1107_1</t>
   </si>
   <si>
     <t>辉煌厅</t>
   </si>
   <si>
-    <t>2_1</t>
-  </si>
-  <si>
-    <t>1103_2</t>
+    <t>1103_1</t>
   </si>
   <si>
     <t>鸿运厅</t>
   </si>
   <si>
-    <t>2_2</t>
-  </si>
-  <si>
-    <t>1104_2</t>
+    <t>1104_1</t>
   </si>
   <si>
     <t>尊享厅</t>
   </si>
   <si>
-    <t>2_3</t>
-  </si>
-  <si>
-    <t>1105_3</t>
+    <t>1105_1</t>
   </si>
   <si>
     <t>至尊厅</t>
   </si>
   <si>
-    <t>2_4</t>
-  </si>
-  <si>
-    <t>1106_4</t>
+    <t>1106_1</t>
   </si>
   <si>
     <t>VIP休息区</t>
   </si>
   <si>
-    <t>2_10</t>
-  </si>
-  <si>
-    <t>1202_5</t>
+    <t>1202_1</t>
   </si>
   <si>
     <t>天际捕鱼厅</t>
   </si>
   <si>
-    <t>2_5</t>
-  </si>
-  <si>
     <t>1111_1</t>
   </si>
   <si>
     <t>富豪捕鱼厅</t>
   </si>
   <si>
-    <t>2_6</t>
-  </si>
-  <si>
-    <t>1112_2</t>
+    <t>1112_1</t>
   </si>
   <si>
     <t>沙龙扑克厅</t>
   </si>
   <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>1108_3</t>
+    <t>1108_1</t>
   </si>
   <si>
     <t>精英扑克厅</t>
   </si>
   <si>
-    <t>2_8</t>
-  </si>
-  <si>
     <t>参观</t>
   </si>
   <si>
     <t>联盟奖杯台</t>
   </si>
   <si>
-    <t>1_12</t>
-  </si>
-  <si>
     <t>宣传牌</t>
   </si>
   <si>
-    <t>1_13</t>
-  </si>
-  <si>
     <t>风云榜</t>
   </si>
   <si>
-    <t>1_14</t>
-  </si>
-  <si>
     <t>装饰区1</t>
   </si>
   <si>
-    <t>2_9</t>
-  </si>
-  <si>
     <t>装饰区2</t>
-  </si>
-  <si>
-    <t>2_11</t>
   </si>
 </sst>
 </file>
@@ -482,7 +409,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,8 +418,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1000,141 +939,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1146,16 +1088,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1170,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1404,25 +1371,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1683,1077 +1650,928 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.25" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="5.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.9083333333333" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:13">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:12">
+      <c r="A5" s="10">
+        <v>1302</v>
+      </c>
+      <c r="B5" s="11">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="G5" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:13">
-      <c r="A5" s="2">
-        <f t="shared" ref="A5:A27" si="0">E5*1000+B5*100+D5</f>
-        <v>1302</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="H5" s="10">
+        <v>4010021</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="11">
+        <v>30</v>
+      </c>
+      <c r="K5" s="12">
+        <v>20</v>
+      </c>
+      <c r="L5" s="13"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:12">
+      <c r="A6" s="10">
+        <v>1201</v>
+      </c>
+      <c r="B6" s="11">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11">
+        <v>2</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="10">
+        <v>4010016</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="11">
+        <v>20</v>
+      </c>
+      <c r="K6" s="12">
+        <v>60</v>
+      </c>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:12">
+      <c r="A7" s="10">
+        <v>1101</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="10">
+        <v>4010004</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="11">
+        <v>10</v>
+      </c>
+      <c r="K7" s="12">
+        <v>60</v>
+      </c>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:12">
+      <c r="A8" s="10">
+        <v>1301</v>
+      </c>
+      <c r="B8" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C8" s="11">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="10">
+        <v>4010018</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="11">
+        <v>30</v>
+      </c>
+      <c r="K8" s="12">
+        <v>60</v>
+      </c>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:12">
+      <c r="A9" s="10">
+        <v>1303</v>
+      </c>
+      <c r="B9" s="11">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11">
+        <v>5</v>
+      </c>
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="10">
+        <v>4010019</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="11">
+        <v>30</v>
+      </c>
+      <c r="K9" s="12">
+        <v>60</v>
+      </c>
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:12">
+      <c r="A10" s="10">
+        <v>1304</v>
+      </c>
+      <c r="B10" s="11">
+        <v>3</v>
+      </c>
+      <c r="C10" s="11">
+        <v>6</v>
+      </c>
+      <c r="D10" s="11">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="10">
+        <v>4010020</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="11">
+        <v>30</v>
+      </c>
+      <c r="K10" s="12">
+        <v>60</v>
+      </c>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:12">
+      <c r="A11" s="10">
+        <v>1102</v>
+      </c>
+      <c r="B11" s="11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="10">
+        <v>4010005</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="11">
+        <v>10</v>
+      </c>
+      <c r="K11" s="12">
+        <v>60</v>
+      </c>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:12">
+      <c r="A12" s="10">
+        <v>1110</v>
+      </c>
+      <c r="B12" s="11">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="10">
+        <v>4010013</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="11">
+        <v>10</v>
+      </c>
+      <c r="K12" s="12">
+        <v>60</v>
+      </c>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:12">
+      <c r="A13" s="10">
+        <v>1107</v>
+      </c>
+      <c r="B13" s="11">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="10">
+        <v>4010010</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="11">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12">
+        <v>60</v>
+      </c>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:12">
+      <c r="A14" s="10">
+        <v>1103</v>
+      </c>
+      <c r="B14" s="11">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="10">
+        <v>4010006</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="11">
+        <v>10</v>
+      </c>
+      <c r="K14" s="12">
+        <v>60</v>
+      </c>
+      <c r="L14" s="14"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:12">
+      <c r="A15" s="10">
+        <v>1104</v>
+      </c>
+      <c r="B15" s="11">
+        <v>1</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="10">
+        <v>4010007</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="11">
+        <v>10</v>
+      </c>
+      <c r="K15" s="12">
+        <v>60</v>
+      </c>
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:12">
+      <c r="A16" s="10">
+        <v>1105</v>
+      </c>
+      <c r="B16" s="11">
+        <v>1</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="10">
+        <v>4010008</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="11">
+        <v>10</v>
+      </c>
+      <c r="K16" s="12">
+        <v>60</v>
+      </c>
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:12">
+      <c r="A17" s="10">
+        <v>1106</v>
+      </c>
+      <c r="B17" s="11">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="10">
+        <v>4010009</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="11">
+        <v>10</v>
+      </c>
+      <c r="K17" s="12">
+        <v>60</v>
+      </c>
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:12">
+      <c r="A18" s="10">
+        <v>1202</v>
+      </c>
+      <c r="B18" s="11">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="10">
+        <v>4010017</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="11">
+        <v>20</v>
+      </c>
+      <c r="K18" s="12">
+        <v>60</v>
+      </c>
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:12">
+      <c r="A19" s="10">
+        <v>1111</v>
+      </c>
+      <c r="B19" s="11">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="10">
+        <v>4010014</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="11">
+        <v>10</v>
+      </c>
+      <c r="K19" s="12">
+        <v>60</v>
+      </c>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:12">
+      <c r="A20" s="10">
+        <v>1112</v>
+      </c>
+      <c r="B20" s="11">
+        <v>1</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="10">
+        <v>4010015</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="11">
+        <v>10</v>
+      </c>
+      <c r="K20" s="12">
+        <v>60</v>
+      </c>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:12">
+      <c r="A21" s="10">
+        <v>1108</v>
+      </c>
+      <c r="B21" s="11">
+        <v>1</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="10">
+        <v>4010011</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" s="11">
+        <v>10</v>
+      </c>
+      <c r="K21" s="12">
+        <v>60</v>
+      </c>
+      <c r="L21" s="14"/>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:12">
+      <c r="A22" s="10">
+        <v>1109</v>
+      </c>
+      <c r="B22" s="11">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="10">
+        <v>4010012</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="11">
+        <v>10</v>
+      </c>
+      <c r="K22" s="12">
+        <v>60</v>
+      </c>
+      <c r="L22" s="14"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="10">
+        <v>1401</v>
+      </c>
+      <c r="B23" s="11">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2">
-        <v>4010021</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="3">
-        <v>30</v>
-      </c>
-      <c r="M5" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:13">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
-        <v>1201</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="2">
-        <v>4010016</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="3">
-        <v>20</v>
-      </c>
-      <c r="M6" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:13">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
-        <v>1101</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="2">
-        <v>4010004</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="C23" s="11">
+        <v>7</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="14"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="10">
+        <v>1402</v>
+      </c>
+      <c r="B24" s="11">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11">
+        <v>8</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="10">
+        <v>1403</v>
+      </c>
+      <c r="B25" s="11">
+        <v>4</v>
+      </c>
+      <c r="C25" s="11">
+        <v>9</v>
+      </c>
+      <c r="D25" s="11">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="10">
+        <v>1404</v>
+      </c>
+      <c r="B26" s="11">
+        <v>4</v>
+      </c>
+      <c r="C26" s="11">
         <v>10</v>
       </c>
-      <c r="M7" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:13">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>1301</v>
-      </c>
-      <c r="B8" s="3">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="2">
-        <v>4010018</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="3">
-        <v>30</v>
-      </c>
-      <c r="M8" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:13">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>1303</v>
-      </c>
-      <c r="B9" s="3">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="2">
-        <v>4010019</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="3">
-        <v>30</v>
-      </c>
-      <c r="M9" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:13">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>1304</v>
-      </c>
-      <c r="B10" s="3">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="D26" s="11">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="10">
+        <v>1405</v>
+      </c>
+      <c r="B27" s="11">
         <v>4</v>
       </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="2">
-        <v>4010020</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="3">
-        <v>30</v>
-      </c>
-      <c r="M10" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:13">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>1102</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="2">
-        <v>4010005</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="3">
+      <c r="C27" s="11">
         <v>10</v>
       </c>
-      <c r="M11" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:13">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="2">
-        <v>4010013</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="L12" s="3">
-        <v>10</v>
-      </c>
-      <c r="M12" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:13">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>1107</v>
-      </c>
-      <c r="B13" s="3">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>7</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="2">
-        <v>4010010</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="3">
-        <v>10</v>
-      </c>
-      <c r="M13" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:13">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>1103</v>
-      </c>
-      <c r="B14" s="3">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="2">
-        <v>4010006</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="3">
-        <v>10</v>
-      </c>
-      <c r="M14" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:13">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>1104</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="2">
-        <v>4010007</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" s="3">
-        <v>10</v>
-      </c>
-      <c r="M15" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:13">
-      <c r="A16" s="2">
-        <f t="shared" si="0"/>
-        <v>1105</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="2">
-        <v>4010008</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="D27" s="11">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L16" s="3">
-        <v>10</v>
-      </c>
-      <c r="M16" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:13">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>1106</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>6</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="2">
-        <v>4010009</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" s="3">
-        <v>10</v>
-      </c>
-      <c r="M17" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:13">
-      <c r="A18" s="2">
-        <f t="shared" si="0"/>
-        <v>1202</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="H27" s="10"/>
+      <c r="I27" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="2">
-        <v>4010017</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" s="3">
-        <v>20</v>
-      </c>
-      <c r="M18" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:13">
-      <c r="A19" s="2">
-        <f t="shared" si="0"/>
-        <v>1111</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
-        <v>11</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="2">
-        <v>4010014</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="3">
-        <v>10</v>
-      </c>
-      <c r="M19" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:13">
-      <c r="A20" s="2">
-        <f t="shared" si="0"/>
-        <v>1112</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3">
-        <v>12</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="2">
-        <v>4010015</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="3">
-        <v>10</v>
-      </c>
-      <c r="M20" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:13">
-      <c r="A21" s="2">
-        <f t="shared" si="0"/>
-        <v>1108</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="2">
-        <v>4010011</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="L21" s="3">
-        <v>10</v>
-      </c>
-      <c r="M21" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:13">
-      <c r="A22" s="2">
-        <f t="shared" si="0"/>
-        <v>1109</v>
-      </c>
-      <c r="B22" s="3">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3">
-        <v>9</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="2">
-        <v>4010012</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L22" s="3">
-        <v>10</v>
-      </c>
-      <c r="M22" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
-        <v>1401</v>
-      </c>
-      <c r="B23" s="3">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="2">
-        <f t="shared" si="0"/>
-        <v>1402</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
-        <v>1403</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>9</v>
-      </c>
-      <c r="D25" s="3">
-        <v>3</v>
-      </c>
-      <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="2">
-        <f t="shared" si="0"/>
-        <v>1404</v>
-      </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3">
-        <v>4</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="2">
-        <f t="shared" si="0"/>
-        <v>1405</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="14"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -270,7 +270,7 @@
     <t>管理</t>
   </si>
   <si>
-    <t>研发部</t>
+    <t>研发部\机台厅</t>
   </si>
   <si>
     <t>1302_1</t>
@@ -1661,7 +1661,7 @@
     <col min="6" max="6" width="18.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="17.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.9083333333333" style="2" customWidth="1"/>
@@ -1884,7 +1884,7 @@
         <v>10</v>
       </c>
       <c r="K7" s="12">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L7" s="14"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -1812,7 +1812,7 @@
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L5" s="13"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>10</v>
       </c>
       <c r="K7" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" s="14"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -270,7 +270,7 @@
     <t>管理</t>
   </si>
   <si>
-    <t>研发部\机台厅</t>
+    <t>研发部\游戏厅</t>
   </si>
   <si>
     <t>1302_1</t>
@@ -285,31 +285,25 @@
     <t>1201_1</t>
   </si>
   <si>
+    <t>接待区</t>
+  </si>
+  <si>
+    <t>1301_1</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_1</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1304_1</t>
+  </si>
+  <si>
     <t>游戏</t>
-  </si>
-  <si>
-    <t>富贵厅</t>
-  </si>
-  <si>
-    <t>1101_1</t>
-  </si>
-  <si>
-    <t>接待区</t>
-  </si>
-  <si>
-    <t>1301_1</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_1</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1304_1</t>
   </si>
   <si>
     <t>贵宾厅</t>
@@ -580,12 +574,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1650,7 +1644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="2" customWidth="1"/>
@@ -1854,13 +1848,13 @@
     </row>
     <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="10">
-        <v>1101</v>
+        <v>1301</v>
       </c>
       <c r="B7" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="11">
         <v>1</v>
@@ -1872,37 +1866,37 @@
         <v>24</v>
       </c>
       <c r="G7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="10">
+        <v>4010018</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="10">
-        <v>4010004</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="J7" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="L7" s="14"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="10">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B8" s="11">
         <v>3</v>
       </c>
       <c r="C8" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="11">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>24</v>
@@ -1911,10 +1905,10 @@
         <v>25</v>
       </c>
       <c r="H8" s="10">
-        <v>4010018</v>
+        <v>4010019</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" s="11">
         <v>30</v>
@@ -1926,19 +1920,19 @@
     </row>
     <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="10">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B9" s="11">
         <v>3</v>
       </c>
       <c r="C9" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>24</v>
@@ -1947,10 +1941,10 @@
         <v>25</v>
       </c>
       <c r="H9" s="10">
-        <v>4010019</v>
+        <v>4010020</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" s="11">
         <v>30</v>
@@ -1962,34 +1956,34 @@
     </row>
     <row r="10" s="2" customFormat="1" spans="1:12">
       <c r="A10" s="10">
-        <v>1304</v>
+        <v>1102</v>
       </c>
       <c r="B10" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" s="11">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H10" s="10">
-        <v>4010020</v>
+        <v>4010005</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J10" s="11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K10" s="12">
         <v>60</v>
@@ -1998,7 +1992,7 @@
     </row>
     <row r="11" s="2" customFormat="1" spans="1:12">
       <c r="A11" s="10">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="B11" s="11">
         <v>1</v>
@@ -2016,10 +2010,10 @@
         <v>24</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H11" s="10">
-        <v>4010005</v>
+        <v>4010013</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>40</v>
@@ -2034,7 +2028,7 @@
     </row>
     <row r="12" s="2" customFormat="1" spans="1:12">
       <c r="A12" s="10">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -2052,10 +2046,10 @@
         <v>24</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H12" s="10">
-        <v>4010013</v>
+        <v>4010010</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>42</v>
@@ -2070,7 +2064,7 @@
     </row>
     <row r="13" s="2" customFormat="1" spans="1:12">
       <c r="A13" s="10">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B13" s="11">
         <v>1</v>
@@ -2088,10 +2082,10 @@
         <v>24</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H13" s="10">
-        <v>4010010</v>
+        <v>4010006</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>44</v>
@@ -2106,7 +2100,7 @@
     </row>
     <row r="14" s="2" customFormat="1" spans="1:12">
       <c r="A14" s="10">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B14" s="11">
         <v>1</v>
@@ -2124,10 +2118,10 @@
         <v>24</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H14" s="10">
-        <v>4010006</v>
+        <v>4010007</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>46</v>
@@ -2142,7 +2136,7 @@
     </row>
     <row r="15" s="2" customFormat="1" spans="1:12">
       <c r="A15" s="10">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B15" s="11">
         <v>1</v>
@@ -2160,10 +2154,10 @@
         <v>24</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H15" s="10">
-        <v>4010007</v>
+        <v>4010008</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>48</v>
@@ -2178,7 +2172,7 @@
     </row>
     <row r="16" s="2" customFormat="1" spans="1:12">
       <c r="A16" s="10">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B16" s="11">
         <v>1</v>
@@ -2196,10 +2190,10 @@
         <v>24</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H16" s="10">
-        <v>4010008</v>
+        <v>4010009</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>50</v>
@@ -2214,13 +2208,13 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:12">
       <c r="A17" s="10">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="B17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="11">
         <v>1</v>
@@ -2232,16 +2226,16 @@
         <v>24</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H17" s="10">
-        <v>4010009</v>
+        <v>4010017</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K17" s="12">
         <v>60</v>
@@ -2250,13 +2244,13 @@
     </row>
     <row r="18" s="2" customFormat="1" spans="1:12">
       <c r="A18" s="10">
-        <v>1202</v>
+        <v>1111</v>
       </c>
       <c r="B18" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="11">
         <v>1</v>
@@ -2268,16 +2262,16 @@
         <v>24</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H18" s="10">
-        <v>4010017</v>
+        <v>4010014</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>54</v>
       </c>
       <c r="J18" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K18" s="12">
         <v>60</v>
@@ -2286,7 +2280,7 @@
     </row>
     <row r="19" s="2" customFormat="1" spans="1:12">
       <c r="A19" s="10">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B19" s="11">
         <v>1</v>
@@ -2304,10 +2298,10 @@
         <v>24</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H19" s="10">
-        <v>4010014</v>
+        <v>4010015</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>56</v>
@@ -2322,7 +2316,7 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="1:12">
       <c r="A20" s="10">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -2340,10 +2334,10 @@
         <v>24</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H20" s="10">
-        <v>4010015</v>
+        <v>4010011</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>58</v>
@@ -2358,7 +2352,7 @@
     </row>
     <row r="21" s="2" customFormat="1" spans="1:12">
       <c r="A21" s="10">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B21" s="11">
         <v>1</v>
@@ -2376,10 +2370,10 @@
         <v>24</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H21" s="10">
-        <v>4010011</v>
+        <v>4010012</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>60</v>
@@ -2392,51 +2386,43 @@
       </c>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:12">
+    <row r="22" spans="1:12">
       <c r="A22" s="10">
-        <v>1109</v>
+        <v>1401</v>
       </c>
       <c r="B22" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22" s="11">
         <v>1</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>61</v>
-      </c>
+      <c r="E22" s="11"/>
       <c r="F22" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="10">
-        <v>4010012</v>
-      </c>
-      <c r="I22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="J22" s="11">
-        <v>10</v>
-      </c>
-      <c r="K22" s="12">
-        <v>60</v>
-      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="10">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B23" s="11">
         <v>4</v>
       </c>
       <c r="C23" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="11">
         <v>1</v>
@@ -2446,11 +2432,11 @@
         <v>24</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
@@ -2458,13 +2444,13 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="10">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B24" s="11">
         <v>4</v>
       </c>
       <c r="C24" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="11">
         <v>1</v>
@@ -2474,11 +2460,11 @@
         <v>24</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
@@ -2486,13 +2472,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="10">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B25" s="11">
         <v>4</v>
       </c>
       <c r="C25" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="11">
         <v>1</v>
@@ -2502,11 +2488,11 @@
         <v>24</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H25" s="10"/>
-      <c r="I25" s="12" t="s">
-        <v>66</v>
+      <c r="I25" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
@@ -2514,7 +2500,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="10">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B26" s="11">
         <v>4</v>
@@ -2530,43 +2516,15 @@
         <v>24</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
       <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="10">
-        <v>1405</v>
-      </c>
-      <c r="B27" s="11">
-        <v>4</v>
-      </c>
-      <c r="C27" s="11">
-        <v>10</v>
-      </c>
-      <c r="D27" s="11">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27735" windowHeight="12150"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -130,12 +130,35 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+true:手动解锁，解锁条件要满足；
+false:自动解锁，解锁条件为空(用于创建新号首次进入场景触发)；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 解锁建筑的前置条件：建筑ID_等级
 注：手动点击解锁</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -203,6 +226,9 @@
   </si>
   <si>
     <t>解锁方式</t>
+  </si>
+  <si>
+    <t>解锁条件</t>
   </si>
   <si>
     <t>解锁消耗</t>
@@ -231,6 +257,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
@@ -249,6 +278,9 @@
     <t>RegionID</t>
   </si>
   <si>
+    <t>UnlockType</t>
+  </si>
+  <si>
     <t>UnlockMethod</t>
   </si>
   <si>
@@ -282,13 +314,10 @@
     <t>普通休息区</t>
   </si>
   <si>
+    <t>接待区</t>
+  </si>
+  <si>
     <t>1201_1</t>
-  </si>
-  <si>
-    <t>接待区</t>
-  </si>
-  <si>
-    <t>1301_1</t>
   </si>
   <si>
     <t>运营部</t>
@@ -574,23 +603,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -939,7 +974,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -963,16 +998,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -981,89 +1016,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1108,6 +1143,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1644,25 +1682,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.9083333333333" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.9083333333333" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1684,86 +1723,95 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4" t="s">
-        <v>12</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3"/>
       <c r="K2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1773,10 +1821,11 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="12"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:12">
+    <row r="5" s="2" customFormat="1" spans="1:13">
       <c r="A5" s="10">
         <v>1302</v>
       </c>
@@ -1789,28 +1838,31 @@
       <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11"/>
       <c r="G5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="10">
+        <v>27</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="10">
         <v>4010021</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="11">
         <v>30</v>
       </c>
-      <c r="K5" s="12">
+      <c r="L5" s="12">
         <v>10</v>
       </c>
-      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:12">
+    <row r="6" s="2" customFormat="1" spans="1:13">
       <c r="A6" s="10">
         <v>1201</v>
       </c>
@@ -1823,30 +1875,33 @@
       <c r="D6" s="11">
         <v>1</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="H6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="10">
         <v>4010016</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="11">
         <v>20</v>
       </c>
-      <c r="K6" s="12">
+      <c r="L6" s="12">
         <v>60</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:12">
+    <row r="7" s="2" customFormat="1" spans="1:13">
       <c r="A7" s="10">
         <v>1301</v>
       </c>
@@ -1859,30 +1914,31 @@
       <c r="D7" s="11">
         <v>1</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="10">
+        <v>4010018</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="11">
         <v>30</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="10">
-        <v>4010018</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="11">
-        <v>30</v>
-      </c>
-      <c r="K7" s="12">
+      <c r="L7" s="12">
         <v>60</v>
       </c>
-      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:12">
+    <row r="8" s="2" customFormat="1" spans="1:13">
       <c r="A8" s="10">
         <v>1303</v>
       </c>
@@ -1895,30 +1951,33 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>32</v>
+      <c r="E8" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="10">
+        <v>27</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="10">
         <v>4010019</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="11">
         <v>30</v>
       </c>
-      <c r="K8" s="12">
+      <c r="L8" s="12">
         <v>60</v>
       </c>
-      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:12">
+    <row r="9" s="2" customFormat="1" spans="1:13">
       <c r="A9" s="10">
         <v>1304</v>
       </c>
@@ -1931,30 +1990,33 @@
       <c r="D9" s="11">
         <v>1</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>34</v>
+      <c r="E9" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="10">
+        <v>27</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="10">
         <v>4010020</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="11">
         <v>30</v>
       </c>
-      <c r="K9" s="12">
+      <c r="L9" s="12">
         <v>60</v>
       </c>
-      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:12">
+    <row r="10" s="2" customFormat="1" spans="1:13">
       <c r="A10" s="10">
         <v>1102</v>
       </c>
@@ -1967,30 +2029,33 @@
       <c r="D10" s="11">
         <v>1</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>36</v>
+      <c r="E10" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="10">
+        <v>27</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="10">
         <v>4010005</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="11">
         <v>10</v>
       </c>
-      <c r="K10" s="12">
+      <c r="L10" s="12">
         <v>60</v>
       </c>
-      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:12">
+    <row r="11" s="2" customFormat="1" spans="1:13">
       <c r="A11" s="10">
         <v>1110</v>
       </c>
@@ -2003,30 +2068,33 @@
       <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="I11" s="10">
         <v>4010013</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="11">
         <v>10</v>
       </c>
-      <c r="K11" s="12">
+      <c r="L11" s="12">
         <v>60</v>
       </c>
-      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:12">
+    <row r="12" s="2" customFormat="1" spans="1:13">
       <c r="A12" s="10">
         <v>1107</v>
       </c>
@@ -2039,30 +2107,33 @@
       <c r="D12" s="11">
         <v>1</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>41</v>
+      <c r="E12" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="10">
+        <v>27</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="10">
         <v>4010010</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="11">
         <v>10</v>
       </c>
-      <c r="K12" s="12">
+      <c r="L12" s="12">
         <v>60</v>
       </c>
-      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:12">
+    <row r="13" s="2" customFormat="1" spans="1:13">
       <c r="A13" s="10">
         <v>1103</v>
       </c>
@@ -2075,30 +2146,33 @@
       <c r="D13" s="11">
         <v>1</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>43</v>
+      <c r="E13" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="10">
+        <v>27</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="10">
         <v>4010006</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="11">
         <v>10</v>
       </c>
-      <c r="K13" s="12">
+      <c r="L13" s="12">
         <v>60</v>
       </c>
-      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:12">
+    <row r="14" s="2" customFormat="1" spans="1:13">
       <c r="A14" s="10">
         <v>1104</v>
       </c>
@@ -2111,30 +2185,33 @@
       <c r="D14" s="11">
         <v>1</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>45</v>
+      <c r="E14" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="10">
+        <v>27</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="10">
         <v>4010007</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11">
         <v>10</v>
       </c>
-      <c r="K14" s="12">
+      <c r="L14" s="12">
         <v>60</v>
       </c>
-      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:12">
+    <row r="15" s="2" customFormat="1" spans="1:13">
       <c r="A15" s="10">
         <v>1105</v>
       </c>
@@ -2147,30 +2224,33 @@
       <c r="D15" s="11">
         <v>1</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>47</v>
+      <c r="E15" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="10">
+        <v>27</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="10">
         <v>4010008</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="11">
         <v>10</v>
       </c>
-      <c r="K15" s="12">
+      <c r="L15" s="12">
         <v>60</v>
       </c>
-      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:12">
+    <row r="16" s="2" customFormat="1" spans="1:13">
       <c r="A16" s="10">
         <v>1106</v>
       </c>
@@ -2183,30 +2263,33 @@
       <c r="D16" s="11">
         <v>1</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>49</v>
+      <c r="E16" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="10">
+        <v>27</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="10">
         <v>4010009</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="11">
         <v>10</v>
       </c>
-      <c r="K16" s="12">
+      <c r="L16" s="12">
         <v>60</v>
       </c>
-      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:12">
+    <row r="17" s="2" customFormat="1" spans="1:13">
       <c r="A17" s="10">
         <v>1202</v>
       </c>
@@ -2219,30 +2302,33 @@
       <c r="D17" s="11">
         <v>1</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>51</v>
+      <c r="E17" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="10">
+        <v>27</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="10">
         <v>4010017</v>
       </c>
-      <c r="I17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="11">
         <v>20</v>
       </c>
-      <c r="K17" s="12">
+      <c r="L17" s="12">
         <v>60</v>
       </c>
-      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:12">
+    <row r="18" s="2" customFormat="1" spans="1:13">
       <c r="A18" s="10">
         <v>1111</v>
       </c>
@@ -2255,30 +2341,33 @@
       <c r="D18" s="11">
         <v>1</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>53</v>
+      <c r="E18" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="10">
+        <v>27</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="10">
         <v>4010014</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="11">
         <v>10</v>
       </c>
-      <c r="K18" s="12">
+      <c r="L18" s="12">
         <v>60</v>
       </c>
-      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:12">
+    <row r="19" s="2" customFormat="1" spans="1:13">
       <c r="A19" s="10">
         <v>1112</v>
       </c>
@@ -2291,30 +2380,33 @@
       <c r="D19" s="11">
         <v>1</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>55</v>
+      <c r="E19" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="10">
+        <v>27</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="10">
         <v>4010015</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="11">
         <v>10</v>
       </c>
-      <c r="K19" s="12">
+      <c r="L19" s="12">
         <v>60</v>
       </c>
-      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:12">
+    <row r="20" s="2" customFormat="1" spans="1:13">
       <c r="A20" s="10">
         <v>1108</v>
       </c>
@@ -2327,30 +2419,33 @@
       <c r="D20" s="11">
         <v>1</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>57</v>
+      <c r="E20" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="10">
+        <v>27</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="10">
         <v>4010011</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="11">
         <v>10</v>
       </c>
-      <c r="K20" s="12">
+      <c r="L20" s="12">
         <v>60</v>
       </c>
-      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:12">
+    <row r="21" s="2" customFormat="1" spans="1:13">
       <c r="A21" s="10">
         <v>1109</v>
       </c>
@@ -2363,30 +2458,33 @@
       <c r="D21" s="11">
         <v>1</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>59</v>
+      <c r="E21" s="11" t="b">
+        <v>1</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="10">
+        <v>27</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="10">
         <v>4010012</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="J21" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" s="11">
+        <v>10</v>
+      </c>
+      <c r="L21" s="12">
         <v>60</v>
       </c>
-      <c r="J21" s="11">
-        <v>10</v>
-      </c>
-      <c r="K21" s="12">
-        <v>60</v>
-      </c>
-      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="10">
         <v>1401</v>
       </c>
@@ -2399,22 +2497,25 @@
       <c r="D22" s="11">
         <v>1</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E22" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15"/>
       <c r="G22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="10"/>
-      <c r="I22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J22" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" s="10"/>
+      <c r="J22" s="12" t="s">
+        <v>64</v>
+      </c>
       <c r="K22" s="12"/>
-      <c r="L22" s="14"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="14"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:13">
       <c r="A23" s="10">
         <v>1402</v>
       </c>
@@ -2427,22 +2528,25 @@
       <c r="D23" s="11">
         <v>1</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E23" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15"/>
       <c r="G23" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="K23" s="12"/>
-      <c r="L23" s="14"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:13">
       <c r="A24" s="10">
         <v>1403</v>
       </c>
@@ -2455,22 +2559,25 @@
       <c r="D24" s="11">
         <v>1</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E24" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15"/>
       <c r="G24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="K24" s="12"/>
-      <c r="L24" s="14"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="14"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:13">
       <c r="A25" s="10">
         <v>1404</v>
       </c>
@@ -2483,22 +2590,25 @@
       <c r="D25" s="11">
         <v>1</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E25" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15"/>
       <c r="G25" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" s="10"/>
+      <c r="J25" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="K25" s="12"/>
-      <c r="L25" s="14"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="14"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:13">
       <c r="A26" s="10">
         <v>1405</v>
       </c>
@@ -2511,20 +2621,23 @@
       <c r="D26" s="11">
         <v>1</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="E26" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15"/>
       <c r="G26" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J26" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="10"/>
+      <c r="J26" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="K26" s="12"/>
-      <c r="L26" s="14"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27735" windowHeight="12150"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
   <si>
     <t>ID</t>
   </si>
@@ -296,112 +296,136 @@
     <t>MaxLevel</t>
   </si>
   <si>
+    <t>1990000_1000000</t>
+  </si>
+  <si>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>研发部\游戏厅</t>
+  </si>
+  <si>
+    <t>游戏</t>
+  </si>
+  <si>
+    <t>贵宾厅</t>
+  </si>
+  <si>
+    <t>接待区</t>
+  </si>
+  <si>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>普通休息区</t>
+  </si>
+  <si>
+    <t>欢乐捕鱼厅</t>
+  </si>
+  <si>
+    <t>1110_1</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>博弈扑克厅</t>
+  </si>
+  <si>
+    <t>1107_1</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_1</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
+    <t>辉煌厅</t>
+  </si>
+  <si>
+    <t>1103_1</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>鸿运厅</t>
+  </si>
+  <si>
+    <t>1104_1</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>尊享厅</t>
+  </si>
+  <si>
+    <t>1105_1</t>
+  </si>
+  <si>
+    <t>1990000_15000000</t>
+  </si>
+  <si>
+    <t>至尊厅</t>
+  </si>
+  <si>
+    <t>1106_1</t>
+  </si>
+  <si>
+    <t>1990000_18000000</t>
+  </si>
+  <si>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>1202_1</t>
+  </si>
+  <si>
+    <t>1990000_20000000</t>
+  </si>
+  <si>
+    <t>天际捕鱼厅</t>
+  </si>
+  <si>
+    <t>1111_1</t>
+  </si>
+  <si>
+    <t>1990000_25000000</t>
+  </si>
+  <si>
+    <t>富豪捕鱼厅</t>
+  </si>
+  <si>
+    <t>1112_1</t>
+  </si>
+  <si>
+    <t>1990000_30000000</t>
+  </si>
+  <si>
+    <t>沙龙扑克厅</t>
+  </si>
+  <si>
+    <t>1108_1</t>
+  </si>
+  <si>
+    <t>1990000_50000000</t>
+  </si>
+  <si>
+    <t>精英扑克厅</t>
+  </si>
+  <si>
     <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>管理</t>
-  </si>
-  <si>
-    <t>研发部\游戏厅</t>
-  </si>
-  <si>
-    <t>1302_1</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>普通休息区</t>
-  </si>
-  <si>
-    <t>接待区</t>
-  </si>
-  <si>
-    <t>1201_1</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_1</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1304_1</t>
-  </si>
-  <si>
-    <t>游戏</t>
-  </si>
-  <si>
-    <t>贵宾厅</t>
-  </si>
-  <si>
-    <t>1102_1</t>
-  </si>
-  <si>
-    <t>欢乐捕鱼厅</t>
-  </si>
-  <si>
-    <t>1110_1</t>
-  </si>
-  <si>
-    <t>博弈扑克厅</t>
-  </si>
-  <si>
-    <t>1107_1</t>
-  </si>
-  <si>
-    <t>辉煌厅</t>
-  </si>
-  <si>
-    <t>1103_1</t>
-  </si>
-  <si>
-    <t>鸿运厅</t>
-  </si>
-  <si>
-    <t>1104_1</t>
-  </si>
-  <si>
-    <t>尊享厅</t>
-  </si>
-  <si>
-    <t>1105_1</t>
-  </si>
-  <si>
-    <t>至尊厅</t>
-  </si>
-  <si>
-    <t>1106_1</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
-  </si>
-  <si>
-    <t>1202_1</t>
-  </si>
-  <si>
-    <t>天际捕鱼厅</t>
-  </si>
-  <si>
-    <t>1111_1</t>
-  </si>
-  <si>
-    <t>富豪捕鱼厅</t>
-  </si>
-  <si>
-    <t>1112_1</t>
-  </si>
-  <si>
-    <t>沙龙扑克厅</t>
-  </si>
-  <si>
-    <t>1108_1</t>
-  </si>
-  <si>
-    <t>精英扑克厅</t>
   </si>
   <si>
     <t>参观</t>
@@ -432,7 +456,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +467,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -814,39 +844,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -968,186 +970,189 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1685,54 +1690,54 @@
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.9083333333333" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1743,19 +1748,19 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="7" t="s">
@@ -1764,880 +1769,860 @@
       <c r="G2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="9"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:13">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>1302</v>
       </c>
-      <c r="B5" s="11">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12">
         <v>4</v>
       </c>
-      <c r="D5" s="11">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11" t="s">
+      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="11">
         <v>4010021</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="12">
         <v>30</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="2">
         <v>10</v>
       </c>
       <c r="M5" s="13"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:13">
-      <c r="A6" s="10">
-        <v>1201</v>
-      </c>
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="11">
-        <v>2</v>
-      </c>
-      <c r="D6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="A6" s="11">
+        <v>1102</v>
+      </c>
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11">
+        <v>4010005</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="10">
-        <v>4010016</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="11">
-        <v>20</v>
-      </c>
-      <c r="L6" s="12">
+      <c r="K6" s="12">
+        <v>10</v>
+      </c>
+      <c r="L6" s="2">
         <v>60</v>
       </c>
       <c r="M6" s="14"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:13">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>1301</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="12">
         <v>3</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="12">
         <v>3</v>
       </c>
-      <c r="D7" s="11">
-        <v>1</v>
-      </c>
-      <c r="E7" s="15" t="b">
+      <c r="D7" s="12">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <v>4010018</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="11">
+      <c r="J7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="12">
         <v>30</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="2">
         <v>60</v>
       </c>
       <c r="M7" s="14"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="10">
-        <v>1303</v>
-      </c>
-      <c r="B8" s="11">
-        <v>3</v>
-      </c>
-      <c r="C8" s="11">
-        <v>5</v>
-      </c>
-      <c r="D8" s="11">
-        <v>1</v>
-      </c>
-      <c r="E8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="A8" s="11">
+        <v>1201</v>
+      </c>
+      <c r="B8" s="12">
+        <v>2</v>
+      </c>
+      <c r="C8" s="12">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="11">
+        <v>4010016</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="10">
-        <v>4010019</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="11">
-        <v>30</v>
-      </c>
-      <c r="L8" s="12">
+      <c r="K8" s="12">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2">
         <v>60</v>
       </c>
       <c r="M8" s="14"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:13">
-      <c r="A9" s="10">
+    <row r="9" s="3" customFormat="1" spans="1:13">
+      <c r="A9" s="9">
+        <v>1110</v>
+      </c>
+      <c r="B9" s="10">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="9">
+        <v>4010013</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="10">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
+        <v>60</v>
+      </c>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:13">
+      <c r="A10" s="9">
+        <v>1107</v>
+      </c>
+      <c r="B10" s="10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="9">
+        <v>4010010</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="10">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
+        <v>60</v>
+      </c>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:13">
+      <c r="A11" s="9">
+        <v>1303</v>
+      </c>
+      <c r="B11" s="10">
+        <v>3</v>
+      </c>
+      <c r="C11" s="10">
+        <v>5</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="9">
+        <v>4010019</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="10">
+        <v>30</v>
+      </c>
+      <c r="L11" s="3">
+        <v>60</v>
+      </c>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:13">
+      <c r="A12" s="9">
         <v>1304</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B12" s="10">
         <v>3</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C12" s="10">
         <v>6</v>
       </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="11" t="s">
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I12" s="9">
         <v>4010020</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="11">
+      <c r="J12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="10">
         <v>30</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L12" s="3">
         <v>60</v>
       </c>
-      <c r="M9" s="14"/>
+      <c r="M12" s="15"/>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:13">
-      <c r="A10" s="10">
-        <v>1102</v>
-      </c>
-      <c r="B10" s="11">
-        <v>1</v>
-      </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
-        <v>1</v>
-      </c>
-      <c r="E10" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="11" t="s">
+    <row r="13" s="3" customFormat="1" spans="1:13">
+      <c r="A13" s="9">
+        <v>1103</v>
+      </c>
+      <c r="B13" s="10">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="10">
-        <v>4010005</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="11">
+      <c r="G13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="9">
+        <v>4010006</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="10">
         <v>10</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L13" s="3">
         <v>60</v>
       </c>
-      <c r="M10" s="14"/>
+      <c r="M13" s="15"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:13">
-      <c r="A11" s="10">
-        <v>1110</v>
-      </c>
-      <c r="B11" s="11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="10">
-        <v>4010013</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="11">
+    <row r="14" s="3" customFormat="1" spans="1:13">
+      <c r="A14" s="9">
+        <v>1104</v>
+      </c>
+      <c r="B14" s="10">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="9">
+        <v>4010007</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="10">
         <v>10</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L14" s="3">
         <v>60</v>
       </c>
-      <c r="M11" s="14"/>
+      <c r="M14" s="15"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:13">
-      <c r="A12" s="10">
-        <v>1107</v>
-      </c>
-      <c r="B12" s="11">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="10">
-        <v>4010010</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="11">
+    <row r="15" s="3" customFormat="1" spans="1:13">
+      <c r="A15" s="9">
+        <v>1105</v>
+      </c>
+      <c r="B15" s="10">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="9">
+        <v>4010008</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15" s="10">
         <v>10</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L15" s="3">
         <v>60</v>
       </c>
-      <c r="M12" s="14"/>
+      <c r="M15" s="15"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:13">
-      <c r="A13" s="10">
-        <v>1103</v>
-      </c>
-      <c r="B13" s="11">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11">
-        <v>1</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="10">
-        <v>4010006</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="11">
+    <row r="16" s="3" customFormat="1" spans="1:13">
+      <c r="A16" s="9">
+        <v>1106</v>
+      </c>
+      <c r="B16" s="10">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="9">
+        <v>4010009</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" s="10">
         <v>10</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L16" s="3">
         <v>60</v>
       </c>
-      <c r="M13" s="14"/>
+      <c r="M16" s="15"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:13">
-      <c r="A14" s="10">
-        <v>1104</v>
-      </c>
-      <c r="B14" s="11">
-        <v>1</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11">
-        <v>1</v>
-      </c>
-      <c r="E14" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="10">
-        <v>4010007</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="11">
+    <row r="17" s="3" customFormat="1" spans="1:13">
+      <c r="A17" s="9">
+        <v>1202</v>
+      </c>
+      <c r="B17" s="10">
+        <v>2</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="9">
+        <v>4010017</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="10">
+        <v>20</v>
+      </c>
+      <c r="L17" s="3">
+        <v>60</v>
+      </c>
+      <c r="M17" s="15"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:13">
+      <c r="A18" s="9">
+        <v>1111</v>
+      </c>
+      <c r="B18" s="10">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="9">
+        <v>4010014</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K18" s="10">
         <v>10</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L18" s="3">
         <v>60</v>
       </c>
-      <c r="M14" s="14"/>
+      <c r="M18" s="15"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:13">
-      <c r="A15" s="10">
-        <v>1105</v>
-      </c>
-      <c r="B15" s="11">
-        <v>1</v>
-      </c>
-      <c r="C15" s="11">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="10">
-        <v>4010008</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="11">
+    <row r="19" s="3" customFormat="1" spans="1:13">
+      <c r="A19" s="9">
+        <v>1112</v>
+      </c>
+      <c r="B19" s="10">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="9">
+        <v>4010015</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K19" s="10">
         <v>10</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L19" s="3">
         <v>60</v>
       </c>
-      <c r="M15" s="14"/>
+      <c r="M19" s="15"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:13">
-      <c r="A16" s="10">
-        <v>1106</v>
-      </c>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11">
-        <v>1</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1</v>
-      </c>
-      <c r="E16" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="10">
-        <v>4010009</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" s="11">
+    <row r="20" s="3" customFormat="1" spans="1:13">
+      <c r="A20" s="9">
+        <v>1108</v>
+      </c>
+      <c r="B20" s="10">
+        <v>1</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="9">
+        <v>4010011</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="10">
         <v>10</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L20" s="3">
         <v>60</v>
       </c>
-      <c r="M16" s="14"/>
+      <c r="M20" s="15"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:13">
-      <c r="A17" s="10">
-        <v>1202</v>
-      </c>
-      <c r="B17" s="11">
-        <v>2</v>
-      </c>
-      <c r="C17" s="11">
-        <v>2</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="10">
-        <v>4010017</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="11">
-        <v>20</v>
-      </c>
-      <c r="L17" s="12">
+    <row r="21" s="3" customFormat="1" spans="1:13">
+      <c r="A21" s="9">
+        <v>1109</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="9">
+        <v>4010012</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="10">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
         <v>60</v>
       </c>
-      <c r="M17" s="14"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:13">
-      <c r="A18" s="10">
-        <v>1111</v>
-      </c>
-      <c r="B18" s="11">
-        <v>1</v>
-      </c>
-      <c r="C18" s="11">
-        <v>1</v>
-      </c>
-      <c r="D18" s="11">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="10">
-        <v>4010014</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K18" s="11">
-        <v>10</v>
-      </c>
-      <c r="L18" s="12">
-        <v>60</v>
-      </c>
-      <c r="M18" s="14"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:13">
-      <c r="A19" s="10">
-        <v>1112</v>
-      </c>
-      <c r="B19" s="11">
-        <v>1</v>
-      </c>
-      <c r="C19" s="11">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19" s="10">
-        <v>4010015</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K19" s="11">
-        <v>10</v>
-      </c>
-      <c r="L19" s="12">
-        <v>60</v>
-      </c>
-      <c r="M19" s="14"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:13">
-      <c r="A20" s="10">
-        <v>1108</v>
-      </c>
-      <c r="B20" s="11">
-        <v>1</v>
-      </c>
-      <c r="C20" s="11">
-        <v>1</v>
-      </c>
-      <c r="D20" s="11">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="10">
-        <v>4010011</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="11">
-        <v>10</v>
-      </c>
-      <c r="L20" s="12">
-        <v>60</v>
-      </c>
-      <c r="M20" s="14"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:13">
-      <c r="A21" s="10">
-        <v>1109</v>
-      </c>
-      <c r="B21" s="11">
-        <v>1</v>
-      </c>
-      <c r="C21" s="11">
-        <v>1</v>
-      </c>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="10">
-        <v>4010012</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="K21" s="11">
-        <v>10</v>
-      </c>
-      <c r="L21" s="12">
-        <v>60</v>
-      </c>
-      <c r="M21" s="14"/>
+      <c r="M21" s="15"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>1401</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>4</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>7</v>
       </c>
-      <c r="D22" s="11">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="14"/>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="15"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>1402</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>4</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>8</v>
       </c>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="14"/>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="15"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>1403</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>4</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>9</v>
       </c>
-      <c r="D24" s="11">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="14"/>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>1404</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>4</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>10</v>
       </c>
-      <c r="D25" s="11">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="14"/>
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="M25" s="15"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="10">
+      <c r="A26" s="9">
         <v>1405</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>4</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>10</v>
       </c>
-      <c r="D26" s="11">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="14"/>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 8. 宣传牌
 9. 风云榜
 10. 装饰-无作用
-</t>
+11.管理属性（包括3-服务能力；5-知名度；6=曝光度）</t>
         </r>
       </text>
     </comment>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -296,7 +296,7 @@
     <t>MaxLevel</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_10000</t>
   </si>
   <si>
     <t>管理</t>
@@ -326,7 +326,7 @@
     <t>1110_1</t>
   </si>
   <si>
-    <t>1990000_2000000</t>
+    <t>1990000_20000</t>
   </si>
   <si>
     <t>博弈扑克厅</t>
@@ -335,97 +335,94 @@
     <t>1107_1</t>
   </si>
   <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_1</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
+    <t>辉煌厅</t>
+  </si>
+  <si>
+    <t>1103_1</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>鸿运厅</t>
+  </si>
+  <si>
+    <t>1104_1</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>尊享厅</t>
+  </si>
+  <si>
+    <t>1105_1</t>
+  </si>
+  <si>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>至尊厅</t>
+  </si>
+  <si>
+    <t>1106_1</t>
+  </si>
+  <si>
+    <t>1990000_180000</t>
+  </si>
+  <si>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>1202_1</t>
+  </si>
+  <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>天际捕鱼厅</t>
+  </si>
+  <si>
+    <t>1111_1</t>
+  </si>
+  <si>
+    <t>1990000_250000</t>
+  </si>
+  <si>
+    <t>富豪捕鱼厅</t>
+  </si>
+  <si>
+    <t>1112_1</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>沙龙扑克厅</t>
+  </si>
+  <si>
+    <t>1108_1</t>
+  </si>
+  <si>
     <t>1990000_500000</t>
   </si>
   <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_1</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>辉煌厅</t>
-  </si>
-  <si>
-    <t>1103_1</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>鸿运厅</t>
-  </si>
-  <si>
-    <t>1104_1</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>尊享厅</t>
-  </si>
-  <si>
-    <t>1105_1</t>
-  </si>
-  <si>
-    <t>1990000_15000000</t>
-  </si>
-  <si>
-    <t>至尊厅</t>
-  </si>
-  <si>
-    <t>1106_1</t>
-  </si>
-  <si>
-    <t>1990000_18000000</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
-  </si>
-  <si>
-    <t>1202_1</t>
-  </si>
-  <si>
-    <t>1990000_20000000</t>
-  </si>
-  <si>
-    <t>天际捕鱼厅</t>
-  </si>
-  <si>
-    <t>1111_1</t>
-  </si>
-  <si>
-    <t>1990000_25000000</t>
-  </si>
-  <si>
-    <t>富豪捕鱼厅</t>
-  </si>
-  <si>
-    <t>1112_1</t>
-  </si>
-  <si>
-    <t>1990000_30000000</t>
-  </si>
-  <si>
-    <t>沙龙扑克厅</t>
-  </si>
-  <si>
-    <t>1108_1</t>
-  </si>
-  <si>
-    <t>1990000_50000000</t>
-  </si>
-  <si>
     <t>精英扑克厅</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
   </si>
   <si>
     <t>参观</t>
@@ -2497,14 +2494,14 @@
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M22" s="15"/>
     </row>
@@ -2526,14 +2523,14 @@
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M23" s="15"/>
     </row>
@@ -2555,14 +2552,14 @@
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M24" s="15"/>
     </row>
@@ -2584,14 +2581,14 @@
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M25" s="15"/>
     </row>
@@ -2613,14 +2610,14 @@
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M26" s="15"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -347,7 +347,7 @@
     <t>营销部</t>
   </si>
   <si>
-    <t>1990000_40000</t>
+    <t>1980000_100</t>
   </si>
   <si>
     <t>辉煌厅</t>
@@ -356,7 +356,7 @@
     <t>1103_1</t>
   </si>
   <si>
-    <t>1990000_80000</t>
+    <t>1980000_200</t>
   </si>
   <si>
     <t>鸿运厅</t>
@@ -365,7 +365,7 @@
     <t>1104_1</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1980000_400</t>
   </si>
   <si>
     <t>尊享厅</t>
@@ -374,7 +374,7 @@
     <t>1105_1</t>
   </si>
   <si>
-    <t>1990000_150000</t>
+    <t>1980000_800</t>
   </si>
   <si>
     <t>至尊厅</t>
@@ -383,7 +383,7 @@
     <t>1106_1</t>
   </si>
   <si>
-    <t>1990000_180000</t>
+    <t>1980000_1000</t>
   </si>
   <si>
     <t>VIP休息区</t>
@@ -392,34 +392,22 @@
     <t>1202_1</t>
   </si>
   <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
     <t>天际捕鱼厅</t>
   </si>
   <si>
     <t>1111_1</t>
   </si>
   <si>
-    <t>1990000_250000</t>
-  </si>
-  <si>
     <t>富豪捕鱼厅</t>
   </si>
   <si>
     <t>1112_1</t>
   </si>
   <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
     <t>沙龙扑克厅</t>
   </si>
   <si>
     <t>1108_1</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
   </si>
   <si>
     <t>精英扑克厅</t>
@@ -2340,7 +2328,7 @@
         <v>58</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>30</v>
@@ -2349,7 +2337,7 @@
         <v>4010014</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K18" s="10">
         <v>10</v>
@@ -2376,10 +2364,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>30</v>
@@ -2388,7 +2376,7 @@
         <v>4010015</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K19" s="10">
         <v>10</v>
@@ -2415,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>30</v>
@@ -2427,7 +2415,7 @@
         <v>4010011</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K20" s="10">
         <v>10</v>
@@ -2454,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>30</v>
@@ -2466,7 +2454,7 @@
         <v>4010012</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K21" s="10">
         <v>10</v>
@@ -2497,11 +2485,11 @@
         <v>27</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M22" s="15"/>
     </row>
@@ -2526,11 +2514,11 @@
         <v>27</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M23" s="15"/>
     </row>
@@ -2555,11 +2543,11 @@
         <v>27</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M24" s="15"/>
     </row>
@@ -2584,11 +2572,11 @@
         <v>27</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M25" s="15"/>
     </row>
@@ -2613,11 +2601,11 @@
         <v>27</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M26" s="15"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -211,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -347,43 +352,28 @@
     <t>营销部</t>
   </si>
   <si>
-    <t>1980000_100</t>
-  </si>
-  <si>
     <t>辉煌厅</t>
   </si>
   <si>
     <t>1103_1</t>
   </si>
   <si>
-    <t>1980000_200</t>
-  </si>
-  <si>
     <t>鸿运厅</t>
   </si>
   <si>
     <t>1104_1</t>
   </si>
   <si>
-    <t>1980000_400</t>
-  </si>
-  <si>
     <t>尊享厅</t>
   </si>
   <si>
     <t>1105_1</t>
   </si>
   <si>
-    <t>1980000_800</t>
-  </si>
-  <si>
     <t>至尊厅</t>
   </si>
   <si>
     <t>1106_1</t>
-  </si>
-  <si>
-    <t>1980000_1000</t>
   </si>
   <si>
     <t>VIP休息区</t>
@@ -2133,7 +2123,7 @@
         <v>39</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>30</v>
@@ -2142,7 +2132,7 @@
         <v>4010006</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K13" s="10">
         <v>10</v>
@@ -2169,10 +2159,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>30</v>
@@ -2181,7 +2171,7 @@
         <v>4010007</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K14" s="10">
         <v>10</v>
@@ -2208,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>30</v>
@@ -2220,7 +2210,7 @@
         <v>4010008</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K15" s="10">
         <v>10</v>
@@ -2247,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>30</v>
@@ -2259,7 +2249,7 @@
         <v>4010009</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K16" s="10">
         <v>10</v>
@@ -2286,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>33</v>
@@ -2298,7 +2288,7 @@
         <v>4010017</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K17" s="10">
         <v>20</v>
@@ -2325,10 +2315,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>30</v>
@@ -2337,7 +2327,7 @@
         <v>4010014</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K18" s="10">
         <v>10</v>
@@ -2364,10 +2354,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>30</v>
@@ -2376,7 +2366,7 @@
         <v>4010015</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K19" s="10">
         <v>10</v>
@@ -2403,10 +2393,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>30</v>
@@ -2415,7 +2405,7 @@
         <v>4010011</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K20" s="10">
         <v>10</v>
@@ -2442,10 +2432,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>30</v>
@@ -2454,7 +2444,7 @@
         <v>4010012</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K21" s="10">
         <v>10</v>
@@ -2485,11 +2475,11 @@
         <v>27</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M22" s="15"/>
     </row>
@@ -2514,11 +2504,11 @@
         <v>27</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M23" s="15"/>
     </row>
@@ -2543,11 +2533,11 @@
         <v>27</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M24" s="15"/>
     </row>
@@ -2572,11 +2562,11 @@
         <v>27</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M25" s="15"/>
     </row>
@@ -2601,11 +2591,11 @@
         <v>27</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M26" s="15"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,8 @@
 8. 宣传牌
 9. 风云榜
 10. 装饰-无作用
-11.管理属性（包括3-服务能力；5-知名度；6=曝光度）</t>
+11.管理属性（包括3-服务能力；5-知名度；6=曝光度）
+12.娱乐城经验</t>
         </r>
       </text>
     </comment>
@@ -158,12 +159,34 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+娱乐城等级</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 解锁建筑的前置条件：建筑ID_等级
 注：手动点击解锁</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -187,7 +210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -233,7 +256,10 @@
     <t>解锁方式</t>
   </si>
   <si>
-    <t>解锁条件</t>
+    <t>解锁条件1</t>
+  </si>
+  <si>
+    <t>解锁条件2</t>
   </si>
   <si>
     <t>解锁消耗</t>
@@ -246,6 +272,9 @@
   </si>
   <si>
     <t>建筑名称</t>
+  </si>
+  <si>
+    <t>解锁游戏ID</t>
   </si>
   <si>
     <t>受影响的雇员类型</t>
@@ -262,6 +291,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -286,6 +318,9 @@
     <t>UnlockType</t>
   </si>
   <si>
+    <t>CasinoLevel</t>
+  </si>
+  <si>
     <t>UnlockMethod</t>
   </si>
   <si>
@@ -295,112 +330,115 @@
     <t>BuildingNameId</t>
   </si>
   <si>
+    <t>UnlockGameId</t>
+  </si>
+  <si>
     <t>EmployeeProfile</t>
   </si>
   <si>
     <t>MaxLevel</t>
   </si>
   <si>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>接待区</t>
+  </si>
+  <si>
+    <t>1_12</t>
+  </si>
+  <si>
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>管理</t>
-  </si>
-  <si>
-    <t>研发部\游戏厅</t>
-  </si>
-  <si>
     <t>游戏</t>
   </si>
   <si>
-    <t>贵宾厅</t>
-  </si>
-  <si>
-    <t>接待区</t>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>1106_1</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
   </si>
   <si>
     <t>休息</t>
   </si>
   <si>
-    <t>普通休息区</t>
-  </si>
-  <si>
-    <t>欢乐捕鱼厅</t>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>1107_1</t>
+  </si>
+  <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_1</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
   </si>
   <si>
     <t>1110_1</t>
   </si>
   <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>博弈扑克厅</t>
-  </si>
-  <si>
-    <t>1107_1</t>
-  </si>
-  <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_1</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>辉煌厅</t>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>超级明星</t>
   </si>
   <si>
     <t>1103_1</t>
   </si>
   <si>
-    <t>鸿运厅</t>
+    <t>财神来了</t>
   </si>
   <si>
     <t>1104_1</t>
   </si>
   <si>
-    <t>尊享厅</t>
+    <t>寒冰王座</t>
   </si>
   <si>
     <t>1105_1</t>
   </si>
   <si>
-    <t>至尊厅</t>
-  </si>
-  <si>
-    <t>1106_1</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
+    <t>绿巨人</t>
   </si>
   <si>
     <t>1202_1</t>
   </si>
   <si>
-    <t>天际捕鱼厅</t>
+    <t>雷神</t>
   </si>
   <si>
     <t>1111_1</t>
   </si>
   <si>
-    <t>富豪捕鱼厅</t>
+    <t>杰克船长</t>
   </si>
   <si>
     <t>1112_1</t>
   </si>
   <si>
-    <t>沙龙扑克厅</t>
+    <t>宙斯vs哈迪斯</t>
   </si>
   <si>
     <t>1108_1</t>
   </si>
   <si>
-    <t>精英扑克厅</t>
+    <t>狼月</t>
   </si>
   <si>
     <t>参观</t>
@@ -431,7 +469,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,6 +498,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -619,7 +663,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,12 +672,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -819,12 +857,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -945,137 +998,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1116,16 +1169,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1662,26 +1718,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="17.625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="5" max="6" width="12.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17.625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1706,92 +1763,110 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A3" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="8"/>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="8"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:17">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1802,14 +1877,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:13">
+    <row r="5" s="2" customFormat="1" spans="1:17">
       <c r="A5" s="11">
-        <v>1302</v>
-      </c>
-      <c r="B5" s="12"/>
+        <v>1301</v>
+      </c>
+      <c r="B5" s="12">
+        <v>3</v>
+      </c>
       <c r="C5" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="12">
         <v>1</v>
@@ -1818,300 +1897,334 @@
         <v>0</v>
       </c>
       <c r="F5" s="12"/>
-      <c r="G5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="11">
-        <v>4010021</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="12">
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="11">
+        <v>4010018</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12">
         <v>30</v>
       </c>
-      <c r="L5" s="2">
+      <c r="N5" s="2">
+        <v>60</v>
+      </c>
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:17">
+      <c r="A6" s="9">
+        <v>1101</v>
+      </c>
+      <c r="B6" s="10">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="9">
+        <v>103900001</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="15">
+        <v>103900</v>
+      </c>
+      <c r="M6" s="10">
         <v>10</v>
       </c>
-      <c r="M5" s="13"/>
+      <c r="N6" s="3">
+        <v>60</v>
+      </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:13">
-      <c r="A6" s="11">
+    <row r="7" s="3" customFormat="1" spans="1:17">
+      <c r="A7" s="9">
+        <v>1202</v>
+      </c>
+      <c r="B7" s="10">
+        <v>2</v>
+      </c>
+      <c r="C7" s="10">
+        <v>2</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="9">
+        <v>4010017</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="10">
+        <v>20</v>
+      </c>
+      <c r="N7" s="3">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:17">
+      <c r="A8" s="9">
         <v>1102</v>
       </c>
-      <c r="B6" s="12">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="12" t="s">
+      <c r="B8" s="10">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="9">
+        <v>102700001</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="15">
+        <v>102700</v>
+      </c>
+      <c r="M8" s="10">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:17">
+      <c r="A9" s="9">
+        <v>1303</v>
+      </c>
+      <c r="B9" s="10">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10">
+        <v>5</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>4</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="9">
+        <v>4010019</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="10">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
-        <v>4010005</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="12">
+      <c r="N9" s="3">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:17">
+      <c r="A10" s="9">
+        <v>1304</v>
+      </c>
+      <c r="B10" s="10">
+        <v>3</v>
+      </c>
+      <c r="C10" s="10">
+        <v>6</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>5</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="9">
+        <v>4010020</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="10">
+        <v>30</v>
+      </c>
+      <c r="N10" s="3">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:17">
+      <c r="A11" s="9">
+        <v>1110</v>
+      </c>
+      <c r="B11" s="10">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>6</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="9">
+        <v>100700001</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="15">
+        <v>101200</v>
+      </c>
+      <c r="M11" s="10">
         <v>10</v>
       </c>
-      <c r="L6" s="2">
+      <c r="N11" s="3">
         <v>60</v>
       </c>
-      <c r="M6" s="14"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:13">
-      <c r="A7" s="11">
-        <v>1301</v>
-      </c>
-      <c r="B7" s="12">
-        <v>3</v>
-      </c>
-      <c r="C7" s="12">
-        <v>3</v>
-      </c>
-      <c r="D7" s="12">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="11">
-        <v>4010018</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="12">
-        <v>30</v>
-      </c>
-      <c r="L7" s="2">
+    <row r="12" s="3" customFormat="1" spans="1:17">
+      <c r="A12" s="9">
+        <v>1107</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10">
+        <v>7</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="9">
+        <v>101800001</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="15">
+        <v>101800</v>
+      </c>
+      <c r="M12" s="10">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>60</v>
       </c>
-      <c r="M7" s="14"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="11">
-        <v>1201</v>
-      </c>
-      <c r="B8" s="12">
-        <v>2</v>
-      </c>
-      <c r="C8" s="12">
-        <v>2</v>
-      </c>
-      <c r="D8" s="12">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="11">
-        <v>4010016</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="12">
-        <v>20</v>
-      </c>
-      <c r="L8" s="2">
-        <v>60</v>
-      </c>
-      <c r="M8" s="14"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:13">
-      <c r="A9" s="9">
-        <v>1110</v>
-      </c>
-      <c r="B9" s="10">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1</v>
-      </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="9">
-        <v>4010013</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="10">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3">
-        <v>60</v>
-      </c>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:13">
-      <c r="A10" s="9">
-        <v>1107</v>
-      </c>
-      <c r="B10" s="10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="9">
-        <v>4010010</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="10">
-        <v>10</v>
-      </c>
-      <c r="L10" s="3">
-        <v>60</v>
-      </c>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:13">
-      <c r="A11" s="9">
-        <v>1303</v>
-      </c>
-      <c r="B11" s="10">
-        <v>3</v>
-      </c>
-      <c r="C11" s="10">
-        <v>5</v>
-      </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="9">
-        <v>4010019</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="10">
-        <v>30</v>
-      </c>
-      <c r="L11" s="3">
-        <v>60</v>
-      </c>
-      <c r="M11" s="15"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:13">
-      <c r="A12" s="9">
-        <v>1304</v>
-      </c>
-      <c r="B12" s="10">
-        <v>3</v>
-      </c>
-      <c r="C12" s="10">
-        <v>6</v>
-      </c>
-      <c r="D12" s="10">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="9">
-        <v>4010020</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="10">
-        <v>30</v>
-      </c>
-      <c r="L12" s="3">
-        <v>60</v>
-      </c>
-      <c r="M12" s="15"/>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="1:13">
+    <row r="13" s="3" customFormat="1" spans="1:17">
       <c r="A13" s="9">
         <v>1103</v>
       </c>
       <c r="B13" s="10">
         <v>1</v>
       </c>
-      <c r="C13" s="10">
-        <v>1</v>
+      <c r="C13" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
@@ -2119,38 +2232,44 @@
       <c r="E13" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="10">
+        <v>8</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="9">
-        <v>4010006</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="10">
+      <c r="I13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="9">
+        <v>100300001</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="15">
+        <v>100300</v>
+      </c>
+      <c r="M13" s="10">
         <v>10</v>
       </c>
-      <c r="L13" s="3">
+      <c r="N13" s="3">
         <v>60</v>
       </c>
-      <c r="M13" s="15"/>
+      <c r="Q13" s="16"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:13">
+    <row r="14" s="3" customFormat="1" spans="1:17">
       <c r="A14" s="9">
         <v>1104</v>
       </c>
       <c r="B14" s="10">
         <v>1</v>
       </c>
-      <c r="C14" s="10">
-        <v>1</v>
+      <c r="C14" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
@@ -2158,38 +2277,44 @@
       <c r="E14" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>45</v>
+      <c r="F14" s="10">
+        <v>9</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="9">
-        <v>4010007</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="10">
+        <v>39</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="9">
+        <v>101200001</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="16">
+        <v>100700</v>
+      </c>
+      <c r="M14" s="10">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>60</v>
       </c>
-      <c r="M14" s="15"/>
+      <c r="Q14" s="16"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:13">
+    <row r="15" s="3" customFormat="1" spans="1:17">
       <c r="A15" s="9">
         <v>1105</v>
       </c>
       <c r="B15" s="10">
         <v>1</v>
       </c>
-      <c r="C15" s="10">
-        <v>1</v>
+      <c r="C15" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -2197,38 +2322,44 @@
       <c r="E15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>47</v>
+      <c r="F15" s="10">
+        <v>10</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="9">
-        <v>4010008</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="10">
+        <v>39</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="9">
+        <v>102500001</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="16">
+        <v>102500</v>
+      </c>
+      <c r="M15" s="10">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>60</v>
       </c>
-      <c r="M15" s="15"/>
+      <c r="Q15" s="16"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:13">
+    <row r="16" s="3" customFormat="1" spans="1:17">
       <c r="A16" s="9">
         <v>1106</v>
       </c>
       <c r="B16" s="10">
         <v>1</v>
       </c>
-      <c r="C16" s="10">
-        <v>1</v>
+      <c r="C16" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
@@ -2236,38 +2367,44 @@
       <c r="E16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>49</v>
+      <c r="F16" s="10">
+        <v>11</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="9">
-        <v>4010009</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="10">
+        <v>39</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="9">
+        <v>103100001</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="16">
+        <v>103100</v>
+      </c>
+      <c r="M16" s="10">
         <v>10</v>
       </c>
-      <c r="L16" s="3">
+      <c r="N16" s="3">
         <v>60</v>
       </c>
-      <c r="M16" s="15"/>
+      <c r="Q16" s="16"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:13">
+    <row r="17" s="3" customFormat="1" spans="1:17">
       <c r="A17" s="9">
-        <v>1202</v>
+        <v>1111</v>
       </c>
       <c r="B17" s="10">
-        <v>2</v>
-      </c>
-      <c r="C17" s="10">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D17" s="10">
         <v>1</v>
@@ -2275,38 +2412,44 @@
       <c r="E17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>51</v>
+      <c r="F17" s="10">
+        <v>12</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="9">
-        <v>4010017</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="10">
-        <v>20</v>
-      </c>
-      <c r="L17" s="3">
+        <v>39</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="9">
+        <v>102200001</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16">
+        <v>102200</v>
+      </c>
+      <c r="M17" s="10">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3">
         <v>60</v>
       </c>
-      <c r="M17" s="15"/>
+      <c r="Q17" s="16"/>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:13">
+    <row r="18" s="3" customFormat="1" spans="1:17">
       <c r="A18" s="9">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B18" s="10">
         <v>1</v>
       </c>
-      <c r="C18" s="10">
-        <v>1</v>
+      <c r="C18" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D18" s="10">
         <v>1</v>
@@ -2314,38 +2457,43 @@
       <c r="E18" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>53</v>
+      <c r="F18" s="10">
+        <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="9">
-        <v>4010014</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="10">
+        <v>39</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="9">
+        <v>102100001</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16">
+        <v>102100</v>
+      </c>
+      <c r="M18" s="10">
         <v>10</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>60</v>
       </c>
-      <c r="M18" s="15"/>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:13">
+    <row r="19" s="3" customFormat="1" spans="1:17">
       <c r="A19" s="9">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B19" s="10">
         <v>1</v>
       </c>
-      <c r="C19" s="10">
-        <v>1</v>
+      <c r="C19" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
@@ -2353,38 +2501,43 @@
       <c r="E19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>55</v>
+      <c r="F19" s="10">
+        <v>14</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="9">
-        <v>4010015</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" s="10">
+        <v>39</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="9">
+        <v>102000001</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16">
+        <v>102000</v>
+      </c>
+      <c r="M19" s="10">
         <v>10</v>
       </c>
-      <c r="L19" s="3">
+      <c r="N19" s="3">
         <v>60</v>
       </c>
-      <c r="M19" s="15"/>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:13">
+    <row r="20" s="3" customFormat="1" spans="1:17">
       <c r="A20" s="9">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B20" s="10">
         <v>1</v>
       </c>
-      <c r="C20" s="10">
-        <v>1</v>
+      <c r="C20" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D20" s="10">
         <v>1</v>
@@ -2392,38 +2545,43 @@
       <c r="E20" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>57</v>
+      <c r="F20" s="10">
+        <v>15</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="9">
-        <v>4010011</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K20" s="10">
+        <v>39</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="9">
+        <v>101500001</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="16">
+        <v>101500</v>
+      </c>
+      <c r="M20" s="10">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>60</v>
       </c>
-      <c r="M20" s="15"/>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:13">
+    <row r="21" spans="1:17">
       <c r="A21" s="9">
-        <v>1109</v>
+        <v>1401</v>
       </c>
       <c r="B21" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D21" s="10">
         <v>1</v>
@@ -2431,38 +2589,29 @@
       <c r="E21" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>37</v>
-      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="9">
-        <v>4010012</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="10">
-        <v>10</v>
-      </c>
-      <c r="L21" s="3">
-        <v>60</v>
-      </c>
-      <c r="M21" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="9"/>
+      <c r="K21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:17">
       <c r="A22" s="9">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B22" s="10">
         <v>4</v>
       </c>
       <c r="C22" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="10">
         <v>1</v>
@@ -2470,28 +2619,29 @@
       <c r="E22" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
       <c r="H22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="9"/>
+      <c r="K22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:17">
       <c r="A23" s="9">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B23" s="10">
         <v>4</v>
       </c>
       <c r="C23" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="10">
         <v>1</v>
@@ -2499,28 +2649,29 @@
       <c r="E23" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M23" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:17">
       <c r="A24" s="9">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B24" s="10">
         <v>4</v>
       </c>
       <c r="C24" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
@@ -2528,22 +2679,24 @@
       <c r="E24" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
       <c r="H24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="M24" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" s="18"/>
+      <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:17">
       <c r="A25" s="9">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B25" s="10">
         <v>4</v>
@@ -2557,51 +2710,27 @@
       <c r="E25" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="M25" s="15"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="9">
-        <v>1405</v>
-      </c>
-      <c r="B26" s="10">
-        <v>4</v>
-      </c>
-      <c r="C26" s="10">
-        <v>10</v>
-      </c>
-      <c r="D26" s="10">
-        <v>1</v>
-      </c>
-      <c r="E26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="M26" s="15"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" s="18"/>
+      <c r="O25" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A$1:A$1048576">
+  <conditionalFormatting sqref="A6">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A5 A7:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -357,9 +357,6 @@
     <t>愤怒的小鸟</t>
   </si>
   <si>
-    <t>1106_1</t>
-  </si>
-  <si>
     <t>1990000_20000</t>
   </si>
   <si>
@@ -372,70 +369,40 @@
     <t>象财神</t>
   </si>
   <si>
-    <t>1107_1</t>
-  </si>
-  <si>
     <t>1990000_5000</t>
   </si>
   <si>
     <t>运营部</t>
   </si>
   <si>
-    <t>1303_1</t>
-  </si>
-  <si>
     <t>营销部</t>
   </si>
   <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1110_1</t>
-  </si>
-  <si>
     <t>篮球巨星</t>
   </si>
   <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>1103_1</t>
-  </si>
-  <si>
     <t>财神来了</t>
   </si>
   <si>
-    <t>1104_1</t>
-  </si>
-  <si>
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>1105_1</t>
-  </si>
-  <si>
     <t>绿巨人</t>
   </si>
   <si>
-    <t>1202_1</t>
-  </si>
-  <si>
     <t>雷神</t>
   </si>
   <si>
-    <t>1111_1</t>
-  </si>
-  <si>
     <t>杰克船长</t>
   </si>
   <si>
-    <t>1112_1</t>
-  </si>
-  <si>
     <t>宙斯vs哈迪斯</t>
-  </si>
-  <si>
-    <t>1108_1</t>
   </si>
   <si>
     <t>狼月</t>
@@ -1976,22 +1943,20 @@
         <v>1</v>
       </c>
       <c r="F7" s="10">
-        <v>2</v>
-      </c>
-      <c r="G7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="I7" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="J7" s="9">
         <v>4010017</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="10">
@@ -2019,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
@@ -2032,7 +1997,7 @@
         <v>102700001</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L8" s="15">
         <v>102700</v>
@@ -2061,13 +2026,11 @@
         <v>1</v>
       </c>
       <c r="F9" s="10">
-        <v>4</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G9" s="10"/>
       <c r="H9" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>32</v>
@@ -2076,7 +2039,7 @@
         <v>4010019</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="10">
@@ -2104,13 +2067,11 @@
         <v>1</v>
       </c>
       <c r="F10" s="10">
-        <v>5</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>46</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>32</v>
@@ -2119,7 +2080,7 @@
         <v>4010020</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="10">
@@ -2147,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
@@ -2160,10 +2121,10 @@
         <v>100700001</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L11" s="15">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="M11" s="10">
         <v>10</v>
@@ -2189,13 +2150,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="10">
-        <v>7</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>49</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G12" s="10"/>
       <c r="H12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>36</v>
@@ -2204,7 +2163,7 @@
         <v>101800001</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L12" s="15">
         <v>101800</v>
@@ -2233,13 +2192,11 @@
         <v>1</v>
       </c>
       <c r="F13" s="10">
-        <v>8</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>43</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>36</v>
@@ -2248,7 +2205,7 @@
         <v>100300001</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L13" s="15">
         <v>100300</v>
@@ -2278,13 +2235,11 @@
         <v>1</v>
       </c>
       <c r="F14" s="10">
-        <v>9</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>52</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G14" s="10"/>
       <c r="H14" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>36</v>
@@ -2293,10 +2248,10 @@
         <v>101200001</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L14" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="M14" s="10">
         <v>10</v>
@@ -2323,13 +2278,11 @@
         <v>1</v>
       </c>
       <c r="F15" s="10">
-        <v>10</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>54</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G15" s="10"/>
       <c r="H15" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>36</v>
@@ -2338,7 +2291,7 @@
         <v>102500001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L15" s="16">
         <v>102500</v>
@@ -2368,13 +2321,11 @@
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>11</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G16" s="10"/>
       <c r="H16" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>36</v>
@@ -2383,7 +2334,7 @@
         <v>103100001</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="L16" s="16">
         <v>103100</v>
@@ -2413,13 +2364,11 @@
         <v>1</v>
       </c>
       <c r="F17" s="10">
-        <v>12</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G17" s="10"/>
       <c r="H17" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>36</v>
@@ -2428,7 +2377,7 @@
         <v>102200001</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L17" s="16">
         <v>102200</v>
@@ -2458,13 +2407,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="10">
-        <v>13</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>60</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>36</v>
@@ -2473,7 +2420,7 @@
         <v>102100001</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L18" s="16">
         <v>102100</v>
@@ -2502,13 +2449,11 @@
         <v>1</v>
       </c>
       <c r="F19" s="10">
-        <v>14</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>62</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>36</v>
@@ -2517,7 +2462,7 @@
         <v>102000001</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L19" s="16">
         <v>102000</v>
@@ -2546,13 +2491,11 @@
         <v>1</v>
       </c>
       <c r="F20" s="10">
-        <v>15</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>64</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G20" s="10"/>
       <c r="H20" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>36</v>
@@ -2561,7 +2504,7 @@
         <v>101500001</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L20" s="16">
         <v>101500</v>
@@ -2595,11 +2538,11 @@
         <v>35</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="O21" s="14"/>
     </row>
@@ -2625,11 +2568,11 @@
         <v>35</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="O22" s="14"/>
     </row>
@@ -2655,11 +2598,11 @@
         <v>35</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="O23" s="14"/>
     </row>
@@ -2685,11 +2628,11 @@
         <v>35</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="18" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="L24" s="18"/>
       <c r="O24" s="14"/>
@@ -2716,11 +2659,11 @@
         <v>35</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="18" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L25" s="18"/>
       <c r="O25" s="14"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -357,6 +357,9 @@
     <t>愤怒的小鸟</t>
   </si>
   <si>
+    <t>象财神</t>
+  </si>
+  <si>
     <t>1990000_20000</t>
   </si>
   <si>
@@ -366,9 +369,6 @@
     <t>VIP休息区</t>
   </si>
   <si>
-    <t>象财神</t>
-  </si>
-  <si>
     <t>1990000_5000</t>
   </si>
   <si>
@@ -384,28 +384,28 @@
     <t>篮球巨星</t>
   </si>
   <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>财神来了</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>财神来了</t>
-  </si>
-  <si>
-    <t>寒冰王座</t>
-  </si>
-  <si>
-    <t>绿巨人</t>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
   </si>
   <si>
     <t>雷神</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
-  </si>
-  <si>
-    <t>宙斯vs哈迪斯</t>
-  </si>
-  <si>
-    <t>狼月</t>
   </si>
   <si>
     <t>参观</t>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="7" s="3" customFormat="1" spans="1:17">
       <c r="A7" s="9">
-        <v>1202</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="10">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D7" s="10">
         <v>1</v>
@@ -1943,39 +1943,40 @@
         <v>1</v>
       </c>
       <c r="F7" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="9">
+        <v>102700001</v>
+      </c>
+      <c r="K7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="9">
-        <v>4010017</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="15">
+        <v>102700</v>
+      </c>
       <c r="M7" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N7" s="3">
         <v>60</v>
       </c>
-      <c r="Q7" s="16"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:17">
       <c r="A8" s="9">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="B8" s="10">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2</v>
       </c>
       <c r="D8" s="10">
         <v>1</v>
@@ -1984,30 +1985,29 @@
         <v>1</v>
       </c>
       <c r="F8" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J8" s="9">
-        <v>102700001</v>
-      </c>
-      <c r="K8" s="14" t="s">
+        <v>4010017</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="15">
-        <v>102700</v>
-      </c>
+      <c r="L8" s="3"/>
       <c r="M8" s="10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N8" s="3">
         <v>60</v>
       </c>
+      <c r="Q8" s="16"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:17">
       <c r="A9" s="9">
@@ -2026,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10" t="s">
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
@@ -2108,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
@@ -2150,11 +2150,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>36</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="13" s="3" customFormat="1" spans="1:17">
       <c r="A13" s="9">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B13" s="10">
         <v>1</v>
@@ -2192,23 +2192,23 @@
         <v>1</v>
       </c>
       <c r="F13" s="10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="9">
-        <v>100300001</v>
+        <v>103100001</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="15">
-        <v>100300</v>
+      <c r="L13" s="16">
+        <v>103100</v>
       </c>
       <c r="M13" s="10">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="14" s="3" customFormat="1" spans="1:17">
       <c r="A14" s="9">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B14" s="10">
         <v>1</v>
@@ -2235,23 +2235,23 @@
         <v>1</v>
       </c>
       <c r="F14" s="10">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J14" s="9">
-        <v>101200001</v>
+        <v>102500001</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>48</v>
       </c>
       <c r="L14" s="16">
-        <v>101200</v>
+        <v>102500</v>
       </c>
       <c r="M14" s="10">
         <v>10</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="15" s="3" customFormat="1" spans="1:17">
       <c r="A15" s="9">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B15" s="10">
         <v>1</v>
@@ -2278,23 +2278,23 @@
         <v>1</v>
       </c>
       <c r="F15" s="10">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J15" s="9">
-        <v>102500001</v>
+        <v>101200001</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="16">
-        <v>102500</v>
+        <v>101200</v>
       </c>
       <c r="M15" s="10">
         <v>10</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="16" s="3" customFormat="1" spans="1:17">
       <c r="A16" s="9">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B16" s="10">
         <v>1</v>
@@ -2321,23 +2321,23 @@
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J16" s="9">
-        <v>103100001</v>
+        <v>100300001</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L16" s="16">
-        <v>103100</v>
+      <c r="L16" s="15">
+        <v>100300</v>
       </c>
       <c r="M16" s="10">
         <v>10</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="17" s="3" customFormat="1" spans="1:17">
       <c r="A17" s="9">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B17" s="10">
         <v>1</v>
@@ -2364,23 +2364,23 @@
         <v>1</v>
       </c>
       <c r="F17" s="10">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J17" s="9">
-        <v>102200001</v>
+        <v>101500001</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>51</v>
       </c>
       <c r="L17" s="16">
-        <v>102200</v>
+        <v>101500</v>
       </c>
       <c r="M17" s="10">
         <v>10</v>
@@ -2388,11 +2388,10 @@
       <c r="N17" s="3">
         <v>60</v>
       </c>
-      <c r="Q17" s="16"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:17">
       <c r="A18" s="9">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B18" s="10">
         <v>1</v>
@@ -2407,23 +2406,23 @@
         <v>1</v>
       </c>
       <c r="F18" s="10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J18" s="9">
-        <v>102100001</v>
+        <v>102000001</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>52</v>
       </c>
       <c r="L18" s="16">
-        <v>102100</v>
+        <v>102000</v>
       </c>
       <c r="M18" s="10">
         <v>10</v>
@@ -2434,7 +2433,7 @@
     </row>
     <row r="19" s="3" customFormat="1" spans="1:17">
       <c r="A19" s="9">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B19" s="10">
         <v>1</v>
@@ -2449,23 +2448,23 @@
         <v>1</v>
       </c>
       <c r="F19" s="10">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J19" s="9">
-        <v>102000001</v>
+        <v>102100001</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>53</v>
       </c>
       <c r="L19" s="16">
-        <v>102000</v>
+        <v>102100</v>
       </c>
       <c r="M19" s="10">
         <v>10</v>
@@ -2476,7 +2475,7 @@
     </row>
     <row r="20" s="3" customFormat="1" spans="1:17">
       <c r="A20" s="9">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B20" s="10">
         <v>1</v>
@@ -2491,23 +2490,23 @@
         <v>1</v>
       </c>
       <c r="F20" s="10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J20" s="9">
-        <v>101500001</v>
+        <v>102200001</v>
       </c>
       <c r="K20" s="14" t="s">
         <v>54</v>
       </c>
       <c r="L20" s="16">
-        <v>101500</v>
+        <v>102200</v>
       </c>
       <c r="M20" s="10">
         <v>10</v>
@@ -2515,6 +2514,7 @@
       <c r="N20" s="3">
         <v>60</v>
       </c>
+      <c r="Q20" s="16"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="9">
@@ -2672,7 +2672,7 @@
   <conditionalFormatting sqref="A6">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A5 A7:A1048576">
+  <conditionalFormatting sqref="A1:A5 A7:A25 A28:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>等级上限</t>
+  </si>
+  <si>
+    <t>交互时间(S)</t>
   </si>
   <si>
     <t>#重要说明：注：
@@ -337,6 +340,9 @@
   </si>
   <si>
     <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>InteractTime</t>
   </si>
   <si>
     <t>管理</t>
@@ -1685,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1701,11 +1707,12 @@
     <col min="12" max="12" width="16" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.625" style="3" customWidth="1"/>
     <col min="14" max="14" width="10.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="15" max="15" width="12.75" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1748,92 +1755,101 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:17">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1847,7 +1863,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:17">
+    <row r="5" s="2" customFormat="1" spans="1:18">
       <c r="A5" s="11">
         <v>1301</v>
       </c>
@@ -1867,13 +1883,13 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5" s="11">
         <v>4010018</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="12">
@@ -1883,8 +1899,9 @@
         <v>60</v>
       </c>
       <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:17">
+    <row r="6" s="3" customFormat="1" spans="1:18">
       <c r="A6" s="9">
         <v>1101</v>
       </c>
@@ -1892,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="10">
         <v>1</v>
@@ -1905,16 +1922,16 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J6" s="9">
         <v>103900001</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L6" s="15">
         <v>103900</v>
@@ -1925,8 +1942,11 @@
       <c r="N6" s="3">
         <v>60</v>
       </c>
+      <c r="O6" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:17">
+    <row r="7" s="3" customFormat="1" spans="1:18">
       <c r="A7" s="9">
         <v>1102</v>
       </c>
@@ -1934,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="10">
         <v>1</v>
@@ -1947,16 +1967,16 @@
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J7" s="9">
         <v>102700001</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7" s="15">
         <v>102700</v>
@@ -1967,8 +1987,11 @@
       <c r="N7" s="3">
         <v>60</v>
       </c>
+      <c r="O7" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:17">
+    <row r="8" s="3" customFormat="1" spans="1:18">
       <c r="A8" s="9">
         <v>1202</v>
       </c>
@@ -1989,16 +2012,16 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J8" s="9">
         <v>4010017</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="10">
@@ -2007,9 +2030,12 @@
       <c r="N8" s="3">
         <v>60</v>
       </c>
-      <c r="Q8" s="16"/>
+      <c r="O8" s="3">
+        <v>300</v>
+      </c>
+      <c r="R8" s="16"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:17">
+    <row r="9" s="3" customFormat="1" spans="1:18">
       <c r="A9" s="9">
         <v>1303</v>
       </c>
@@ -2030,16 +2056,16 @@
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J9" s="9">
         <v>4010019</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="10">
@@ -2048,9 +2074,9 @@
       <c r="N9" s="3">
         <v>60</v>
       </c>
-      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:17">
+    <row r="10" s="3" customFormat="1" spans="1:18">
       <c r="A10" s="9">
         <v>1304</v>
       </c>
@@ -2071,16 +2097,16 @@
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J10" s="9">
         <v>4010020</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="10">
@@ -2089,9 +2115,9 @@
       <c r="N10" s="3">
         <v>60</v>
       </c>
-      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:17">
+    <row r="11" s="3" customFormat="1" spans="1:18">
       <c r="A11" s="9">
         <v>1110</v>
       </c>
@@ -2099,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="10">
         <v>1</v>
@@ -2112,16 +2138,16 @@
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J11" s="9">
         <v>100700001</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L11" s="15">
         <v>100700</v>
@@ -2132,8 +2158,11 @@
       <c r="N11" s="3">
         <v>60</v>
       </c>
+      <c r="O11" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:17">
+    <row r="12" s="3" customFormat="1" spans="1:18">
       <c r="A12" s="9">
         <v>1107</v>
       </c>
@@ -2141,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
@@ -2154,16 +2183,16 @@
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J12" s="9">
         <v>101800001</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L12" s="15">
         <v>101800</v>
@@ -2174,8 +2203,11 @@
       <c r="N12" s="3">
         <v>60</v>
       </c>
+      <c r="O12" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:17">
+    <row r="13" s="3" customFormat="1" spans="1:18">
       <c r="A13" s="9">
         <v>1106</v>
       </c>
@@ -2183,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
@@ -2196,16 +2228,16 @@
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J13" s="9">
         <v>103100001</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L13" s="16">
         <v>103100</v>
@@ -2216,9 +2248,12 @@
       <c r="N13" s="3">
         <v>60</v>
       </c>
-      <c r="Q13" s="16"/>
+      <c r="O13" s="3">
+        <v>300</v>
+      </c>
+      <c r="R13" s="16"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:17">
+    <row r="14" s="3" customFormat="1" spans="1:18">
       <c r="A14" s="9">
         <v>1105</v>
       </c>
@@ -2226,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
@@ -2239,16 +2274,16 @@
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J14" s="9">
         <v>102500001</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L14" s="16">
         <v>102500</v>
@@ -2259,9 +2294,12 @@
       <c r="N14" s="3">
         <v>60</v>
       </c>
-      <c r="Q14" s="16"/>
+      <c r="O14" s="3">
+        <v>300</v>
+      </c>
+      <c r="R14" s="16"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:17">
+    <row r="15" s="3" customFormat="1" spans="1:18">
       <c r="A15" s="9">
         <v>1104</v>
       </c>
@@ -2269,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -2282,16 +2320,16 @@
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J15" s="9">
         <v>101200001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L15" s="16">
         <v>101200</v>
@@ -2302,9 +2340,12 @@
       <c r="N15" s="3">
         <v>60</v>
       </c>
-      <c r="Q15" s="16"/>
+      <c r="O15" s="3">
+        <v>300</v>
+      </c>
+      <c r="R15" s="16"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:17">
+    <row r="16" s="3" customFormat="1" spans="1:18">
       <c r="A16" s="9">
         <v>1103</v>
       </c>
@@ -2312,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
@@ -2325,16 +2366,16 @@
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="9">
         <v>100300001</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L16" s="15">
         <v>100300</v>
@@ -2345,9 +2386,12 @@
       <c r="N16" s="3">
         <v>60</v>
       </c>
-      <c r="Q16" s="16"/>
+      <c r="O16" s="3">
+        <v>300</v>
+      </c>
+      <c r="R16" s="16"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:17">
+    <row r="17" s="3" customFormat="1" spans="1:18">
       <c r="A17" s="9">
         <v>1109</v>
       </c>
@@ -2355,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" s="10">
         <v>1</v>
@@ -2368,16 +2412,16 @@
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J17" s="9">
         <v>101500001</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L17" s="16">
         <v>101500</v>
@@ -2388,8 +2432,11 @@
       <c r="N17" s="3">
         <v>60</v>
       </c>
+      <c r="O17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:17">
+    <row r="18" s="3" customFormat="1" spans="1:18">
       <c r="A18" s="9">
         <v>1108</v>
       </c>
@@ -2397,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" s="10">
         <v>1</v>
@@ -2410,16 +2457,16 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="9">
         <v>102000001</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L18" s="16">
         <v>102000</v>
@@ -2430,8 +2477,11 @@
       <c r="N18" s="3">
         <v>60</v>
       </c>
+      <c r="O18" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:17">
+    <row r="19" s="3" customFormat="1" spans="1:18">
       <c r="A19" s="9">
         <v>1112</v>
       </c>
@@ -2439,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
@@ -2452,16 +2502,16 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J19" s="9">
         <v>102100001</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L19" s="16">
         <v>102100</v>
@@ -2472,8 +2522,11 @@
       <c r="N19" s="3">
         <v>60</v>
       </c>
+      <c r="O19" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:17">
+    <row r="20" s="3" customFormat="1" spans="1:18">
       <c r="A20" s="9">
         <v>1111</v>
       </c>
@@ -2481,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" s="10">
         <v>1</v>
@@ -2494,16 +2547,16 @@
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J20" s="9">
         <v>102200001</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L20" s="16">
         <v>102200</v>
@@ -2514,9 +2567,12 @@
       <c r="N20" s="3">
         <v>60</v>
       </c>
-      <c r="Q20" s="16"/>
+      <c r="O20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="16"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:18">
       <c r="A21" s="9">
         <v>1401</v>
       </c>
@@ -2535,18 +2591,19 @@
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="A22" s="9">
         <v>1402</v>
       </c>
@@ -2565,18 +2622,19 @@
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:18">
       <c r="A23" s="9">
         <v>1403</v>
       </c>
@@ -2595,18 +2653,19 @@
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:18">
       <c r="A24" s="9">
         <v>1404</v>
       </c>
@@ -2625,19 +2684,20 @@
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L24" s="18"/>
       <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:18">
       <c r="A25" s="9">
         <v>1405</v>
       </c>
@@ -2656,17 +2716,18 @@
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L25" s="18"/>
       <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -283,7 +283,7 @@
     <t>等级上限</t>
   </si>
   <si>
-    <t>交互时间(S)</t>
+    <t>交互时间(MS)</t>
   </si>
   <si>
     <t>#重要说明：注：
@@ -1943,7 +1943,7 @@
         <v>60</v>
       </c>
       <c r="O6" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:18">
@@ -1988,7 +1988,7 @@
         <v>60</v>
       </c>
       <c r="O7" s="3">
-        <v>300</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:18">
@@ -2031,7 +2031,7 @@
         <v>60</v>
       </c>
       <c r="O8" s="3">
-        <v>300</v>
+        <v>6000</v>
       </c>
       <c r="R8" s="16"/>
     </row>
@@ -2159,7 +2159,7 @@
         <v>60</v>
       </c>
       <c r="O11" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:18">
@@ -2204,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="O12" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:18">
@@ -2249,7 +2249,7 @@
         <v>60</v>
       </c>
       <c r="O13" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="R13" s="16"/>
     </row>
@@ -2295,7 +2295,7 @@
         <v>60</v>
       </c>
       <c r="O14" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="R14" s="16"/>
     </row>
@@ -2341,7 +2341,7 @@
         <v>60</v>
       </c>
       <c r="O15" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="R15" s="16"/>
     </row>
@@ -2387,7 +2387,7 @@
         <v>60</v>
       </c>
       <c r="O16" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="R16" s="16"/>
     </row>
@@ -2433,7 +2433,7 @@
         <v>60</v>
       </c>
       <c r="O17" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:18">
@@ -2478,7 +2478,7 @@
         <v>60</v>
       </c>
       <c r="O18" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:18">
@@ -2523,7 +2523,7 @@
         <v>60</v>
       </c>
       <c r="O19" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:18">
@@ -2568,7 +2568,7 @@
         <v>60</v>
       </c>
       <c r="O20" s="3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="R20" s="16"/>
     </row>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -384,31 +384,61 @@
     <t>营销部</t>
   </si>
   <si>
+    <t>1102_10</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
   </si>
   <si>
+    <t>1110_15</t>
+  </si>
+  <si>
     <t>篮球巨星</t>
   </si>
   <si>
+    <t>1107_20</t>
+  </si>
+  <si>
     <t>绿巨人</t>
   </si>
   <si>
+    <t>1106_25</t>
+  </si>
+  <si>
     <t>寒冰王座</t>
   </si>
   <si>
+    <t>1105_30</t>
+  </si>
+  <si>
     <t>财神来了</t>
   </si>
   <si>
+    <t>1104_30</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
+    <t>1103_30</t>
+  </si>
+  <si>
     <t>狼月</t>
   </si>
   <si>
+    <t>1109_30</t>
+  </si>
+  <si>
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
+    <t>1108_30</t>
+  </si>
+  <si>
     <t>杰克船长</t>
+  </si>
+  <si>
+    <t>1112_30</t>
   </si>
   <si>
     <t>雷神</t>
@@ -2136,7 +2166,9 @@
       <c r="F11" s="10">
         <v>7</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="H11" s="10" t="s">
         <v>37</v>
       </c>
@@ -2147,7 +2179,7 @@
         <v>100700001</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L11" s="15">
         <v>100700</v>
@@ -2179,9 +2211,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="10">
-        <v>10</v>
-      </c>
-      <c r="G12" s="10"/>
+        <v>11</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="H12" s="10" t="s">
         <v>41</v>
       </c>
@@ -2192,7 +2226,7 @@
         <v>101800001</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L12" s="15">
         <v>101800</v>
@@ -2224,9 +2258,11 @@
         <v>1</v>
       </c>
       <c r="F13" s="10">
-        <v>12</v>
-      </c>
-      <c r="G13" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="H13" s="10" t="s">
         <v>41</v>
       </c>
@@ -2237,7 +2273,7 @@
         <v>103100001</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L13" s="16">
         <v>103100</v>
@@ -2270,9 +2306,11 @@
         <v>1</v>
       </c>
       <c r="F14" s="10">
-        <v>14</v>
-      </c>
-      <c r="G14" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="H14" s="10" t="s">
         <v>41</v>
       </c>
@@ -2283,7 +2321,7 @@
         <v>102500001</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L14" s="16">
         <v>102500</v>
@@ -2316,9 +2354,11 @@
         <v>1</v>
       </c>
       <c r="F15" s="10">
-        <v>16</v>
-      </c>
-      <c r="G15" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="H15" s="10" t="s">
         <v>41</v>
       </c>
@@ -2329,7 +2369,7 @@
         <v>101200001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L15" s="16">
         <v>101200</v>
@@ -2362,9 +2402,11 @@
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>18</v>
-      </c>
-      <c r="G16" s="10"/>
+        <v>27</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="H16" s="10" t="s">
         <v>41</v>
       </c>
@@ -2375,7 +2417,7 @@
         <v>100300001</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L16" s="15">
         <v>100300</v>
@@ -2408,9 +2450,11 @@
         <v>1</v>
       </c>
       <c r="F17" s="10">
-        <v>20</v>
-      </c>
-      <c r="G17" s="10"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="H17" s="10" t="s">
         <v>41</v>
       </c>
@@ -2421,7 +2465,7 @@
         <v>101500001</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L17" s="16">
         <v>101500</v>
@@ -2453,9 +2497,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="10">
-        <v>22</v>
-      </c>
-      <c r="G18" s="10"/>
+        <v>35</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="H18" s="10" t="s">
         <v>41</v>
       </c>
@@ -2466,7 +2512,7 @@
         <v>102000001</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L18" s="16">
         <v>102000</v>
@@ -2498,9 +2544,11 @@
         <v>1</v>
       </c>
       <c r="F19" s="10">
-        <v>24</v>
-      </c>
-      <c r="G19" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="H19" s="10" t="s">
         <v>41</v>
       </c>
@@ -2511,7 +2559,7 @@
         <v>102100001</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L19" s="16">
         <v>102100</v>
@@ -2543,9 +2591,11 @@
         <v>1</v>
       </c>
       <c r="F20" s="10">
-        <v>26</v>
-      </c>
-      <c r="G20" s="10"/>
+        <v>43</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="H20" s="10" t="s">
         <v>41</v>
       </c>
@@ -2556,7 +2606,7 @@
         <v>102200001</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="L20" s="16">
         <v>102200</v>
@@ -2594,11 +2644,11 @@
         <v>37</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
@@ -2625,11 +2675,11 @@
         <v>37</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
@@ -2656,11 +2706,11 @@
         <v>37</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
@@ -2687,11 +2737,11 @@
         <v>37</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="18" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L24" s="18"/>
       <c r="O24" s="14"/>
@@ -2719,11 +2769,11 @@
         <v>37</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="18" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="L25" s="18"/>
       <c r="O25" s="14"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -363,9 +363,15 @@
     <t>愤怒的小鸟</t>
   </si>
   <si>
+    <t>1101_3</t>
+  </si>
+  <si>
     <t>象财神</t>
   </si>
   <si>
+    <t>1102_5</t>
+  </si>
+  <si>
     <t>1990000_20000</t>
   </si>
   <si>
@@ -375,70 +381,55 @@
     <t>VIP休息区</t>
   </si>
   <si>
+    <t>1202_3</t>
+  </si>
+  <si>
     <t>1990000_5000</t>
   </si>
   <si>
     <t>运营部</t>
   </si>
   <si>
+    <t>1303_3</t>
+  </si>
+  <si>
     <t>营销部</t>
   </si>
   <si>
-    <t>1102_10</t>
+    <t>1304_3</t>
   </si>
   <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1110_15</t>
+    <t>1110_12</t>
   </si>
   <si>
     <t>篮球巨星</t>
   </si>
   <si>
-    <t>1107_20</t>
+    <t>1107_15</t>
   </si>
   <si>
     <t>绿巨人</t>
   </si>
   <si>
-    <t>1106_25</t>
-  </si>
-  <si>
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>1105_30</t>
-  </si>
-  <si>
     <t>财神来了</t>
   </si>
   <si>
-    <t>1104_30</t>
-  </si>
-  <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>1103_30</t>
-  </si>
-  <si>
     <t>狼月</t>
   </si>
   <si>
-    <t>1109_30</t>
-  </si>
-  <si>
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>1108_30</t>
-  </si>
-  <si>
     <t>杰克船长</t>
-  </si>
-  <si>
-    <t>1112_30</t>
   </si>
   <si>
     <t>雷神</t>
@@ -472,7 +463,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +498,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1001,137 +998,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,6 +1140,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1179,6 +1179,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1729,7 +1732,7 @@
     <col min="3" max="3" width="15" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
     <col min="5" max="6" width="12.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.125" style="4" customWidth="1"/>
     <col min="8" max="8" width="18.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.125" style="3" customWidth="1"/>
     <col min="10" max="10" width="17.5" style="3" customWidth="1"/>
@@ -1743,40 +1746,40 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1788,47 +1791,47 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:18">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="O2" s="1" t="s">
@@ -1836,36 +1839,36 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:18">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -1877,96 +1880,96 @@
       <c r="O3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="8"/>
+      <c r="P3" s="9"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:18">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>1301</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <v>3</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <v>3</v>
       </c>
-      <c r="D5" s="12">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="b">
+      <c r="D5" s="13">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12" t="s">
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="12">
         <v>4010018</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12">
+      <c r="L5" s="12"/>
+      <c r="M5" s="13">
         <v>30</v>
       </c>
       <c r="N5" s="2">
         <v>60</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:18">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>1101</v>
       </c>
-      <c r="B6" s="10">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <v>103900001</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="16">
         <v>103900</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="11">
         <v>10</v>
       </c>
       <c r="N6" s="3">
@@ -1977,41 +1980,43 @@
       </c>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:18">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>1102</v>
       </c>
-      <c r="B7" s="10">
-        <v>1</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="10">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11">
         <v>3</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="10">
         <v>102700001</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="15">
+      <c r="K7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="16">
         <v>102700</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="11">
         <v>10</v>
       </c>
       <c r="N7" s="3">
@@ -2022,39 +2027,41 @@
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:18">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>1202</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>2</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>2</v>
       </c>
-      <c r="D8" s="10">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="D8" s="11">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
         <v>4</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="G8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="9">
+      <c r="H8" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="10">
         <v>4010017</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>43</v>
+      <c r="K8" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="L8" s="3"/>
-      <c r="M8" s="10">
+      <c r="M8" s="11">
         <v>20</v>
       </c>
       <c r="N8" s="3">
@@ -2063,128 +2070,132 @@
       <c r="O8" s="3">
         <v>6000</v>
       </c>
-      <c r="R8" s="16"/>
+      <c r="R8" s="18"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:18">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <v>1303</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>3</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <v>5</v>
       </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
         <v>4</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="G9" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <v>4010019</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>45</v>
+      <c r="K9" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="L9" s="3"/>
-      <c r="M9" s="10">
+      <c r="M9" s="11">
         <v>30</v>
       </c>
       <c r="N9" s="3">
         <v>60</v>
       </c>
-      <c r="R9" s="17"/>
+      <c r="R9" s="19"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:18">
-      <c r="A10" s="9">
+      <c r="A10" s="10">
         <v>1304</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>3</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <v>6</v>
       </c>
-      <c r="D10" s="10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="D10" s="11">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11">
         <v>4</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="G10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="10">
         <v>4010020</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>46</v>
+      <c r="K10" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="10">
+      <c r="M10" s="11">
         <v>30</v>
       </c>
       <c r="N10" s="3">
         <v>60</v>
       </c>
-      <c r="R10" s="17"/>
+      <c r="R10" s="19"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:18">
-      <c r="A11" s="9">
+      <c r="A11" s="10">
         <v>1110</v>
       </c>
-      <c r="B11" s="10">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11">
         <v>7</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="10">
         <v>100700001</v>
       </c>
-      <c r="K11" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="15">
+      <c r="K11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="16">
         <v>100700</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="11">
         <v>10</v>
       </c>
       <c r="N11" s="3">
@@ -2195,43 +2206,43 @@
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:18">
-      <c r="A12" s="9">
+      <c r="A12" s="10">
         <v>1107</v>
       </c>
-      <c r="B12" s="10">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="11">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="10">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11">
         <v>11</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="G12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="10">
         <v>101800001</v>
       </c>
-      <c r="K12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="15">
+      <c r="K12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="16">
         <v>101800</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="11">
         <v>10</v>
       </c>
       <c r="N12" s="3">
@@ -2242,43 +2253,43 @@
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:18">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>1106</v>
       </c>
-      <c r="B13" s="10">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="11">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="10">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="D13" s="11">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
         <v>15</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="G13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="10">
         <v>103100001</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="16">
+      <c r="K13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="18">
         <v>103100</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="11">
         <v>10</v>
       </c>
       <c r="N13" s="3">
@@ -2287,46 +2298,44 @@
       <c r="O13" s="3">
         <v>5000</v>
       </c>
-      <c r="R13" s="16"/>
+      <c r="R13" s="18"/>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:18">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <v>1105</v>
       </c>
-      <c r="B14" s="10">
-        <v>1</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="11">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="10">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11">
         <v>19</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="10">
         <v>102500001</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" s="16">
+      <c r="K14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="18">
         <v>102500</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="11">
         <v>10</v>
       </c>
       <c r="N14" s="3">
@@ -2335,46 +2344,44 @@
       <c r="O14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="16"/>
+      <c r="R14" s="18"/>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:18">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>1104</v>
       </c>
-      <c r="B15" s="10">
-        <v>1</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="11">
+        <v>1</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="D15" s="11">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11">
         <v>23</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="10" t="s">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="10">
         <v>101200001</v>
       </c>
-      <c r="K15" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15" s="16">
+      <c r="K15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="18">
         <v>101200</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="11">
         <v>10</v>
       </c>
       <c r="N15" s="3">
@@ -2383,46 +2390,44 @@
       <c r="O15" s="3">
         <v>5000</v>
       </c>
-      <c r="R15" s="16"/>
+      <c r="R15" s="18"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:18">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <v>1103</v>
       </c>
-      <c r="B16" s="10">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="11">
+        <v>1</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="D16" s="11">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
         <v>27</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="G16" s="11"/>
+      <c r="H16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <v>100300001</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" s="15">
+      <c r="K16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16">
         <v>100300</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="11">
         <v>10</v>
       </c>
       <c r="N16" s="3">
@@ -2431,46 +2436,44 @@
       <c r="O16" s="3">
         <v>5000</v>
       </c>
-      <c r="R16" s="16"/>
+      <c r="R16" s="18"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:18">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>1109</v>
       </c>
-      <c r="B17" s="10">
-        <v>1</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="11">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11">
         <v>31</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" s="10" t="s">
+      <c r="G17" s="11"/>
+      <c r="H17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <v>101500001</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="18">
         <v>101500</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="11">
         <v>10</v>
       </c>
       <c r="N17" s="3">
@@ -2481,43 +2484,41 @@
       </c>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:18">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>1108</v>
       </c>
-      <c r="B18" s="10">
-        <v>1</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="11">
+        <v>1</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="10">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11">
         <v>35</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11"/>
+      <c r="H18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="10">
+        <v>102000001</v>
+      </c>
+      <c r="K18" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="9">
-        <v>102000001</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18" s="16">
+      <c r="L18" s="18">
         <v>102000</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="11">
         <v>10</v>
       </c>
       <c r="N18" s="3">
@@ -2528,43 +2529,41 @@
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:18">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>1112</v>
       </c>
-      <c r="B19" s="10">
-        <v>1</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="11">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="10">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11">
         <v>39</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="G19" s="11"/>
+      <c r="H19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="10">
         <v>102100001</v>
       </c>
-      <c r="K19" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L19" s="16">
+      <c r="K19" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="18">
         <v>102100</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="11">
         <v>10</v>
       </c>
       <c r="N19" s="3">
@@ -2575,43 +2574,41 @@
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:18">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>1111</v>
       </c>
-      <c r="B20" s="10">
-        <v>1</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="11">
+        <v>1</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="10">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11">
         <v>43</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="G20" s="11"/>
+      <c r="H20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="10">
         <v>102200001</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L20" s="16">
+      <c r="K20" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="18">
         <v>102200</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="11">
         <v>10</v>
       </c>
       <c r="N20" s="3">
@@ -2620,171 +2617,177 @@
       <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="16"/>
+      <c r="R20" s="18"/>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>1401</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>4</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="11">
         <v>7</v>
       </c>
-      <c r="D21" s="10">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10" t="s">
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="9"/>
+      <c r="I21" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="10"/>
       <c r="K21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
+        <v>65</v>
+      </c>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="9">
+      <c r="A22" s="10">
         <v>1402</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>4</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="11">
         <v>8</v>
       </c>
-      <c r="D22" s="10">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10" t="s">
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" s="9"/>
+      <c r="I22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="10"/>
       <c r="K22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <v>1403</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>4</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="11">
         <v>9</v>
       </c>
-      <c r="D23" s="10">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10" t="s">
+      <c r="D23" s="11">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>1404</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>4</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="11">
         <v>10</v>
       </c>
-      <c r="D24" s="10">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10" t="s">
+      <c r="D24" s="11">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="L24" s="18"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="I24" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="20"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <v>1405</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>4</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="11">
         <v>10</v>
       </c>
-      <c r="D25" s="10">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10" t="s">
+      <c r="D25" s="11">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="L25" s="18"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
+      <c r="I25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="10"/>
+      <c r="K25" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A5 A7:A25 A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.显示的先后顺序为：从左往右；
+2.若有满足的条件则跳过显示不满足的条件；
+3.若所有条件都满足，则显示最后一个条件</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -210,7 +234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -239,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -260,6 +284,9 @@
   </si>
   <si>
     <t>解锁条件2</t>
+  </si>
+  <si>
+    <t>解锁提示多语言</t>
   </si>
   <si>
     <t>解锁消耗</t>
@@ -327,6 +354,9 @@
     <t>UnlockMethod</t>
   </si>
   <si>
+    <t>languageID</t>
+  </si>
+  <si>
     <t>UnlockCost</t>
   </si>
   <si>
@@ -354,6 +384,9 @@
     <t>1_12</t>
   </si>
   <si>
+    <t>4010047_0_4010048</t>
+  </si>
+  <si>
     <t>1990000_10000</t>
   </si>
   <si>
@@ -364,6 +397,9 @@
   </si>
   <si>
     <t>1101_3</t>
+  </si>
+  <si>
+    <t>4010047_4010046_4010048</t>
   </si>
   <si>
     <t>象财神</t>
@@ -1128,7 +1164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,9 +1198,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1175,6 +1208,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1188,9 +1224,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1724,7 +1757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1733,19 +1766,20 @@
     <col min="4" max="4" width="10.125" style="3" customWidth="1"/>
     <col min="5" max="6" width="12.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="17.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16" style="3" customWidth="1"/>
-    <col min="13" max="13" width="17.625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="23" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.75" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="10.375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="12.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1773,7 +1807,7 @@
       <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -1782,7 +1816,7 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1791,990 +1825,1045 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:18">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>16</v>
+      <c r="I2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:18">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:19">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="N3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:18">
-      <c r="A5" s="12">
+    <row r="5" s="2" customFormat="1" spans="1:19">
+      <c r="A5" s="11">
         <v>1301</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>3</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <v>3</v>
       </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13" t="b">
+      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="12">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="11">
         <v>4010018</v>
       </c>
-      <c r="K5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="13">
+      <c r="L5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="N5" s="12">
         <v>30</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>60</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:18">
+    <row r="6" s="3" customFormat="1" spans="1:19">
       <c r="A6" s="10">
         <v>1101</v>
       </c>
-      <c r="B6" s="11">
-        <v>1</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11">
-        <v>1</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="10">
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="10">
         <v>103900001</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="16">
+      <c r="L6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="16">
         <v>103900</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="4">
         <v>10</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>60</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:18">
+    <row r="7" s="3" customFormat="1" spans="1:19">
       <c r="A7" s="10">
         <v>1102</v>
       </c>
-      <c r="B7" s="11">
-        <v>1</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="11">
-        <v>1</v>
-      </c>
-      <c r="E7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
         <v>3</v>
       </c>
       <c r="G7" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="10">
+      <c r="J7" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="10">
         <v>102700001</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="16">
+      <c r="L7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="16">
         <v>102700</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="4">
         <v>10</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>60</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:18">
+    <row r="8" s="3" customFormat="1" spans="1:19">
       <c r="A8" s="10">
         <v>1202</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="11">
-        <v>1</v>
-      </c>
-      <c r="E8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
         <v>4</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="10">
+        <v>47</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="10">
         <v>4010017</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="11">
+      <c r="L8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="4">
         <v>20</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>60</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6000</v>
       </c>
-      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:18">
+    <row r="9" s="3" customFormat="1" spans="1:19">
       <c r="A9" s="10">
         <v>1303</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
         <v>4</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="10">
+        <v>51</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="10">
         <v>4010019</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="11">
+      <c r="L9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="4">
         <v>30</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>60</v>
       </c>
-      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:18">
+    <row r="10" s="3" customFormat="1" spans="1:19">
       <c r="A10" s="10">
         <v>1304</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="4">
         <v>3</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="4">
         <v>6</v>
       </c>
-      <c r="D10" s="11">
-        <v>1</v>
-      </c>
-      <c r="E10" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
         <v>4</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="10">
+        <v>51</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="10">
         <v>4010020</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="11">
+      <c r="L10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="4">
         <v>30</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60</v>
       </c>
-      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:18">
+    <row r="11" s="3" customFormat="1" spans="1:19">
       <c r="A11" s="10">
         <v>1110</v>
       </c>
-      <c r="B11" s="11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
         <v>7</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="10">
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="10">
         <v>100700001</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="L11" s="16">
+      <c r="L11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16">
         <v>100700</v>
       </c>
-      <c r="M11" s="11">
+      <c r="N11" s="4">
         <v>10</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>60</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:18">
+    <row r="12" s="3" customFormat="1" spans="1:19">
       <c r="A12" s="10">
         <v>1107</v>
       </c>
-      <c r="B12" s="11">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
         <v>11</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="10">
+      <c r="G12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="10">
         <v>101800001</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="16">
+      <c r="L12" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16">
         <v>101800</v>
       </c>
-      <c r="M12" s="11">
+      <c r="N12" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>60</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:18">
+    <row r="13" s="3" customFormat="1" spans="1:19">
       <c r="A13" s="10">
         <v>1106</v>
       </c>
-      <c r="B13" s="11">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="11">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
         <v>15</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="10">
+      <c r="G13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="10">
         <v>103100001</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" s="18">
+      <c r="L13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="18">
         <v>103100</v>
       </c>
-      <c r="M13" s="11">
+      <c r="N13" s="4">
         <v>10</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>60</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>5000</v>
       </c>
-      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:18">
+    <row r="14" s="3" customFormat="1" spans="1:19">
       <c r="A14" s="10">
         <v>1105</v>
       </c>
-      <c r="B14" s="11">
-        <v>1</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="11">
-        <v>1</v>
-      </c>
-      <c r="E14" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="11">
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
         <v>19</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="10">
+      <c r="G14" s="4"/>
+      <c r="H14" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="10">
         <v>102500001</v>
       </c>
-      <c r="K14" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="18">
+      <c r="L14" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="18">
         <v>102500</v>
       </c>
-      <c r="M14" s="11">
+      <c r="N14" s="4">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>60</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:18">
+    <row r="15" s="3" customFormat="1" spans="1:19">
       <c r="A15" s="10">
         <v>1104</v>
       </c>
-      <c r="B15" s="11">
-        <v>1</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="11">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11">
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
         <v>23</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="10">
+      <c r="G15" s="4"/>
+      <c r="H15" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="10">
         <v>101200001</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="18">
+      <c r="L15" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="18">
         <v>101200</v>
       </c>
-      <c r="M15" s="11">
+      <c r="N15" s="4">
         <v>10</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5000</v>
       </c>
-      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:18">
+    <row r="16" s="3" customFormat="1" spans="1:19">
       <c r="A16" s="10">
         <v>1103</v>
       </c>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1</v>
-      </c>
-      <c r="E16" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11">
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
         <v>27</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="10">
+      <c r="G16" s="4"/>
+      <c r="H16" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="10">
         <v>100300001</v>
       </c>
-      <c r="K16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="16">
+      <c r="L16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="16">
         <v>100300</v>
       </c>
-      <c r="M16" s="11">
+      <c r="N16" s="4">
         <v>10</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>60</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>5000</v>
       </c>
-      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:18">
+    <row r="17" s="3" customFormat="1" spans="1:19">
       <c r="A17" s="10">
         <v>1109</v>
       </c>
-      <c r="B17" s="11">
-        <v>1</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
         <v>31</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J17" s="10">
+      <c r="G17" s="4"/>
+      <c r="H17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="10">
         <v>101500001</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="L17" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="18">
+        <v>101500</v>
+      </c>
+      <c r="N17" s="4">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3">
         <v>60</v>
       </c>
-      <c r="L17" s="18">
-        <v>101500</v>
-      </c>
-      <c r="M17" s="11">
-        <v>10</v>
-      </c>
-      <c r="N17" s="3">
-        <v>60</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:18">
+    <row r="18" s="3" customFormat="1" spans="1:19">
       <c r="A18" s="10">
         <v>1108</v>
       </c>
-      <c r="B18" s="11">
-        <v>1</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="11">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="11">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
         <v>35</v>
       </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="10">
+      <c r="G18" s="4"/>
+      <c r="H18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="10">
         <v>102000001</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="L18" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="18">
         <v>102000</v>
       </c>
-      <c r="M18" s="11">
+      <c r="N18" s="4">
         <v>10</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>60</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:18">
+    <row r="19" s="3" customFormat="1" spans="1:19">
       <c r="A19" s="10">
         <v>1112</v>
       </c>
-      <c r="B19" s="11">
-        <v>1</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
         <v>39</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="10">
+      <c r="G19" s="4"/>
+      <c r="H19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="10">
         <v>102100001</v>
       </c>
-      <c r="K19" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="L19" s="18">
+      <c r="L19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="18">
         <v>102100</v>
       </c>
-      <c r="M19" s="11">
+      <c r="N19" s="4">
         <v>10</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>60</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:18">
+    <row r="20" s="3" customFormat="1" spans="1:19">
       <c r="A20" s="10">
         <v>1111</v>
       </c>
-      <c r="B20" s="11">
-        <v>1</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="11">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
         <v>43</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="10">
+      <c r="G20" s="4"/>
+      <c r="H20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="10">
         <v>102200001</v>
       </c>
-      <c r="K20" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" s="18">
+      <c r="L20" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20" s="18">
         <v>102200</v>
       </c>
-      <c r="M20" s="11">
+      <c r="N20" s="4">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>60</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:19">
       <c r="A21" s="10">
         <v>1401</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="4">
         <v>4</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="4">
         <v>7</v>
       </c>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O21" s="15"/>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:19">
       <c r="A22" s="10">
         <v>1402</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="4">
         <v>4</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="4">
         <v>8</v>
       </c>
-      <c r="D22" s="11">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="10"/>
-      <c r="K22" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O22" s="15"/>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K22" s="10"/>
+      <c r="L22" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:19">
       <c r="A23" s="10">
         <v>1403</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="4">
         <v>4</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="4">
         <v>9</v>
       </c>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="10"/>
-      <c r="K23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O23" s="15"/>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K23" s="10"/>
+      <c r="L23" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:19">
       <c r="A24" s="10">
         <v>1404</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="4">
         <v>4</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="4">
         <v>10</v>
       </c>
-      <c r="D24" s="11">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="20" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L24" s="20"/>
-      <c r="O24" s="15"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="M24" s="14"/>
       <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:19">
       <c r="A25" s="10">
         <v>1405</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="4">
         <v>4</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="4">
         <v>10</v>
       </c>
-      <c r="D25" s="11">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="L25" s="20"/>
-      <c r="O25" s="15"/>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="L25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M25" s="14"/>
       <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -2133,7 +2133,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2179,7 +2179,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -263,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -313,8 +313,10 @@
     <t>交互时间(MS)</t>
   </si>
   <si>
-    <t>#重要说明：注：
-1. 该表配置数据顺序即为解锁建筑的顺序。
+    <t>跳转ID</t>
+  </si>
+  <si>
+    <t>#重要说明：注：1. 该表配置数据顺序即为解锁建筑的顺序。
 2.修改了解锁顺序，前端文件“”也需要修改，直接找前端程序修改或策划自己去修改。</t>
   </si>
   <si>
@@ -373,6 +375,9 @@
   </si>
   <si>
     <t>InteractTime</t>
+  </si>
+  <si>
+    <t>JumpId</t>
   </si>
   <si>
     <t>管理</t>
@@ -1757,7 +1762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1774,12 +1779,12 @@
     <col min="13" max="13" width="16" style="3" customWidth="1"/>
     <col min="14" max="14" width="17.625" style="3" customWidth="1"/>
     <col min="15" max="15" width="10.375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="3" customWidth="1"/>
-    <col min="17" max="17" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="3"/>
+    <col min="16" max="17" width="12.75" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1828,104 +1833,113 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:20">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:19">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:20">
       <c r="A4" s="10"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1939,7 +1953,7 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:19">
+    <row r="5" s="2" customFormat="1" spans="1:20">
       <c r="A5" s="11">
         <v>1301</v>
       </c>
@@ -1960,13 +1974,13 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K5" s="11">
         <v>4010018</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="12">
@@ -1976,9 +1990,12 @@
         <v>60</v>
       </c>
       <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="Q5" s="13">
+        <v>3554</v>
+      </c>
+      <c r="R5" s="13"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:19">
+    <row r="6" s="3" customFormat="1" spans="1:20">
       <c r="A6" s="10">
         <v>1101</v>
       </c>
@@ -1986,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1999,19 +2016,19 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K6" s="10">
         <v>103900001</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M6" s="16">
         <v>103900</v>
@@ -2025,8 +2042,11 @@
       <c r="P6" s="3">
         <v>5000</v>
       </c>
+      <c r="Q6" s="3">
+        <v>1101</v>
+      </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:19">
+    <row r="7" s="3" customFormat="1" spans="1:20">
       <c r="A7" s="10">
         <v>1102</v>
       </c>
@@ -2034,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -2046,22 +2066,22 @@
         <v>3</v>
       </c>
       <c r="G7" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="K7" s="10">
         <v>102700001</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M7" s="16">
         <v>102700</v>
@@ -2075,8 +2095,11 @@
       <c r="P7" s="3">
         <v>8000</v>
       </c>
+      <c r="Q7" s="3">
+        <v>1102</v>
+      </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:19">
+    <row r="8" s="3" customFormat="1" spans="1:20">
       <c r="A8" s="10">
         <v>1202</v>
       </c>
@@ -2096,22 +2119,22 @@
         <v>4</v>
       </c>
       <c r="G8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="I8" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K8" s="10">
         <v>4010017</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4">
@@ -2123,9 +2146,12 @@
       <c r="P8" s="3">
         <v>6000</v>
       </c>
-      <c r="S8" s="18"/>
+      <c r="Q8" s="3">
+        <v>3551</v>
+      </c>
+      <c r="T8" s="18"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:19">
+    <row r="9" s="3" customFormat="1" spans="1:20">
       <c r="A9" s="10">
         <v>1303</v>
       </c>
@@ -2145,22 +2171,22 @@
         <v>4</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K9" s="10">
         <v>4010019</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="4">
@@ -2169,9 +2195,12 @@
       <c r="O9" s="3">
         <v>60</v>
       </c>
-      <c r="S9" s="19"/>
+      <c r="Q9" s="3">
+        <v>3552</v>
+      </c>
+      <c r="T9" s="19"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:19">
+    <row r="10" s="3" customFormat="1" spans="1:20">
       <c r="A10" s="10">
         <v>1304</v>
       </c>
@@ -2191,22 +2220,22 @@
         <v>4</v>
       </c>
       <c r="G10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>51</v>
-      </c>
       <c r="J10" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K10" s="10">
         <v>4010020</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="4">
@@ -2215,9 +2244,12 @@
       <c r="O10" s="3">
         <v>60</v>
       </c>
-      <c r="S10" s="19"/>
+      <c r="Q10" s="3">
+        <v>3553</v>
+      </c>
+      <c r="T10" s="19"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:19">
+    <row r="11" s="3" customFormat="1" spans="1:20">
       <c r="A11" s="10">
         <v>1110</v>
       </c>
@@ -2225,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2237,22 +2269,22 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K11" s="10">
         <v>100700001</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M11" s="16">
         <v>100700</v>
@@ -2266,8 +2298,11 @@
       <c r="P11" s="3">
         <v>5000</v>
       </c>
+      <c r="Q11" s="3">
+        <v>3203</v>
+      </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:19">
+    <row r="12" s="3" customFormat="1" spans="1:20">
       <c r="A12" s="10">
         <v>1107</v>
       </c>
@@ -2275,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2287,22 +2322,22 @@
         <v>11</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K12" s="10">
         <v>101800001</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M12" s="16">
         <v>101800</v>
@@ -2316,8 +2351,11 @@
       <c r="P12" s="3">
         <v>5000</v>
       </c>
+      <c r="Q12" s="3">
+        <v>3204</v>
+      </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:19">
+    <row r="13" s="3" customFormat="1" spans="1:20">
       <c r="A13" s="10">
         <v>1106</v>
       </c>
@@ -2325,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -2337,22 +2375,22 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K13" s="10">
         <v>103100001</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M13" s="18">
         <v>103100</v>
@@ -2366,9 +2404,12 @@
       <c r="P13" s="3">
         <v>5000</v>
       </c>
-      <c r="S13" s="18"/>
+      <c r="Q13" s="3">
+        <v>3208</v>
+      </c>
+      <c r="T13" s="18"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:19">
+    <row r="14" s="3" customFormat="1" spans="1:20">
       <c r="A14" s="10">
         <v>1105</v>
       </c>
@@ -2376,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -2389,19 +2430,19 @@
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K14" s="10">
         <v>102500001</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M14" s="18">
         <v>102500</v>
@@ -2415,9 +2456,12 @@
       <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="18"/>
+      <c r="Q14" s="3">
+        <v>3207</v>
+      </c>
+      <c r="T14" s="18"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:19">
+    <row r="15" s="3" customFormat="1" spans="1:20">
       <c r="A15" s="10">
         <v>1104</v>
       </c>
@@ -2425,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -2438,19 +2482,19 @@
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K15" s="10">
         <v>101200001</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M15" s="18">
         <v>101200</v>
@@ -2464,9 +2508,12 @@
       <c r="P15" s="3">
         <v>5000</v>
       </c>
-      <c r="S15" s="18"/>
+      <c r="Q15" s="3">
+        <v>3206</v>
+      </c>
+      <c r="T15" s="18"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:19">
+    <row r="16" s="3" customFormat="1" spans="1:20">
       <c r="A16" s="10">
         <v>1103</v>
       </c>
@@ -2474,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -2487,19 +2534,19 @@
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K16" s="10">
         <v>100300001</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M16" s="16">
         <v>100300</v>
@@ -2513,9 +2560,12 @@
       <c r="P16" s="3">
         <v>5000</v>
       </c>
-      <c r="S16" s="18"/>
+      <c r="Q16" s="3">
+        <v>3205</v>
+      </c>
+      <c r="T16" s="18"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:19">
+    <row r="17" s="3" customFormat="1" spans="1:20">
       <c r="A17" s="10">
         <v>1109</v>
       </c>
@@ -2523,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -2536,19 +2586,19 @@
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K17" s="10">
         <v>101500001</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M17" s="18">
         <v>101500</v>
@@ -2562,8 +2612,11 @@
       <c r="P17" s="3">
         <v>5000</v>
       </c>
+      <c r="Q17" s="3">
+        <v>3212</v>
+      </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:19">
+    <row r="18" s="3" customFormat="1" spans="1:20">
       <c r="A18" s="10">
         <v>1108</v>
       </c>
@@ -2571,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -2584,19 +2637,19 @@
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K18" s="10">
         <v>102000001</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M18" s="18">
         <v>102000</v>
@@ -2610,8 +2663,11 @@
       <c r="P18" s="3">
         <v>5000</v>
       </c>
+      <c r="Q18" s="3">
+        <v>3211</v>
+      </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:19">
+    <row r="19" s="3" customFormat="1" spans="1:20">
       <c r="A19" s="10">
         <v>1112</v>
       </c>
@@ -2619,7 +2675,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -2632,19 +2688,19 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K19" s="10">
         <v>102100001</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M19" s="18">
         <v>102100</v>
@@ -2658,8 +2714,11 @@
       <c r="P19" s="3">
         <v>5000</v>
       </c>
+      <c r="Q19" s="3">
+        <v>3210</v>
+      </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:19">
+    <row r="20" s="3" customFormat="1" spans="1:20">
       <c r="A20" s="10">
         <v>1111</v>
       </c>
@@ -2667,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -2680,19 +2739,19 @@
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K20" s="10">
         <v>102200001</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M20" s="18">
         <v>102200</v>
@@ -2706,9 +2765,12 @@
       <c r="P20" s="3">
         <v>5000</v>
       </c>
-      <c r="S20" s="18"/>
+      <c r="Q20" s="3">
+        <v>3209</v>
+      </c>
+      <c r="T20" s="18"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:20">
       <c r="A21" s="10">
         <v>1401</v>
       </c>
@@ -2727,19 +2789,20 @@
       <c r="F21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:20">
       <c r="A22" s="10">
         <v>1402</v>
       </c>
@@ -2758,19 +2821,20 @@
       <c r="F22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:20">
       <c r="A23" s="10">
         <v>1403</v>
       </c>
@@ -2789,19 +2853,20 @@
       <c r="F23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:20">
       <c r="A24" s="10">
         <v>1404</v>
       </c>
@@ -2820,20 +2885,21 @@
       <c r="F24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M24" s="14"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:20">
       <c r="A25" s="10">
         <v>1405</v>
       </c>
@@ -2852,18 +2918,19 @@
       <c r="F25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M25" s="14"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,8 @@
 9. 风云榜
 10. 装饰-无作用
 11.管理属性（包括3-服务能力；5-知名度；6=曝光度）
-12.娱乐城经验</t>
+12.娱乐城经验
+13.看广告金币收益增加</t>
         </r>
       </text>
     </comment>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -402,40 +402,40 @@
     <t>愤怒的小鸟</t>
   </si>
   <si>
-    <t>1101_3</t>
+    <t>1101_4</t>
   </si>
   <si>
     <t>4010047_4010046_4010048</t>
   </si>
   <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>1202_3</t>
+  </si>
+  <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>1303_5</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1304_5</t>
+  </si>
+  <si>
     <t>象财神</t>
-  </si>
-  <si>
-    <t>1102_5</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
-  </si>
-  <si>
-    <t>1202_3</t>
-  </si>
-  <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_3</t>
-  </si>
-  <si>
-    <t>营销部</t>
   </si>
   <si>
     <t>1304_3</t>
@@ -539,13 +539,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1170,7 +1170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1213,23 +1213,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2015,23 +2018,23 @@
       <c r="F6" s="4">
         <v>1</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="14"/>
+      <c r="H6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="14" t="s">
         <v>43</v>
       </c>
       <c r="K6" s="10">
         <v>103900001</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="17">
         <v>103900</v>
       </c>
       <c r="N6" s="4">
@@ -2049,13 +2052,13 @@
     </row>
     <row r="7" s="3" customFormat="1" spans="1:20">
       <c r="A7" s="10">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -2066,49 +2069,48 @@
       <c r="F7" s="4">
         <v>3</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>43</v>
+      <c r="I7" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="K7" s="10">
-        <v>102700001</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="16">
-        <v>102700</v>
-      </c>
+        <v>4010017</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="3"/>
       <c r="N7" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O7" s="3">
         <v>60</v>
       </c>
       <c r="P7" s="3">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="Q7" s="3">
-        <v>1102</v>
-      </c>
+        <v>3551</v>
+      </c>
+      <c r="T7" s="18"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:20">
       <c r="A8" s="10">
-        <v>1202</v>
+        <v>1303</v>
       </c>
       <c r="B8" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2117,50 +2119,47 @@
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>50</v>
+      <c r="I8" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="K8" s="10">
-        <v>4010017</v>
+        <v>4010019</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O8" s="3">
         <v>60</v>
       </c>
-      <c r="P8" s="3">
-        <v>6000</v>
-      </c>
       <c r="Q8" s="3">
-        <v>3551</v>
-      </c>
-      <c r="T8" s="18"/>
+        <v>3552</v>
+      </c>
+      <c r="T8" s="19"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:20">
       <c r="A9" s="10">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B9" s="4">
         <v>3</v>
       </c>
       <c r="C9" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2169,22 +2168,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>4</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="17" t="s">
+      <c r="I9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>38</v>
       </c>
       <c r="K9" s="10">
-        <v>4010019</v>
+        <v>4010020</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>54</v>
@@ -2197,19 +2196,19 @@
         <v>60</v>
       </c>
       <c r="Q9" s="3">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="T9" s="19"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:20">
       <c r="A10" s="10">
-        <v>1304</v>
+        <v>1102</v>
       </c>
       <c r="B10" s="4">
-        <v>3</v>
-      </c>
-      <c r="C10" s="4">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2218,37 +2217,41 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>4</v>
-      </c>
-      <c r="G10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>38</v>
+      <c r="I10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="K10" s="10">
-        <v>4010020</v>
-      </c>
-      <c r="L10" s="10" t="s">
+        <v>102700001</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="3"/>
+      <c r="M10" s="17">
+        <v>102700</v>
+      </c>
       <c r="N10" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O10" s="3">
         <v>60</v>
       </c>
+      <c r="P10" s="3">
+        <v>8000</v>
+      </c>
       <c r="Q10" s="3">
-        <v>3553</v>
-      </c>
-      <c r="T10" s="19"/>
+        <v>1102</v>
+      </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:20">
       <c r="A11" s="10">
@@ -2272,7 +2275,7 @@
       <c r="G11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="20" t="s">
         <v>46</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2284,10 +2287,10 @@
       <c r="K11" s="10">
         <v>100700001</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="17">
         <v>100700</v>
       </c>
       <c r="N11" s="4">
@@ -2325,11 +2328,11 @@
       <c r="G12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="20" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>43</v>
@@ -2337,10 +2340,10 @@
       <c r="K12" s="10">
         <v>101800001</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="17">
         <v>101800</v>
       </c>
       <c r="N12" s="4">
@@ -2378,11 +2381,11 @@
       <c r="G13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="20" t="s">
         <v>46</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>43</v>
@@ -2390,7 +2393,7 @@
       <c r="K13" s="10">
         <v>103100001</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="16" t="s">
         <v>62</v>
       </c>
       <c r="M13" s="18">
@@ -2430,11 +2433,11 @@
         <v>19</v>
       </c>
       <c r="G14" s="4"/>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>43</v>
@@ -2442,7 +2445,7 @@
       <c r="K14" s="10">
         <v>102500001</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="16" t="s">
         <v>63</v>
       </c>
       <c r="M14" s="18">
@@ -2482,11 +2485,11 @@
         <v>23</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>43</v>
@@ -2494,7 +2497,7 @@
       <c r="K15" s="10">
         <v>101200001</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="16" t="s">
         <v>64</v>
       </c>
       <c r="M15" s="18">
@@ -2534,11 +2537,11 @@
         <v>27</v>
       </c>
       <c r="G16" s="4"/>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>43</v>
@@ -2546,10 +2549,10 @@
       <c r="K16" s="10">
         <v>100300001</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="17">
         <v>100300</v>
       </c>
       <c r="N16" s="4">
@@ -2586,11 +2589,11 @@
         <v>31</v>
       </c>
       <c r="G17" s="4"/>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>43</v>
@@ -2598,7 +2601,7 @@
       <c r="K17" s="10">
         <v>101500001</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="16" t="s">
         <v>66</v>
       </c>
       <c r="M17" s="18">
@@ -2637,11 +2640,11 @@
         <v>35</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>43</v>
@@ -2649,7 +2652,7 @@
       <c r="K18" s="10">
         <v>102000001</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="16" t="s">
         <v>67</v>
       </c>
       <c r="M18" s="18">
@@ -2688,11 +2691,11 @@
         <v>39</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>43</v>
@@ -2700,7 +2703,7 @@
       <c r="K19" s="10">
         <v>102100001</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="16" t="s">
         <v>68</v>
       </c>
       <c r="M19" s="18">
@@ -2739,11 +2742,11 @@
         <v>43</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="20" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>43</v>
@@ -2751,7 +2754,7 @@
       <c r="K20" s="10">
         <v>102200001</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="16" t="s">
         <v>69</v>
       </c>
       <c r="M20" s="18">
@@ -2799,9 +2802,9 @@
       <c r="L21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="10">
@@ -2831,9 +2834,9 @@
       <c r="L22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="10">
@@ -2863,9 +2866,9 @@
       <c r="L23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="10">
@@ -2892,13 +2895,13 @@
         <v>70</v>
       </c>
       <c r="K24" s="10"/>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="14"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
+      <c r="M24" s="20"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="10">
@@ -2925,23 +2928,23 @@
         <v>70</v>
       </c>
       <c r="K25" s="10"/>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="14"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
+      <c r="M25" s="20"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A5 A7:A25 A28:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -256,6 +256,28 @@
 这里的等级，根据 建筑配置表中的 最大等级来配置
 ：BuildingUpgradeTable.xlsx
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数据看板 中的跳转ID</t>
         </r>
       </text>
     </comment>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -2292,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>57</v>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>59</v>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>61</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="20" t="s">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -2013,7 +2013,7 @@
         <v>30</v>
       </c>
       <c r="O5" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P5" s="13"/>
       <c r="Q5" s="13">
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P6" s="3">
         <v>5000</v>
@@ -2113,8 +2113,8 @@
       <c r="N7" s="4">
         <v>20</v>
       </c>
-      <c r="O7" s="3">
-        <v>60</v>
+      <c r="O7" s="2">
+        <v>20</v>
       </c>
       <c r="P7" s="3">
         <v>6000</v>
@@ -2166,7 +2166,7 @@
         <v>30</v>
       </c>
       <c r="O8" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="3">
         <v>3552</v>
@@ -2214,8 +2214,8 @@
       <c r="N9" s="4">
         <v>30</v>
       </c>
-      <c r="O9" s="3">
-        <v>60</v>
+      <c r="O9" s="2">
+        <v>20</v>
       </c>
       <c r="Q9" s="3">
         <v>3553</v>
@@ -2266,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P10" s="3">
         <v>8000</v>
@@ -2318,8 +2318,8 @@
       <c r="N11" s="4">
         <v>10</v>
       </c>
-      <c r="O11" s="3">
-        <v>60</v>
+      <c r="O11" s="2">
+        <v>20</v>
       </c>
       <c r="P11" s="3">
         <v>5000</v>
@@ -2372,7 +2372,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P12" s="3">
         <v>5000</v>
@@ -2424,8 +2424,8 @@
       <c r="N13" s="4">
         <v>10</v>
       </c>
-      <c r="O13" s="3">
-        <v>60</v>
+      <c r="O13" s="2">
+        <v>20</v>
       </c>
       <c r="P13" s="3">
         <v>5000</v>
@@ -2477,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P14" s="3">
         <v>5000</v>
@@ -2528,8 +2528,8 @@
       <c r="N15" s="4">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
-        <v>60</v>
+      <c r="O15" s="2">
+        <v>20</v>
       </c>
       <c r="P15" s="3">
         <v>5000</v>
@@ -2581,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P16" s="3">
         <v>5000</v>
@@ -2632,8 +2632,8 @@
       <c r="N17" s="4">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
-        <v>60</v>
+      <c r="O17" s="2">
+        <v>20</v>
       </c>
       <c r="P17" s="3">
         <v>5000</v>
@@ -2684,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P18" s="3">
         <v>5000</v>
@@ -2734,8 +2734,8 @@
       <c r="N19" s="4">
         <v>10</v>
       </c>
-      <c r="O19" s="3">
-        <v>60</v>
+      <c r="O19" s="2">
+        <v>20</v>
       </c>
       <c r="P19" s="3">
         <v>5000</v>
@@ -2786,7 +2786,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P20" s="3">
         <v>5000</v>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>交互时间(MS)</t>
+  </si>
+  <si>
+    <t>奖励显示间隔（ms)</t>
   </si>
   <si>
     <t>跳转ID</t>
@@ -398,6 +401,9 @@
   </si>
   <si>
     <t>InteractTime</t>
+  </si>
+  <si>
+    <t>RewardDisplayInterval</t>
   </si>
   <si>
     <t>JumpId</t>
@@ -1788,7 +1794,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1805,12 +1811,14 @@
     <col min="13" max="13" width="16" style="3" customWidth="1"/>
     <col min="14" max="14" width="17.625" style="3" customWidth="1"/>
     <col min="15" max="15" width="10.375" style="3" customWidth="1"/>
-    <col min="16" max="17" width="12.75" style="3" customWidth="1"/>
-    <col min="18" max="18" width="11.9083333333333" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="3"/>
+    <col min="16" max="16" width="12.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.2" style="3" customWidth="1"/>
+    <col min="18" max="18" width="12.75" style="3" customWidth="1"/>
+    <col min="19" max="19" width="11.9083333333333" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:21">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1862,110 +1870,119 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:20">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:21">
       <c r="A2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="I2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:21">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="9"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:21">
       <c r="A4" s="10"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1979,7 +1996,7 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:20">
+    <row r="5" s="2" customFormat="1" spans="1:21">
       <c r="A5" s="11">
         <v>1301</v>
       </c>
@@ -2000,13 +2017,13 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K5" s="11">
         <v>4010018</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="12">
@@ -2015,13 +2032,16 @@
       <c r="O5" s="2">
         <v>20</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13">
+      <c r="P5" s="13">
+        <v>2000</v>
+      </c>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13">
         <v>3554</v>
       </c>
-      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:20">
+    <row r="6" s="3" customFormat="1" spans="1:21">
       <c r="A6" s="10">
         <v>1101</v>
       </c>
@@ -2029,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -2042,19 +2062,19 @@
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="10">
         <v>103900001</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M6" s="17">
         <v>103900</v>
@@ -2066,13 +2086,16 @@
         <v>20</v>
       </c>
       <c r="P6" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R6" s="3">
         <v>1101</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:20">
+    <row r="7" s="3" customFormat="1" spans="1:21">
       <c r="A7" s="10">
         <v>1202</v>
       </c>
@@ -2092,22 +2115,22 @@
         <v>3</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K7" s="10">
         <v>4010017</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="4">
@@ -2119,12 +2142,12 @@
       <c r="P7" s="3">
         <v>6000</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>3551</v>
       </c>
-      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:20">
+    <row r="8" s="3" customFormat="1" spans="1:21">
       <c r="A8" s="10">
         <v>1303</v>
       </c>
@@ -2144,22 +2167,22 @@
         <v>5</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8" s="10">
         <v>4010019</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4">
@@ -2168,12 +2191,12 @@
       <c r="O8" s="3">
         <v>20</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3552</v>
       </c>
-      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:20">
+    <row r="9" s="3" customFormat="1" spans="1:21">
       <c r="A9" s="10">
         <v>1304</v>
       </c>
@@ -2193,22 +2216,22 @@
         <v>5</v>
       </c>
       <c r="G9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="J9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K9" s="10">
         <v>4010020</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="4">
@@ -2217,12 +2240,12 @@
       <c r="O9" s="2">
         <v>20</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3553</v>
       </c>
-      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:20">
+    <row r="10" s="3" customFormat="1" spans="1:21">
       <c r="A10" s="10">
         <v>1102</v>
       </c>
@@ -2230,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2242,22 +2265,22 @@
         <v>6</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K10" s="10">
         <v>102700001</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M10" s="17">
         <v>102700</v>
@@ -2269,13 +2292,16 @@
         <v>20</v>
       </c>
       <c r="P10" s="3">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="Q10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R10" s="3">
         <v>1102</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:20">
+    <row r="11" s="3" customFormat="1" spans="1:21">
       <c r="A11" s="10">
         <v>1110</v>
       </c>
@@ -2283,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2295,22 +2321,22 @@
         <v>8</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K11" s="10">
         <v>100700001</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M11" s="17">
         <v>100700</v>
@@ -2322,13 +2348,16 @@
         <v>20</v>
       </c>
       <c r="P11" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q11" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R11" s="3">
         <v>3203</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:20">
+    <row r="12" s="3" customFormat="1" spans="1:21">
       <c r="A12" s="10">
         <v>1107</v>
       </c>
@@ -2336,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2348,22 +2377,22 @@
         <v>10</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K12" s="10">
         <v>101800001</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M12" s="17">
         <v>101800</v>
@@ -2375,13 +2404,16 @@
         <v>20</v>
       </c>
       <c r="P12" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R12" s="3">
         <v>3204</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:20">
+    <row r="13" s="3" customFormat="1" spans="1:21">
       <c r="A13" s="10">
         <v>1106</v>
       </c>
@@ -2389,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -2401,22 +2433,22 @@
         <v>13</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K13" s="10">
         <v>103100001</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M13" s="18">
         <v>103100</v>
@@ -2428,14 +2460,17 @@
         <v>20</v>
       </c>
       <c r="P13" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q13" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R13" s="3">
         <v>3208</v>
       </c>
-      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:20">
+    <row r="14" s="3" customFormat="1" spans="1:21">
       <c r="A14" s="10">
         <v>1105</v>
       </c>
@@ -2443,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -2456,19 +2491,19 @@
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="10">
         <v>102500001</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M14" s="18">
         <v>102500</v>
@@ -2480,14 +2515,17 @@
         <v>20</v>
       </c>
       <c r="P14" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R14" s="3">
         <v>3207</v>
       </c>
-      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:20">
+    <row r="15" s="3" customFormat="1" spans="1:21">
       <c r="A15" s="10">
         <v>1104</v>
       </c>
@@ -2495,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -2508,19 +2546,19 @@
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K15" s="10">
         <v>101200001</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M15" s="18">
         <v>101200</v>
@@ -2532,14 +2570,17 @@
         <v>20</v>
       </c>
       <c r="P15" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R15" s="3">
         <v>3206</v>
       </c>
-      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:20">
+    <row r="16" s="3" customFormat="1" spans="1:21">
       <c r="A16" s="10">
         <v>1103</v>
       </c>
@@ -2547,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -2560,19 +2601,19 @@
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K16" s="10">
         <v>100300001</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M16" s="17">
         <v>100300</v>
@@ -2584,14 +2625,17 @@
         <v>20</v>
       </c>
       <c r="P16" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q16" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R16" s="3">
         <v>3205</v>
       </c>
-      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:20">
+    <row r="17" s="3" customFormat="1" spans="1:21">
       <c r="A17" s="10">
         <v>1109</v>
       </c>
@@ -2599,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -2612,19 +2656,19 @@
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="10">
         <v>101500001</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M17" s="18">
         <v>101500</v>
@@ -2636,13 +2680,16 @@
         <v>20</v>
       </c>
       <c r="P17" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R17" s="3">
         <v>3212</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:20">
+    <row r="18" s="3" customFormat="1" spans="1:21">
       <c r="A18" s="10">
         <v>1108</v>
       </c>
@@ -2650,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -2663,19 +2710,19 @@
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="10">
         <v>102000001</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M18" s="18">
         <v>102000</v>
@@ -2687,13 +2734,16 @@
         <v>20</v>
       </c>
       <c r="P18" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R18" s="3">
         <v>3211</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:20">
+    <row r="19" s="3" customFormat="1" spans="1:21">
       <c r="A19" s="10">
         <v>1112</v>
       </c>
@@ -2701,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -2714,19 +2764,19 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K19" s="10">
         <v>102100001</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M19" s="18">
         <v>102100</v>
@@ -2738,13 +2788,16 @@
         <v>20</v>
       </c>
       <c r="P19" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q19" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R19" s="3">
         <v>3210</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:20">
+    <row r="20" s="3" customFormat="1" spans="1:21">
       <c r="A20" s="10">
         <v>1111</v>
       </c>
@@ -2752,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -2765,19 +2818,19 @@
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K20" s="10">
         <v>102200001</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M20" s="18">
         <v>102200</v>
@@ -2789,14 +2842,17 @@
         <v>20</v>
       </c>
       <c r="P20" s="3">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="Q20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R20" s="3">
         <v>3209</v>
       </c>
-      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:21">
       <c r="A21" s="10">
         <v>1401</v>
       </c>
@@ -2815,20 +2871,21 @@
       <c r="F21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:21">
       <c r="A22" s="10">
         <v>1402</v>
       </c>
@@ -2847,20 +2904,21 @@
       <c r="F22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
       <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:21">
       <c r="A23" s="10">
         <v>1403</v>
       </c>
@@ -2879,20 +2937,21 @@
       <c r="F23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:21">
       <c r="A24" s="10">
         <v>1404</v>
       </c>
@@ -2911,21 +2970,22 @@
       <c r="F24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M24" s="20"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:21">
       <c r="A25" s="10">
         <v>1405</v>
       </c>
@@ -2944,19 +3004,20 @@
       <c r="F25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M25" s="20"/>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -2033,7 +2033,7 @@
         <v>20</v>
       </c>
       <c r="P5" s="13">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="Q5" s="13"/>
       <c r="R5" s="13">
@@ -2086,7 +2086,7 @@
         <v>20</v>
       </c>
       <c r="P6" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="Q6" s="3">
         <v>3000</v>
@@ -2140,7 +2140,7 @@
         <v>20</v>
       </c>
       <c r="P7" s="3">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="R7" s="3">
         <v>3551</v>
@@ -2292,7 +2292,7 @@
         <v>20</v>
       </c>
       <c r="P10" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="Q10" s="3">
         <v>3000</v>
@@ -2348,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="P11" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="Q11" s="3">
         <v>3000</v>
@@ -2404,7 +2404,7 @@
         <v>20</v>
       </c>
       <c r="P12" s="3">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="Q12" s="3">
         <v>3000</v>
@@ -2460,7 +2460,7 @@
         <v>20</v>
       </c>
       <c r="P13" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q13" s="3">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>20</v>
       </c>
       <c r="P14" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q14" s="3">
         <v>3000</v>
@@ -2570,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="P15" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q15" s="3">
         <v>3000</v>
@@ -2625,7 +2625,7 @@
         <v>20</v>
       </c>
       <c r="P16" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q16" s="3">
         <v>3000</v>
@@ -2680,7 +2680,7 @@
         <v>20</v>
       </c>
       <c r="P17" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q17" s="3">
         <v>3000</v>
@@ -2734,7 +2734,7 @@
         <v>20</v>
       </c>
       <c r="P18" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q18" s="3">
         <v>3000</v>
@@ -2788,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="P19" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q19" s="3">
         <v>3000</v>
@@ -2842,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="P20" s="3">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="Q20" s="3">
         <v>3000</v>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="80">
   <si>
     <t>ID</t>
   </si>
@@ -421,7 +421,7 @@
     <t>4010047_0_4010048</t>
   </si>
   <si>
-    <t>1990000_10000</t>
+    <t>1990000_100</t>
   </si>
   <si>
     <t>游戏</t>
@@ -430,76 +430,82 @@
     <t>愤怒的小鸟</t>
   </si>
   <si>
-    <t>1101_4</t>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>VIP休息区</t>
+  </si>
+  <si>
+    <t>运营部</t>
+  </si>
+  <si>
+    <t>营销部</t>
+  </si>
+  <si>
+    <t>1101_10</t>
   </si>
   <si>
     <t>4010047_4010046_4010048</t>
   </si>
   <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>VIP休息区</t>
-  </si>
-  <si>
-    <t>1202_3</t>
-  </si>
-  <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>运营部</t>
-  </si>
-  <si>
-    <t>1303_5</t>
-  </si>
-  <si>
-    <t>营销部</t>
-  </si>
-  <si>
-    <t>1304_5</t>
-  </si>
-  <si>
     <t>象财神</t>
   </si>
   <si>
-    <t>1304_3</t>
+    <t>1102_10</t>
   </si>
   <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1110_12</t>
+    <t>1110_10</t>
   </si>
   <si>
     <t>篮球巨星</t>
   </si>
   <si>
-    <t>1107_15</t>
+    <t>1107_10</t>
   </si>
   <si>
     <t>绿巨人</t>
   </si>
   <si>
+    <t>1106_10</t>
+  </si>
+  <si>
     <t>寒冰王座</t>
   </si>
   <si>
+    <t>1105_10</t>
+  </si>
+  <si>
     <t>财神来了</t>
   </si>
   <si>
+    <t>1104_10</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
+    <t>1103_10</t>
+  </si>
+  <si>
     <t>狼月</t>
   </si>
   <si>
+    <t>1109_10</t>
+  </si>
+  <si>
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
+    <t>1108_10</t>
+  </si>
+  <si>
     <t>杰克船长</t>
+  </si>
+  <si>
+    <t>1112_10</t>
   </si>
   <si>
     <t>雷神</t>
@@ -733,12 +739,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1074,7 +1086,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1098,16 +1110,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1116,89 +1128,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1252,6 +1264,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2111,26 +2126,24 @@
       <c r="E7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="4">
-        <v>3</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="18">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="K7" s="10">
         <v>4010017</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="4">
@@ -2145,7 +2158,7 @@
       <c r="R7" s="3">
         <v>3551</v>
       </c>
-      <c r="U7" s="18"/>
+      <c r="U7" s="19"/>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:21">
       <c r="A8" s="10">
@@ -2163,17 +2176,15 @@
       <c r="E8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="4">
-        <v>5</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>52</v>
-      </c>
+      <c r="F8" s="18">
+        <v>3</v>
+      </c>
+      <c r="G8" s="14"/>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>40</v>
@@ -2182,7 +2193,7 @@
         <v>4010019</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4">
@@ -2194,7 +2205,7 @@
       <c r="R8" s="3">
         <v>3552</v>
       </c>
-      <c r="U8" s="19"/>
+      <c r="U8" s="20"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:21">
       <c r="A9" s="10">
@@ -2212,17 +2223,15 @@
       <c r="E9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="4">
-        <v>5</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>55</v>
-      </c>
+      <c r="F9" s="18">
+        <v>4</v>
+      </c>
+      <c r="G9" s="14"/>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>40</v>
@@ -2231,7 +2240,7 @@
         <v>4010020</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="4">
@@ -2243,7 +2252,7 @@
       <c r="R9" s="3">
         <v>3553</v>
       </c>
-      <c r="U9" s="19"/>
+      <c r="U9" s="20"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:21">
       <c r="A10" s="10">
@@ -2265,10 +2274,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>44</v>
@@ -2280,7 +2289,7 @@
         <v>102700001</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M10" s="17">
         <v>102700</v>
@@ -2318,15 +2327,15 @@
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <v>8</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="4" t="s">
@@ -2336,7 +2345,7 @@
         <v>100700001</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M11" s="17">
         <v>100700</v>
@@ -2374,16 +2383,16 @@
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>45</v>
@@ -2392,7 +2401,7 @@
         <v>101800001</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M12" s="17">
         <v>101800</v>
@@ -2430,16 +2439,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>45</v>
@@ -2448,9 +2457,9 @@
         <v>103100001</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M13" s="18">
+        <v>59</v>
+      </c>
+      <c r="M13" s="19">
         <v>103100</v>
       </c>
       <c r="N13" s="4">
@@ -2468,7 +2477,7 @@
       <c r="R13" s="3">
         <v>3208</v>
       </c>
-      <c r="U13" s="18"/>
+      <c r="U13" s="19"/>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:21">
       <c r="A14" s="10">
@@ -2487,14 +2496,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>17</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>49</v>
+        <v>26</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>45</v>
@@ -2503,9 +2514,9 @@
         <v>102500001</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M14" s="18">
+        <v>61</v>
+      </c>
+      <c r="M14" s="19">
         <v>102500</v>
       </c>
       <c r="N14" s="4">
@@ -2523,7 +2534,7 @@
       <c r="R14" s="3">
         <v>3207</v>
       </c>
-      <c r="U14" s="18"/>
+      <c r="U14" s="19"/>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:21">
       <c r="A15" s="10">
@@ -2542,14 +2553,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <v>23</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>45</v>
@@ -2558,9 +2571,9 @@
         <v>101200001</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="18">
+        <v>63</v>
+      </c>
+      <c r="M15" s="19">
         <v>101200</v>
       </c>
       <c r="N15" s="4">
@@ -2578,7 +2591,7 @@
       <c r="R15" s="3">
         <v>3206</v>
       </c>
-      <c r="U15" s="18"/>
+      <c r="U15" s="19"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:21">
       <c r="A16" s="10">
@@ -2597,14 +2610,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>27</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>45</v>
@@ -2613,7 +2628,7 @@
         <v>100300001</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M16" s="17">
         <v>100300</v>
@@ -2633,7 +2648,7 @@
       <c r="R16" s="3">
         <v>3205</v>
       </c>
-      <c r="U16" s="18"/>
+      <c r="U16" s="19"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:21">
       <c r="A17" s="10">
@@ -2652,14 +2667,16 @@
         <v>1</v>
       </c>
       <c r="F17" s="4">
-        <v>31</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>45</v>
@@ -2668,9 +2685,9 @@
         <v>101500001</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="M17" s="18">
+        <v>67</v>
+      </c>
+      <c r="M17" s="19">
         <v>101500</v>
       </c>
       <c r="N17" s="4">
@@ -2706,14 +2723,16 @@
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>35</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>45</v>
@@ -2724,7 +2743,7 @@
       <c r="L18" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="19">
         <v>102000</v>
       </c>
       <c r="N18" s="4">
@@ -2760,14 +2779,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="4">
-        <v>39</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>45</v>
@@ -2776,9 +2797,9 @@
         <v>102100001</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M19" s="18">
+        <v>71</v>
+      </c>
+      <c r="M19" s="19">
         <v>102100</v>
       </c>
       <c r="N19" s="4">
@@ -2814,14 +2835,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="4">
-        <v>43</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>45</v>
@@ -2830,9 +2853,9 @@
         <v>102200001</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="M20" s="18">
+        <v>73</v>
+      </c>
+      <c r="M20" s="19">
         <v>102200</v>
       </c>
       <c r="N20" s="4">
@@ -2850,7 +2873,7 @@
       <c r="R20" s="3">
         <v>3209</v>
       </c>
-      <c r="U20" s="18"/>
+      <c r="U20" s="19"/>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="10">
@@ -2870,15 +2893,15 @@
       </c>
       <c r="F21" s="4"/>
       <c r="H21" s="4"/>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
@@ -2903,15 +2926,15 @@
       </c>
       <c r="F22" s="4"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
@@ -2936,15 +2959,15 @@
       </c>
       <c r="F23" s="4"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
@@ -2969,17 +2992,17 @@
       </c>
       <c r="F24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K24" s="10"/>
-      <c r="L24" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="M24" s="20"/>
+      <c r="L24" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="21"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
@@ -3003,17 +3026,17 @@
       </c>
       <c r="F25" s="4"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="14" t="s">
         <v>44</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K25" s="10"/>
-      <c r="L25" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25" s="20"/>
+      <c r="L25" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" s="21"/>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
@@ -3021,16 +3044,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A5 A7:A25 A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingAreaTable" sheetId="1" r:id="rId1"/>
@@ -728,12 +728,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2101,7 +2101,7 @@
         <v>20</v>
       </c>
       <c r="P6" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="Q6" s="3">
         <v>3000</v>
@@ -2301,7 +2301,7 @@
         <v>20</v>
       </c>
       <c r="P10" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="Q10" s="3">
         <v>3000</v>
@@ -2357,7 +2357,7 @@
         <v>20</v>
       </c>
       <c r="P11" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="Q11" s="3">
         <v>3000</v>
@@ -2413,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="P12" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="Q12" s="3">
         <v>3000</v>
@@ -2469,7 +2469,7 @@
         <v>20</v>
       </c>
       <c r="P13" s="3">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="Q13" s="3">
         <v>3000</v>
@@ -2526,7 +2526,7 @@
         <v>20</v>
       </c>
       <c r="P14" s="3">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="Q14" s="3">
         <v>3000</v>
@@ -2583,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="P15" s="3">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="Q15" s="3">
         <v>3000</v>
@@ -2640,7 +2640,7 @@
         <v>20</v>
       </c>
       <c r="P16" s="3">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="Q16" s="3">
         <v>3000</v>
@@ -2697,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="P17" s="3">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="Q17" s="3">
         <v>3000</v>
@@ -2753,7 +2753,7 @@
         <v>20</v>
       </c>
       <c r="P18" s="3">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="Q18" s="3">
         <v>3000</v>
@@ -2809,7 +2809,7 @@
         <v>20</v>
       </c>
       <c r="P19" s="3">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="Q19" s="3">
         <v>3000</v>
@@ -2865,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="P20" s="3">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="Q20" s="3">
         <v>3000</v>

--- a/hall/resources/sample/BuildingAreaTable.xlsx
+++ b/hall/resources/sample/BuildingAreaTable.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -442,7 +442,7 @@
     <t>营销部</t>
   </si>
   <si>
-    <t>1101_10</t>
+    <t>1101_5</t>
   </si>
   <si>
     <t>4010047_4010046_4010048</t>
@@ -451,19 +451,13 @@
     <t>象财神</t>
   </si>
   <si>
-    <t>1102_10</t>
-  </si>
-  <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>1110_10</t>
+    <t>1110_7</t>
   </si>
   <si>
     <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>1107_10</t>
   </si>
   <si>
     <t>绿巨人</t>
@@ -728,12 +722,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2271,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>51</v>
@@ -2327,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>52</v>
@@ -2345,7 +2339,7 @@
         <v>100700001</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M11" s="17">
         <v>100700</v>
@@ -2383,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>52</v>
@@ -2401,7 +2395,7 @@
         <v>101800001</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="17">
         <v>101800</v>
@@ -2439,10 +2433,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>52</v>
@@ -2457,7 +2451,7 @@
         <v>103100001</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M13" s="19">
         <v>103100</v>
@@ -2496,10 +2490,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>52</v>
@@ -2514,7 +2508,7 @@
         <v>102500001</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M14" s="19">
         <v>102500</v>
@@ -2553,10 +2547,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>52</v>
@@ -2571,7 +2565,7 @@
         <v>101200001</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M15" s="19">
         <v>101200</v>
@@ -2610,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>52</v>
@@ -2628,7 +2622,7 @@
         <v>100300001</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M16" s="17">
         <v>100300</v>
@@ -2667,10 +2661,10 @@
         <v>1</v>
       </c>
       <c r="F17" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>52</v>
@@ -2685,7 +2679,7 @@
         <v>101500001</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M17" s="19">
         <v>101500</v>
@@ -2723,10 +2717,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>52</v>
@@ -2741,7 +2735,7 @@
         <v>102000001</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M18" s="19">
         <v>102000</v>
@@ -2779,10 +2773,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>52</v>
@@ -2797,7 +2791,7 @@
         <v>102100001</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M19" s="19">
         <v>102100</v>
@@ -2835,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>52</v>
@@ -2853,7 +2847,7 @@
         <v>102200001</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M20" s="19">
         <v>102200</v>
@@ -2897,11 +2891,11 @@
         <v>44</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
@@ -2930,11 +2924,11 @@
         <v>44</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
@@ -2963,11 +2957,11 @@
         <v>44</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
@@ -2996,11 +2990,11 @@
         <v>44</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M24" s="21"/>
       <c r="P24" s="16"/>
@@ -3030,11 +3024,11 @@
         <v>44</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M25" s="21"/>
       <c r="P25" s="16"/>
@@ -3044,19 +3038,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A5 A7:A25 A28:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
